--- a/Predictions/timestamp_rolling_gt_next_tick.xlsx
+++ b/Predictions/timestamp_rolling_gt_next_tick.xlsx
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>21.44140815734863</v>
+        <v>21.44140625</v>
       </c>
       <c r="B2" t="n">
-        <v>6.114813327789307</v>
+        <v>6.114814281463623</v>
       </c>
       <c r="C2" t="n">
         <v>1.687668561935425</v>
@@ -474,7 +474,7 @@
         <v>16.07298469543457</v>
       </c>
       <c r="E2" t="n">
-        <v>55.25888061523438</v>
+        <v>55.25887680053711</v>
       </c>
       <c r="F2" t="n">
         <v>-4.423366069793701</v>
@@ -485,10 +485,10 @@
         <v>19.59602355957031</v>
       </c>
       <c r="B3" t="n">
-        <v>5.919834613800049</v>
+        <v>5.919833660125732</v>
       </c>
       <c r="C3" t="n">
-        <v>2.981912136077881</v>
+        <v>2.981911897659302</v>
       </c>
       <c r="D3" t="n">
         <v>19.03303527832031</v>
@@ -497,7 +497,7 @@
         <v>55.29248809814453</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.138886213302612</v>
+        <v>-1.138886451721191</v>
       </c>
     </row>
     <row r="4">
@@ -505,7 +505,7 @@
         <v>17.61653137207031</v>
       </c>
       <c r="B4" t="n">
-        <v>5.380171298980713</v>
+        <v>5.380170345306396</v>
       </c>
       <c r="C4" t="n">
         <v>3.968274831771851</v>
@@ -545,19 +545,19 @@
         <v>13.49853134155273</v>
       </c>
       <c r="B6" t="n">
-        <v>3.635778903961182</v>
+        <v>3.635779857635498</v>
       </c>
       <c r="C6" t="n">
-        <v>5.488000392913818</v>
+        <v>5.48799991607666</v>
       </c>
       <c r="D6" t="n">
-        <v>26.14764976501465</v>
+        <v>26.14765167236328</v>
       </c>
       <c r="E6" t="n">
         <v>46.0722541809082</v>
       </c>
       <c r="F6" t="n">
-        <v>6.949481010437012</v>
+        <v>6.949480533599854</v>
       </c>
     </row>
     <row r="7">
@@ -565,7 +565,7 @@
         <v>11.46507358551025</v>
       </c>
       <c r="B7" t="n">
-        <v>2.587293148040771</v>
+        <v>2.587292194366455</v>
       </c>
       <c r="C7" t="n">
         <v>6.158910751342773</v>
@@ -574,7 +574,7 @@
         <v>27.96586418151855</v>
       </c>
       <c r="E7" t="n">
-        <v>40.49612045288086</v>
+        <v>40.49611663818359</v>
       </c>
       <c r="F7" t="n">
         <v>8.029861450195312</v>
@@ -585,10 +585,10 @@
         <v>9.480586051940918</v>
       </c>
       <c r="B8" t="n">
-        <v>1.515555024147034</v>
+        <v>1.515554904937744</v>
       </c>
       <c r="C8" t="n">
-        <v>6.814532279968262</v>
+        <v>6.814531803131104</v>
       </c>
       <c r="D8" t="n">
         <v>29.4472770690918</v>
@@ -605,33 +605,33 @@
         <v>7.545021057128906</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4990278482437134</v>
+        <v>0.4990276992321014</v>
       </c>
       <c r="C9" t="n">
         <v>7.496321678161621</v>
       </c>
       <c r="D9" t="n">
-        <v>30.52943801879883</v>
+        <v>30.52943992614746</v>
       </c>
       <c r="E9" t="n">
         <v>26.73877334594727</v>
       </c>
       <c r="F9" t="n">
-        <v>7.803411483764648</v>
+        <v>7.80341100692749</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5.665897369384766</v>
+        <v>5.665896892547607</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.3710817098617554</v>
+        <v>-0.3710818588733673</v>
       </c>
       <c r="C10" t="n">
         <v>8.258571624755859</v>
       </c>
       <c r="D10" t="n">
-        <v>31.18669128417969</v>
+        <v>31.18669319152832</v>
       </c>
       <c r="E10" t="n">
         <v>19.17094230651855</v>
@@ -642,30 +642,30 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3.868793249130249</v>
+        <v>3.868793964385986</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.9978708028793335</v>
+        <v>-0.9978709816932678</v>
       </c>
       <c r="C11" t="n">
-        <v>9.133467674255371</v>
+        <v>9.133468627929688</v>
       </c>
       <c r="D11" t="n">
         <v>31.4458179473877</v>
       </c>
       <c r="E11" t="n">
-        <v>11.62716674804688</v>
+        <v>11.62716579437256</v>
       </c>
       <c r="F11" t="n">
-        <v>5.568443775177002</v>
+        <v>5.568443298339844</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2.187930822372437</v>
+        <v>2.187931537628174</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.318833708763123</v>
+        <v>-1.318831920623779</v>
       </c>
       <c r="C12" t="n">
         <v>10.08470821380615</v>
@@ -674,7 +674,7 @@
         <v>31.3984489440918</v>
       </c>
       <c r="E12" t="n">
-        <v>4.618947505950928</v>
+        <v>4.618947982788086</v>
       </c>
       <c r="F12" t="n">
         <v>4.522222995758057</v>
@@ -682,10 +682,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.650766134262085</v>
+        <v>0.6507658362388611</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.312886595726013</v>
+        <v>-1.312886714935303</v>
       </c>
       <c r="C13" t="n">
         <v>11.02143955230713</v>
@@ -694,38 +694,38 @@
         <v>31.20336723327637</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.256485462188721</v>
+        <v>-1.256487011909485</v>
       </c>
       <c r="F13" t="n">
-        <v>4.039758682250977</v>
+        <v>4.039758205413818</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.7364141941070557</v>
+        <v>-0.7364144921302795</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.9886602163314819</v>
+        <v>-0.9886603951454163</v>
       </c>
       <c r="C14" t="n">
-        <v>11.83179378509521</v>
+        <v>11.8317928314209</v>
       </c>
       <c r="D14" t="n">
         <v>30.99928665161133</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.457664966583252</v>
+        <v>-5.457664489746094</v>
       </c>
       <c r="F14" t="n">
-        <v>4.073398113250732</v>
+        <v>4.073397636413574</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-1.997195482254028</v>
+        <v>-1.997194766998291</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.3740171194076538</v>
+        <v>-0.3740153610706329</v>
       </c>
       <c r="C15" t="n">
         <v>12.39922714233398</v>
@@ -734,18 +734,18 @@
         <v>30.85886573791504</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.632524967193604</v>
+        <v>-7.632524490356445</v>
       </c>
       <c r="F15" t="n">
-        <v>4.258270740509033</v>
+        <v>4.258270263671875</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-3.188065767288208</v>
+        <v>-3.188065052032471</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4734827280044556</v>
+        <v>0.4734825789928436</v>
       </c>
       <c r="C16" t="n">
         <v>12.64423179626465</v>
@@ -754,58 +754,58 @@
         <v>30.77327919006348</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.68272066116333</v>
+        <v>-7.682722091674805</v>
       </c>
       <c r="F16" t="n">
-        <v>4.103098392486572</v>
+        <v>4.103097915649414</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-4.351275444030762</v>
+        <v>-4.351274967193604</v>
       </c>
       <c r="B17" t="n">
-        <v>1.528610825538635</v>
+        <v>1.528610706329346</v>
       </c>
       <c r="C17" t="n">
         <v>12.49044704437256</v>
       </c>
       <c r="D17" t="n">
-        <v>30.66972732543945</v>
+        <v>30.66972923278809</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.047764301300049</v>
+        <v>-6.047765731811523</v>
       </c>
       <c r="F17" t="n">
-        <v>3.16002345085144</v>
+        <v>3.160023212432861</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-5.475905418395996</v>
+        <v>-5.475904941558838</v>
       </c>
       <c r="B18" t="n">
         <v>2.834546566009521</v>
       </c>
       <c r="C18" t="n">
-        <v>11.81196022033691</v>
+        <v>11.8119592666626</v>
       </c>
       <c r="D18" t="n">
         <v>30.48380851745605</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.294216632843018</v>
+        <v>-3.294218301773071</v>
       </c>
       <c r="F18" t="n">
-        <v>1.22650408744812</v>
+        <v>1.226503968238831</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-6.448916435241699</v>
+        <v>-6.448917865753174</v>
       </c>
       <c r="B19" t="n">
-        <v>4.556563854217529</v>
+        <v>4.556564807891846</v>
       </c>
       <c r="C19" t="n">
         <v>10.3313102722168</v>
@@ -814,27 +814,27 @@
         <v>30.19507789611816</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06810718774795532</v>
+        <v>0.06810939311981201</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.259037494659424</v>
+        <v>-1.259037256240845</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-7.070195198059082</v>
+        <v>-7.070194721221924</v>
       </c>
       <c r="B20" t="n">
-        <v>6.916427135467529</v>
+        <v>6.916428089141846</v>
       </c>
       <c r="C20" t="n">
         <v>7.71525764465332</v>
       </c>
       <c r="D20" t="n">
-        <v>33.2146110534668</v>
+        <v>33.21461486816406</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9901661276817322</v>
+        <v>-0.9901658296585083</v>
       </c>
       <c r="F20" t="n">
         <v>1.466728448867798</v>
@@ -842,10 +842,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-7.093592643737793</v>
+        <v>-7.093594074249268</v>
       </c>
       <c r="B21" t="n">
-        <v>10.16660118103027</v>
+        <v>10.16660022735596</v>
       </c>
       <c r="C21" t="n">
         <v>3.634465217590332</v>
@@ -854,35 +854,35 @@
         <v>32.7855110168457</v>
       </c>
       <c r="E21" t="n">
-        <v>2.01120138168335</v>
+        <v>2.011201620101929</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8537764549255371</v>
+        <v>-0.8537766933441162</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-6.299344062805176</v>
+        <v>-6.299343585968018</v>
       </c>
       <c r="B22" t="n">
-        <v>14.49208831787109</v>
+        <v>14.49208736419678</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.859313011169434</v>
+        <v>-1.859313368797302</v>
       </c>
       <c r="D22" t="n">
-        <v>32.17982482910156</v>
+        <v>32.17982864379883</v>
       </c>
       <c r="E22" t="n">
-        <v>4.955769062042236</v>
+        <v>4.955769538879395</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.485604763031006</v>
+        <v>-2.485605001449585</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-4.545924186706543</v>
+        <v>-4.545923709869385</v>
       </c>
       <c r="B23" t="n">
         <v>19.91064834594727</v>
@@ -891,18 +891,18 @@
         <v>-7.802365779876709</v>
       </c>
       <c r="D23" t="n">
-        <v>31.40562057495117</v>
+        <v>31.4056224822998</v>
       </c>
       <c r="E23" t="n">
-        <v>7.610508441925049</v>
+        <v>7.610507965087891</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.901726245880127</v>
+        <v>-2.90172553062439</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-1.955256700515747</v>
+        <v>-1.95525598526001</v>
       </c>
       <c r="B24" t="n">
         <v>25.99744606018066</v>
@@ -917,18 +917,18 @@
         <v>9.75511360168457</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.094965934753418</v>
+        <v>-2.094965696334839</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1.239973783493042</v>
+        <v>1.239973545074463</v>
       </c>
       <c r="B25" t="n">
-        <v>32.0445671081543</v>
+        <v>32.04457092285156</v>
       </c>
       <c r="C25" t="n">
-        <v>-14.51277160644531</v>
+        <v>-14.512770652771</v>
       </c>
       <c r="D25" t="n">
         <v>29.25117301940918</v>
@@ -942,16 +942,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4.734204292297363</v>
+        <v>4.734203815460205</v>
       </c>
       <c r="B26" t="n">
         <v>37.17813110351562</v>
       </c>
       <c r="C26" t="n">
-        <v>-13.66947174072266</v>
+        <v>-13.66947078704834</v>
       </c>
       <c r="D26" t="n">
-        <v>27.81206703186035</v>
+        <v>27.81206893920898</v>
       </c>
       <c r="E26" t="n">
         <v>11.90242004394531</v>
@@ -971,13 +971,13 @@
         <v>-10.5537166595459</v>
       </c>
       <c r="D27" t="n">
-        <v>26.13946914672852</v>
+        <v>26.13947105407715</v>
       </c>
       <c r="E27" t="n">
         <v>12.00064373016357</v>
       </c>
       <c r="F27" t="n">
-        <v>2.994667053222656</v>
+        <v>2.994666814804077</v>
       </c>
     </row>
     <row r="28">
@@ -1008,7 +1008,7 @@
         <v>41.62061309814453</v>
       </c>
       <c r="C29" t="n">
-        <v>-2.210516452789307</v>
+        <v>-2.210516691207886</v>
       </c>
       <c r="D29" t="n">
         <v>22.28615951538086</v>
@@ -1025,7 +1025,7 @@
         <v>17.20433235168457</v>
       </c>
       <c r="B30" t="n">
-        <v>39.36634826660156</v>
+        <v>39.36635208129883</v>
       </c>
       <c r="C30" t="n">
         <v>1.327176213264465</v>
@@ -1057,7 +1057,7 @@
         <v>9.274946212768555</v>
       </c>
       <c r="F31" t="n">
-        <v>7.433788776397705</v>
+        <v>7.433788299560547</v>
       </c>
     </row>
     <row r="32">
@@ -1074,7 +1074,7 @@
         <v>16.00725746154785</v>
       </c>
       <c r="E32" t="n">
-        <v>8.332728385925293</v>
+        <v>8.332729339599609</v>
       </c>
       <c r="F32" t="n">
         <v>8.257535934448242</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>22.99179077148438</v>
+        <v>22.99178886413574</v>
       </c>
       <c r="B33" t="n">
         <v>25.12253761291504</v>
@@ -1094,27 +1094,27 @@
         <v>13.93195343017578</v>
       </c>
       <c r="E33" t="n">
-        <v>7.443483829498291</v>
+        <v>7.443483352661133</v>
       </c>
       <c r="F33" t="n">
-        <v>9.117576599121094</v>
+        <v>9.117575645446777</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>24.23853492736816</v>
+        <v>24.2385368347168</v>
       </c>
       <c r="B34" t="n">
         <v>19.04565238952637</v>
       </c>
       <c r="C34" t="n">
-        <v>5.743017673492432</v>
+        <v>5.74301815032959</v>
       </c>
       <c r="D34" t="n">
-        <v>11.93467235565186</v>
+        <v>11.93467330932617</v>
       </c>
       <c r="E34" t="n">
-        <v>6.658355236053467</v>
+        <v>6.658356666564941</v>
       </c>
       <c r="F34" t="n">
         <v>10.03778266906738</v>
@@ -1131,10 +1131,10 @@
         <v>5.093740940093994</v>
       </c>
       <c r="D35" t="n">
-        <v>10.06984424591064</v>
+        <v>10.06984519958496</v>
       </c>
       <c r="E35" t="n">
-        <v>6.036590099334717</v>
+        <v>6.036589622497559</v>
       </c>
       <c r="F35" t="n">
         <v>11.03246116638184</v>
@@ -1142,7 +1142,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>25.90891075134277</v>
+        <v>25.90891265869141</v>
       </c>
       <c r="B36" t="n">
         <v>6.407106876373291</v>
@@ -1154,7 +1154,7 @@
         <v>8.393510818481445</v>
       </c>
       <c r="E36" t="n">
-        <v>5.63928747177124</v>
+        <v>5.639286994934082</v>
       </c>
       <c r="F36" t="n">
         <v>12.10856056213379</v>
@@ -1165,7 +1165,7 @@
         <v>26.47961616516113</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1908765882253647</v>
+        <v>0.1908764392137527</v>
       </c>
       <c r="C37" t="n">
         <v>3.902754306793213</v>
@@ -1174,7 +1174,7 @@
         <v>6.927595138549805</v>
       </c>
       <c r="E37" t="n">
-        <v>5.495574474334717</v>
+        <v>5.495574951171875</v>
       </c>
       <c r="F37" t="n">
         <v>13.25740051269531</v>
@@ -1185,7 +1185,7 @@
         <v>27.01716804504395</v>
       </c>
       <c r="B38" t="n">
-        <v>-5.453996181488037</v>
+        <v>-5.453994274139404</v>
       </c>
       <c r="C38" t="n">
         <v>3.77524209022522</v>
@@ -1194,7 +1194,7 @@
         <v>5.653020858764648</v>
       </c>
       <c r="E38" t="n">
-        <v>5.607202053070068</v>
+        <v>5.60720157623291</v>
       </c>
       <c r="F38" t="n">
         <v>14.44929218292236</v>
@@ -1205,7 +1205,7 @@
         <v>27.63172721862793</v>
       </c>
       <c r="B39" t="n">
-        <v>-9.88369083404541</v>
+        <v>-9.883689880371094</v>
       </c>
       <c r="C39" t="n">
         <v>3.769729852676392</v>
@@ -1214,7 +1214,7 @@
         <v>4.520417213439941</v>
       </c>
       <c r="E39" t="n">
-        <v>5.964938640594482</v>
+        <v>5.964939117431641</v>
       </c>
       <c r="F39" t="n">
         <v>15.62326335906982</v>
@@ -1225,16 +1225,16 @@
         <v>28.34905624389648</v>
       </c>
       <c r="B40" t="n">
-        <v>-12.5137357711792</v>
+        <v>-12.51373863220215</v>
       </c>
       <c r="C40" t="n">
-        <v>3.639242887496948</v>
+        <v>3.639243125915527</v>
       </c>
       <c r="D40" t="n">
-        <v>3.458949089050293</v>
+        <v>3.458948135375977</v>
       </c>
       <c r="E40" t="n">
-        <v>6.569222927093506</v>
+        <v>6.569222450256348</v>
       </c>
       <c r="F40" t="n">
         <v>16.68514633178711</v>
@@ -1245,7 +1245,7 @@
         <v>29.06997489929199</v>
       </c>
       <c r="B41" t="n">
-        <v>-13.12063121795654</v>
+        <v>-13.12063217163086</v>
       </c>
       <c r="C41" t="n">
         <v>3.326799869537354</v>
@@ -1254,10 +1254,10 @@
         <v>2.391517639160156</v>
       </c>
       <c r="E41" t="n">
-        <v>7.427855968475342</v>
+        <v>7.4278564453125</v>
       </c>
       <c r="F41" t="n">
-        <v>17.55253410339355</v>
+        <v>17.55253219604492</v>
       </c>
     </row>
     <row r="42">
@@ -1265,10 +1265,10 @@
         <v>29.58150672912598</v>
       </c>
       <c r="B42" t="n">
-        <v>-11.96098804473877</v>
+        <v>-11.96098899841309</v>
       </c>
       <c r="C42" t="n">
-        <v>2.848669052124023</v>
+        <v>2.848669290542603</v>
       </c>
       <c r="D42" t="n">
         <v>1.275003433227539</v>
@@ -1285,19 +1285,19 @@
         <v>29.70211601257324</v>
       </c>
       <c r="B43" t="n">
-        <v>-9.792624473571777</v>
+        <v>-9.792625427246094</v>
       </c>
       <c r="C43" t="n">
         <v>2.015948534011841</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1299047321081161</v>
+        <v>0.1299048066139221</v>
       </c>
       <c r="E43" t="n">
         <v>10.13568115234375</v>
       </c>
       <c r="F43" t="n">
-        <v>18.32455635070801</v>
+        <v>18.32455444335938</v>
       </c>
     </row>
     <row r="44">
@@ -1305,13 +1305,13 @@
         <v>29.37685966491699</v>
       </c>
       <c r="B44" t="n">
-        <v>-7.267556667327881</v>
+        <v>-7.267554759979248</v>
       </c>
       <c r="C44" t="n">
         <v>0.4735918343067169</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.9172849655151367</v>
+        <v>-0.9172829985618591</v>
       </c>
       <c r="E44" t="n">
         <v>12.25109195709229</v>
@@ -1322,16 +1322,16 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>28.68072509765625</v>
+        <v>28.68072700500488</v>
       </c>
       <c r="B45" t="n">
-        <v>-4.764201641082764</v>
+        <v>-4.764203548431396</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.753300666809082</v>
+        <v>-1.753300547599792</v>
       </c>
       <c r="D45" t="n">
-        <v>-1.645218849182129</v>
+        <v>-1.645216941833496</v>
       </c>
       <c r="E45" t="n">
         <v>15.12150096893311</v>
@@ -1348,10 +1348,10 @@
         <v>-2.595841884613037</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5760158896446228</v>
+        <v>0.576015830039978</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3660573959350586</v>
+        <v>-0.3660592436790466</v>
       </c>
       <c r="E46" t="n">
         <v>19.6419792175293</v>
@@ -1365,13 +1365,13 @@
         <v>29.13036918640137</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.6823934316635132</v>
+        <v>-0.6823936104774475</v>
       </c>
       <c r="C47" t="n">
-        <v>-1.754701137542725</v>
+        <v>-1.754701256752014</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1451044231653214</v>
+        <v>-0.1451043486595154</v>
       </c>
       <c r="E47" t="n">
         <v>23.73296546936035</v>
@@ -1385,13 +1385,13 @@
         <v>27.92717742919922</v>
       </c>
       <c r="B48" t="n">
-        <v>0.9289079904556274</v>
+        <v>0.9289059042930603</v>
       </c>
       <c r="C48" t="n">
-        <v>-3.43358325958252</v>
+        <v>-3.433582782745361</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9709062576293945</v>
+        <v>0.9709063172340393</v>
       </c>
       <c r="E48" t="n">
         <v>28.96307373046875</v>
@@ -1405,7 +1405,7 @@
         <v>26.66284942626953</v>
       </c>
       <c r="B49" t="n">
-        <v>2.388295650482178</v>
+        <v>2.388296604156494</v>
       </c>
       <c r="C49" t="n">
         <v>-3.697185039520264</v>
@@ -1414,30 +1414,30 @@
         <v>2.996949195861816</v>
       </c>
       <c r="E49" t="n">
-        <v>35.18606185913086</v>
+        <v>35.18606567382812</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.792515754699707</v>
+        <v>-3.792515993118286</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>25.37053680419922</v>
+        <v>25.37053871154785</v>
       </c>
       <c r="B50" t="n">
-        <v>3.774511814117432</v>
+        <v>3.774512767791748</v>
       </c>
       <c r="C50" t="n">
         <v>-2.612247705459595</v>
       </c>
       <c r="D50" t="n">
-        <v>5.746723175048828</v>
+        <v>5.746724128723145</v>
       </c>
       <c r="E50" t="n">
         <v>41.77863693237305</v>
       </c>
       <c r="F50" t="n">
-        <v>-8.214187622070312</v>
+        <v>-8.214188575744629</v>
       </c>
     </row>
     <row r="51">
@@ -1448,7 +1448,7 @@
         <v>4.945450305938721</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.8296518921852112</v>
+        <v>-0.829651951789856</v>
       </c>
       <c r="D51" t="n">
         <v>8.90379524230957</v>
@@ -1468,13 +1468,13 @@
         <v>5.629170894622803</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9590094685554504</v>
+        <v>0.9590094089508057</v>
       </c>
       <c r="D52" t="n">
         <v>12.17672157287598</v>
       </c>
       <c r="E52" t="n">
-        <v>52.34543991088867</v>
+        <v>52.34543609619141</v>
       </c>
       <c r="F52" t="n">
         <v>-8.828831672668457</v>
@@ -1485,7 +1485,7 @@
         <v>20.62509536743164</v>
       </c>
       <c r="B53" t="n">
-        <v>5.734955310821533</v>
+        <v>5.73495626449585</v>
       </c>
       <c r="C53" t="n">
         <v>2.428501844406128</v>
@@ -1497,7 +1497,7 @@
         <v>54.76484298706055</v>
       </c>
       <c r="F53" t="n">
-        <v>-6.026090621948242</v>
+        <v>-6.0260910987854</v>
       </c>
     </row>
     <row r="54">
@@ -1517,7 +1517,7 @@
         <v>55.08745956420898</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.492030143737793</v>
+        <v>-2.492030382156372</v>
       </c>
     </row>
     <row r="55">
@@ -1537,7 +1537,7 @@
         <v>53.61552810668945</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9945365190505981</v>
+        <v>0.9945365786552429</v>
       </c>
     </row>
     <row r="56">
@@ -1557,7 +1557,7 @@
         <v>50.66776275634766</v>
       </c>
       <c r="F56" t="n">
-        <v>3.945390224456787</v>
+        <v>3.945389986038208</v>
       </c>
     </row>
     <row r="57">
@@ -1565,7 +1565,7 @@
         <v>12.11798667907715</v>
       </c>
       <c r="B57" t="n">
-        <v>2.836286067962646</v>
+        <v>2.83628511428833</v>
       </c>
       <c r="C57" t="n">
         <v>6.182946681976318</v>
@@ -1577,7 +1577,7 @@
         <v>46.47842025756836</v>
       </c>
       <c r="F57" t="n">
-        <v>6.130643367767334</v>
+        <v>6.130642890930176</v>
       </c>
     </row>
     <row r="58">
@@ -1585,33 +1585,33 @@
         <v>10.01347827911377</v>
       </c>
       <c r="B58" t="n">
-        <v>1.95212709903717</v>
+        <v>1.952127933502197</v>
       </c>
       <c r="C58" t="n">
-        <v>6.964167594909668</v>
+        <v>6.964168071746826</v>
       </c>
       <c r="D58" t="n">
-        <v>27.55125427246094</v>
+        <v>27.55125617980957</v>
       </c>
       <c r="E58" t="n">
         <v>41.25951385498047</v>
       </c>
       <c r="F58" t="n">
-        <v>7.542943000793457</v>
+        <v>7.542942523956299</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>7.990589618682861</v>
+        <v>7.990589141845703</v>
       </c>
       <c r="B59" t="n">
-        <v>1.112545609474182</v>
+        <v>1.112545490264893</v>
       </c>
       <c r="C59" t="n">
         <v>7.732068538665771</v>
       </c>
       <c r="D59" t="n">
-        <v>29.14215278625488</v>
+        <v>29.14215469360352</v>
       </c>
       <c r="E59" t="n">
         <v>35.14380264282227</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>6.04466438293457</v>
+        <v>6.044664859771729</v>
       </c>
       <c r="B60" t="n">
-        <v>0.3263117074966431</v>
+        <v>0.3263134658336639</v>
       </c>
       <c r="C60" t="n">
         <v>8.491707801818848</v>
@@ -1642,39 +1642,39 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4.175992965698242</v>
+        <v>4.175992488861084</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.3612912893295288</v>
+        <v>-0.3612914383411407</v>
       </c>
       <c r="C61" t="n">
-        <v>9.256364822387695</v>
+        <v>9.256365776062012</v>
       </c>
       <c r="D61" t="n">
-        <v>31.07729721069336</v>
+        <v>31.07729911804199</v>
       </c>
       <c r="E61" t="n">
         <v>21.00459289550781</v>
       </c>
       <c r="F61" t="n">
-        <v>7.246137619018555</v>
+        <v>7.246137142181396</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2.40432333946228</v>
+        <v>2.404323101043701</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.8600324392318726</v>
+        <v>-0.8600307106971741</v>
       </c>
       <c r="C62" t="n">
-        <v>10.03280830383301</v>
+        <v>10.03280925750732</v>
       </c>
       <c r="D62" t="n">
         <v>31.46946907043457</v>
       </c>
       <c r="E62" t="n">
-        <v>13.69804763793945</v>
+        <v>13.69804668426514</v>
       </c>
       <c r="F62" t="n">
         <v>6.251384258270264</v>
@@ -1682,30 +1682,30 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.7545859813690186</v>
+        <v>0.7545866370201111</v>
       </c>
       <c r="B63" t="n">
-        <v>-1.079459547996521</v>
+        <v>-1.079461574554443</v>
       </c>
       <c r="C63" t="n">
         <v>10.7972936630249</v>
       </c>
       <c r="D63" t="n">
-        <v>31.60136795043945</v>
+        <v>31.60136985778809</v>
       </c>
       <c r="E63" t="n">
-        <v>6.854531764984131</v>
+        <v>6.854532241821289</v>
       </c>
       <c r="F63" t="n">
-        <v>5.450605869293213</v>
+        <v>5.450605392456055</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-0.7457306385040283</v>
+        <v>-0.7457318902015686</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.9319089651107788</v>
+        <v>-0.9319091439247131</v>
       </c>
       <c r="C64" t="n">
         <v>11.49567031860352</v>
@@ -1714,47 +1714,47 @@
         <v>31.60845565795898</v>
       </c>
       <c r="E64" t="n">
-        <v>1.060098171234131</v>
+        <v>1.060096621513367</v>
       </c>
       <c r="F64" t="n">
-        <v>5.136620044708252</v>
+        <v>5.136619567871094</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-2.090733766555786</v>
+        <v>-2.090734958648682</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.3694432973861694</v>
+        <v>-0.3694434463977814</v>
       </c>
       <c r="C65" t="n">
-        <v>12.05819797515869</v>
+        <v>12.05819702148438</v>
       </c>
       <c r="D65" t="n">
-        <v>31.61435508728027</v>
+        <v>31.61435699462891</v>
       </c>
       <c r="E65" t="n">
-        <v>-3.233219623565674</v>
+        <v>-3.233217477798462</v>
       </c>
       <c r="F65" t="n">
-        <v>5.258790016174316</v>
+        <v>5.258789539337158</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-3.311526536941528</v>
+        <v>-3.311525821685791</v>
       </c>
       <c r="B66" t="n">
-        <v>0.5874487161636353</v>
+        <v>0.5874485373497009</v>
       </c>
       <c r="C66" t="n">
-        <v>12.41564464569092</v>
+        <v>12.41564559936523</v>
       </c>
       <c r="D66" t="n">
-        <v>31.67366981506348</v>
+        <v>31.67367172241211</v>
       </c>
       <c r="E66" t="n">
-        <v>-5.701130390167236</v>
+        <v>-5.701131820678711</v>
       </c>
       <c r="F66" t="n">
         <v>5.564603805541992</v>
@@ -1762,19 +1762,19 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-4.465447425842285</v>
+        <v>-4.46544885635376</v>
       </c>
       <c r="B67" t="n">
-        <v>1.867310166358948</v>
+        <v>1.867310047149658</v>
       </c>
       <c r="C67" t="n">
         <v>12.48532295227051</v>
       </c>
       <c r="D67" t="n">
-        <v>31.77260398864746</v>
+        <v>31.77260589599609</v>
       </c>
       <c r="E67" t="n">
-        <v>-6.210098743438721</v>
+        <v>-6.210098266601562</v>
       </c>
       <c r="F67" t="n">
         <v>5.666619777679443</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-5.599362373352051</v>
+        <v>-5.599361896514893</v>
       </c>
       <c r="B68" t="n">
-        <v>3.371726512908936</v>
+        <v>3.371727466583252</v>
       </c>
       <c r="C68" t="n">
         <v>12.17688655853271</v>
@@ -1794,7 +1794,7 @@
         <v>31.84543418884277</v>
       </c>
       <c r="E68" t="n">
-        <v>-4.995518207550049</v>
+        <v>-4.995517730712891</v>
       </c>
       <c r="F68" t="n">
         <v>5.067599773406982</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-6.687911033630371</v>
+        <v>-6.687912464141846</v>
       </c>
       <c r="B69" t="n">
         <v>5.096287250518799</v>
@@ -1811,10 +1811,10 @@
         <v>11.30015659332275</v>
       </c>
       <c r="D69" t="n">
-        <v>31.82487297058105</v>
+        <v>31.82487487792969</v>
       </c>
       <c r="E69" t="n">
-        <v>-2.512287616729736</v>
+        <v>-2.51228928565979</v>
       </c>
       <c r="F69" t="n">
         <v>3.378950834274292</v>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-7.606743812561035</v>
+        <v>-7.606743335723877</v>
       </c>
       <c r="B70" t="n">
         <v>7.166304111480713</v>
@@ -1831,13 +1831,13 @@
         <v>9.52202033996582</v>
       </c>
       <c r="D70" t="n">
-        <v>31.66789436340332</v>
+        <v>31.66789627075195</v>
       </c>
       <c r="E70" t="n">
-        <v>0.7786327004432678</v>
+        <v>0.7786329984664917</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8097211122512817</v>
+        <v>0.8097212314605713</v>
       </c>
     </row>
     <row r="71">
@@ -1854,7 +1854,7 @@
         <v>34.27399444580078</v>
       </c>
       <c r="E71" t="n">
-        <v>0.4575152993202209</v>
+        <v>0.4575155973434448</v>
       </c>
       <c r="F71" t="n">
         <v>1.409748196601868</v>
@@ -1862,19 +1862,19 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-8.007960319519043</v>
+        <v>-8.007962226867676</v>
       </c>
       <c r="B72" t="n">
         <v>13.46810722351074</v>
       </c>
       <c r="C72" t="n">
-        <v>1.531050801277161</v>
+        <v>1.531050682067871</v>
       </c>
       <c r="D72" t="n">
         <v>33.96356964111328</v>
       </c>
       <c r="E72" t="n">
-        <v>3.732045650482178</v>
+        <v>3.732045888900757</v>
       </c>
       <c r="F72" t="n">
         <v>-1.345711708068848</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-7.028367042541504</v>
+        <v>-7.028366565704346</v>
       </c>
       <c r="B73" t="n">
         <v>18.24349975585938</v>
@@ -1894,15 +1894,15 @@
         <v>33.5078125</v>
       </c>
       <c r="E73" t="n">
-        <v>7.016332149505615</v>
+        <v>7.01633358001709</v>
       </c>
       <c r="F73" t="n">
-        <v>-3.118787288665771</v>
+        <v>-3.118787527084351</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-5.141280174255371</v>
+        <v>-5.141279697418213</v>
       </c>
       <c r="B74" t="n">
         <v>24.08427619934082</v>
@@ -1917,32 +1917,32 @@
         <v>10.08639812469482</v>
       </c>
       <c r="F74" t="n">
-        <v>-3.212769031524658</v>
+        <v>-3.212769269943237</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-2.456477403640747</v>
+        <v>-2.45647668838501</v>
       </c>
       <c r="B75" t="n">
         <v>30.4969539642334</v>
       </c>
       <c r="C75" t="n">
-        <v>-15.45810031890869</v>
+        <v>-15.45810222625732</v>
       </c>
       <c r="D75" t="n">
-        <v>32.08594512939453</v>
+        <v>32.0859489440918</v>
       </c>
       <c r="E75" t="n">
         <v>12.66594886779785</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.800118207931519</v>
+        <v>-1.800117969512939</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.7708213329315186</v>
+        <v>0.7708210349082947</v>
       </c>
       <c r="B76" t="n">
         <v>36.64367294311523</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4.227009773254395</v>
+        <v>4.227010250091553</v>
       </c>
       <c r="B77" t="n">
         <v>41.55078887939453</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>7.626902103424072</v>
+        <v>7.626901626586914</v>
       </c>
       <c r="B78" t="n">
         <v>44.61349105834961</v>
@@ -2014,10 +2014,10 @@
         <v>26.05494689941406</v>
       </c>
       <c r="E79" t="n">
-        <v>15.49099159240723</v>
+        <v>15.49099063873291</v>
       </c>
       <c r="F79" t="n">
-        <v>5.696434020996094</v>
+        <v>5.696433544158936</v>
       </c>
     </row>
     <row r="80">
@@ -2028,16 +2028,16 @@
         <v>44.71590042114258</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.666900873184204</v>
+        <v>-1.666900992393494</v>
       </c>
       <c r="D80" t="n">
         <v>23.95768737792969</v>
       </c>
       <c r="E80" t="n">
-        <v>14.75194549560547</v>
+        <v>14.75194454193115</v>
       </c>
       <c r="F80" t="n">
-        <v>6.825351238250732</v>
+        <v>6.825350761413574</v>
       </c>
     </row>
     <row r="81">
@@ -2057,7 +2057,7 @@
         <v>13.68058681488037</v>
       </c>
       <c r="F81" t="n">
-        <v>7.697139263153076</v>
+        <v>7.69713830947876</v>
       </c>
     </row>
     <row r="82">
@@ -2068,13 +2068,13 @@
         <v>38.35565567016602</v>
       </c>
       <c r="C82" t="n">
-        <v>4.212202548980713</v>
+        <v>4.212202072143555</v>
       </c>
       <c r="D82" t="n">
         <v>19.42578506469727</v>
       </c>
       <c r="E82" t="n">
-        <v>12.39847564697266</v>
+        <v>12.39847469329834</v>
       </c>
       <c r="F82" t="n">
         <v>8.400934219360352</v>
@@ -2094,7 +2094,7 @@
         <v>17.1215763092041</v>
       </c>
       <c r="E83" t="n">
-        <v>11.04671382904053</v>
+        <v>11.04671287536621</v>
       </c>
       <c r="F83" t="n">
         <v>9.043695449829102</v>
@@ -2117,7 +2117,7 @@
         <v>9.737434387207031</v>
       </c>
       <c r="F84" t="n">
-        <v>9.694579124450684</v>
+        <v>9.694578170776367</v>
       </c>
     </row>
     <row r="85">
@@ -2145,7 +2145,7 @@
         <v>23.17848205566406</v>
       </c>
       <c r="B86" t="n">
-        <v>14.20132541656494</v>
+        <v>14.20132446289062</v>
       </c>
       <c r="C86" t="n">
         <v>5.743066787719727</v>
@@ -2154,7 +2154,7 @@
         <v>10.96358776092529</v>
       </c>
       <c r="E86" t="n">
-        <v>7.613511562347412</v>
+        <v>7.613511085510254</v>
       </c>
       <c r="F86" t="n">
         <v>11.1883544921875</v>
@@ -2165,39 +2165,39 @@
         <v>23.70354652404785</v>
       </c>
       <c r="B87" t="n">
-        <v>7.590354442596436</v>
+        <v>7.590355396270752</v>
       </c>
       <c r="C87" t="n">
         <v>4.921989917755127</v>
       </c>
       <c r="D87" t="n">
-        <v>9.372425079345703</v>
+        <v>9.37242603302002</v>
       </c>
       <c r="E87" t="n">
-        <v>6.997741222381592</v>
+        <v>6.997740745544434</v>
       </c>
       <c r="F87" t="n">
-        <v>12.13063907623291</v>
+        <v>12.13063812255859</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>24.09939193725586</v>
+        <v>24.09939384460449</v>
       </c>
       <c r="B88" t="n">
-        <v>1.376961350440979</v>
+        <v>1.376961231231689</v>
       </c>
       <c r="C88" t="n">
         <v>4.189527988433838</v>
       </c>
       <c r="D88" t="n">
-        <v>8.044873237609863</v>
+        <v>8.04487419128418</v>
       </c>
       <c r="E88" t="n">
-        <v>6.761260509490967</v>
+        <v>6.761260032653809</v>
       </c>
       <c r="F88" t="n">
-        <v>13.22689056396484</v>
+        <v>13.22688961029053</v>
       </c>
     </row>
     <row r="89">
@@ -2205,19 +2205,19 @@
         <v>24.48716354370117</v>
       </c>
       <c r="B89" t="n">
-        <v>-4.144858837127686</v>
+        <v>-4.144860744476318</v>
       </c>
       <c r="C89" t="n">
-        <v>3.816786050796509</v>
+        <v>3.816786289215088</v>
       </c>
       <c r="D89" t="n">
         <v>6.950642585754395</v>
       </c>
       <c r="E89" t="n">
-        <v>6.922660350799561</v>
+        <v>6.922660827636719</v>
       </c>
       <c r="F89" t="n">
-        <v>14.44065284729004</v>
+        <v>14.44065189361572</v>
       </c>
     </row>
     <row r="90">
@@ -2225,16 +2225,16 @@
         <v>24.97182655334473</v>
       </c>
       <c r="B90" t="n">
-        <v>-8.54133129119873</v>
+        <v>-8.541332244873047</v>
       </c>
       <c r="C90" t="n">
-        <v>3.695663690567017</v>
+        <v>3.695663452148438</v>
       </c>
       <c r="D90" t="n">
         <v>6.029208183288574</v>
       </c>
       <c r="E90" t="n">
-        <v>7.47267484664917</v>
+        <v>7.472675323486328</v>
       </c>
       <c r="F90" t="n">
         <v>15.6882209777832</v>
@@ -2242,16 +2242,16 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>25.58839797973633</v>
+        <v>25.58839988708496</v>
       </c>
       <c r="B91" t="n">
-        <v>-11.32310581207275</v>
+        <v>-11.32310676574707</v>
       </c>
       <c r="C91" t="n">
-        <v>3.506877183914185</v>
+        <v>3.506877422332764</v>
       </c>
       <c r="D91" t="n">
-        <v>5.18459415435791</v>
+        <v>5.184595108032227</v>
       </c>
       <c r="E91" t="n">
         <v>8.341655731201172</v>
@@ -2265,36 +2265,36 @@
         <v>26.26418876647949</v>
       </c>
       <c r="B92" t="n">
-        <v>-12.14970874786377</v>
+        <v>-12.14970970153809</v>
       </c>
       <c r="C92" t="n">
         <v>3.128812789916992</v>
       </c>
       <c r="D92" t="n">
-        <v>4.322245597839355</v>
+        <v>4.322244644165039</v>
       </c>
       <c r="E92" t="n">
-        <v>9.470156669616699</v>
+        <v>9.470157623291016</v>
       </c>
       <c r="F92" t="n">
-        <v>17.86553764343262</v>
+        <v>17.86553955078125</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>26.84214210510254</v>
+        <v>26.84214401245117</v>
       </c>
       <c r="B93" t="n">
-        <v>-11.31028461456299</v>
+        <v>-11.31028747558594</v>
       </c>
       <c r="C93" t="n">
         <v>2.702703237533569</v>
       </c>
       <c r="D93" t="n">
-        <v>3.356194496154785</v>
+        <v>3.356195449829102</v>
       </c>
       <c r="E93" t="n">
-        <v>10.81924152374268</v>
+        <v>10.81924057006836</v>
       </c>
       <c r="F93" t="n">
         <v>18.59156227111816</v>
@@ -2305,13 +2305,13 @@
         <v>27.18791198730469</v>
       </c>
       <c r="B94" t="n">
-        <v>-9.345295906066895</v>
+        <v>-9.345296859741211</v>
       </c>
       <c r="C94" t="n">
         <v>2.156238794326782</v>
       </c>
       <c r="D94" t="n">
-        <v>2.262472152709961</v>
+        <v>2.262473106384277</v>
       </c>
       <c r="E94" t="n">
         <v>12.38584804534912</v>
@@ -2325,7 +2325,7 @@
         <v>27.25304985046387</v>
       </c>
       <c r="B95" t="n">
-        <v>-6.806540966033936</v>
+        <v>-6.806542873382568</v>
       </c>
       <c r="C95" t="n">
         <v>0.9915872812271118</v>
@@ -2348,10 +2348,10 @@
         <v>-4.052876949310303</v>
       </c>
       <c r="C96" t="n">
-        <v>-1.081645488739014</v>
+        <v>-1.081645369529724</v>
       </c>
       <c r="D96" t="n">
-        <v>0.1440915912389755</v>
+        <v>0.1440916657447815</v>
       </c>
       <c r="E96" t="n">
         <v>16.55619621276855</v>
@@ -2362,22 +2362,22 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>32.7109489440918</v>
+        <v>32.71094512939453</v>
       </c>
       <c r="B97" t="n">
-        <v>5.448959827423096</v>
+        <v>5.448960781097412</v>
       </c>
       <c r="C97" t="n">
-        <v>-6.057275772094727</v>
+        <v>-6.057275295257568</v>
       </c>
       <c r="D97" t="n">
-        <v>-14.11501598358154</v>
+        <v>-14.11501789093018</v>
       </c>
       <c r="E97" t="n">
-        <v>12.89249801635742</v>
+        <v>12.89249706268311</v>
       </c>
       <c r="F97" t="n">
-        <v>5.304746627807617</v>
+        <v>5.304746150970459</v>
       </c>
     </row>
     <row r="98">
@@ -2385,7 +2385,7 @@
         <v>33.47395706176758</v>
       </c>
       <c r="B98" t="n">
-        <v>9.642599105834961</v>
+        <v>9.642598152160645</v>
       </c>
       <c r="C98" t="n">
         <v>-9.472084045410156</v>
@@ -2397,7 +2397,7 @@
         <v>17.87347030639648</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.463013172149658</v>
+        <v>-1.463012933731079</v>
       </c>
     </row>
     <row r="99">
@@ -2428,13 +2428,13 @@
         <v>18.1113224029541</v>
       </c>
       <c r="C100" t="n">
-        <v>-7.310549259185791</v>
+        <v>-7.310548305511475</v>
       </c>
       <c r="D100" t="n">
         <v>-6.529208183288574</v>
       </c>
       <c r="E100" t="n">
-        <v>29.64704322814941</v>
+        <v>29.64704132080078</v>
       </c>
       <c r="F100" t="n">
         <v>-14.00612926483154</v>
@@ -2454,7 +2454,7 @@
         <v>-2.674740791320801</v>
       </c>
       <c r="E101" t="n">
-        <v>36.3421745300293</v>
+        <v>36.34217834472656</v>
       </c>
       <c r="F101" t="n">
         <v>-14.67357158660889</v>
@@ -2468,7 +2468,7 @@
         <v>20.80165100097656</v>
       </c>
       <c r="C102" t="n">
-        <v>-1.427673578262329</v>
+        <v>-1.427673697471619</v>
       </c>
       <c r="D102" t="n">
         <v>1.544735908508301</v>
@@ -2477,12 +2477,12 @@
         <v>43.04413986206055</v>
       </c>
       <c r="F102" t="n">
-        <v>-12.00063800811768</v>
+        <v>-12.00063896179199</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>29.93349456787109</v>
+        <v>29.93349266052246</v>
       </c>
       <c r="B103" t="n">
         <v>19.66530990600586</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>27.33155822753906</v>
+        <v>27.33155632019043</v>
       </c>
       <c r="B104" t="n">
         <v>17.99419403076172</v>
@@ -2511,13 +2511,13 @@
         <v>1.68007755279541</v>
       </c>
       <c r="D104" t="n">
-        <v>10.14219856262207</v>
+        <v>10.14219951629639</v>
       </c>
       <c r="E104" t="n">
         <v>53.00614547729492</v>
       </c>
       <c r="F104" t="n">
-        <v>-4.409514904022217</v>
+        <v>-4.409515380859375</v>
       </c>
     </row>
     <row r="105">
@@ -2548,7 +2548,7 @@
         <v>14.00260829925537</v>
       </c>
       <c r="C106" t="n">
-        <v>3.857009410858154</v>
+        <v>3.857009649276733</v>
       </c>
       <c r="D106" t="n">
         <v>17.67443466186523</v>
@@ -2557,7 +2557,7 @@
         <v>55.03853988647461</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8124592304229736</v>
+        <v>0.8124593496322632</v>
       </c>
     </row>
     <row r="107">
@@ -2565,7 +2565,7 @@
         <v>18.18756294250488</v>
       </c>
       <c r="B107" t="n">
-        <v>11.0638370513916</v>
+        <v>11.06383609771729</v>
       </c>
       <c r="C107" t="n">
         <v>4.040149211883545</v>
@@ -2574,7 +2574,7 @@
         <v>20.77007102966309</v>
       </c>
       <c r="E107" t="n">
-        <v>53.06145095825195</v>
+        <v>53.06144714355469</v>
       </c>
       <c r="F107" t="n">
         <v>2.335421085357666</v>
@@ -2585,10 +2585,10 @@
         <v>14.93478775024414</v>
       </c>
       <c r="B108" t="n">
-        <v>7.746928691864014</v>
+        <v>7.74692964553833</v>
       </c>
       <c r="C108" t="n">
-        <v>3.790030717849731</v>
+        <v>3.790030956268311</v>
       </c>
       <c r="D108" t="n">
         <v>23.35972023010254</v>
@@ -2605,19 +2605,19 @@
         <v>11.83092212677002</v>
       </c>
       <c r="B109" t="n">
-        <v>4.829380512237549</v>
+        <v>4.829379558563232</v>
       </c>
       <c r="C109" t="n">
         <v>3.679421901702881</v>
       </c>
       <c r="D109" t="n">
-        <v>25.42351150512695</v>
+        <v>25.42351341247559</v>
       </c>
       <c r="E109" t="n">
-        <v>44.37055969238281</v>
+        <v>44.37055587768555</v>
       </c>
       <c r="F109" t="n">
-        <v>3.82109522819519</v>
+        <v>3.821094989776611</v>
       </c>
     </row>
     <row r="110">
@@ -2631,7 +2631,7 @@
         <v>4.032492160797119</v>
       </c>
       <c r="D110" t="n">
-        <v>26.95767402648926</v>
+        <v>26.95767593383789</v>
       </c>
       <c r="E110" t="n">
         <v>38.24296569824219</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>6.481892585754395</v>
+        <v>6.481892108917236</v>
       </c>
       <c r="B111" t="n">
-        <v>1.641085267066956</v>
+        <v>1.641087055206299</v>
       </c>
       <c r="C111" t="n">
         <v>4.870926380157471</v>
@@ -2662,16 +2662,16 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>4.177309036254883</v>
+        <v>4.177308559417725</v>
       </c>
       <c r="B112" t="n">
-        <v>1.156832337379456</v>
+        <v>1.156832218170166</v>
       </c>
       <c r="C112" t="n">
         <v>6.054930686950684</v>
       </c>
       <c r="D112" t="n">
-        <v>28.5993537902832</v>
+        <v>28.59935569763184</v>
       </c>
       <c r="E112" t="n">
         <v>24.11040687561035</v>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1.974237203598022</v>
+        <v>1.974236965179443</v>
       </c>
       <c r="B113" t="n">
-        <v>1.000515580177307</v>
+        <v>1.000515460968018</v>
       </c>
       <c r="C113" t="n">
         <v>7.37754487991333</v>
@@ -2697,55 +2697,55 @@
         <v>16.89493179321289</v>
       </c>
       <c r="F113" t="n">
-        <v>-1.267461776733398</v>
+        <v>-1.267461538314819</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-0.2144033759832382</v>
+        <v>-0.2144036591053009</v>
       </c>
       <c r="B114" t="n">
-        <v>0.9009290933609009</v>
+        <v>0.9009289145469666</v>
       </c>
       <c r="C114" t="n">
-        <v>8.644565582275391</v>
+        <v>8.644564628601074</v>
       </c>
       <c r="D114" t="n">
         <v>29.11742973327637</v>
       </c>
       <c r="E114" t="n">
-        <v>10.12013149261475</v>
+        <v>10.12013053894043</v>
       </c>
       <c r="F114" t="n">
-        <v>-2.764822483062744</v>
+        <v>-2.764822721481323</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-2.402331590652466</v>
+        <v>-2.402330875396729</v>
       </c>
       <c r="B115" t="n">
-        <v>0.7573534250259399</v>
+        <v>0.7573532462120056</v>
       </c>
       <c r="C115" t="n">
-        <v>9.740626335144043</v>
+        <v>9.740625381469727</v>
       </c>
       <c r="D115" t="n">
-        <v>29.3732967376709</v>
+        <v>29.37329864501953</v>
       </c>
       <c r="E115" t="n">
-        <v>4.297740459442139</v>
+        <v>4.297740936279297</v>
       </c>
       <c r="F115" t="n">
-        <v>-3.387939453125</v>
+        <v>-3.387938737869263</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-4.526888847351074</v>
+        <v>-4.526888370513916</v>
       </c>
       <c r="B116" t="n">
-        <v>0.6776186227798462</v>
+        <v>0.6776184439659119</v>
       </c>
       <c r="C116" t="n">
         <v>10.64062023162842</v>
@@ -2754,18 +2754,18 @@
         <v>29.78906440734863</v>
       </c>
       <c r="E116" t="n">
-        <v>0.07262569665908813</v>
+        <v>0.0726240873336792</v>
       </c>
       <c r="F116" t="n">
-        <v>-3.23035192489624</v>
+        <v>-3.230351686477661</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-6.476078987121582</v>
+        <v>-6.476080417633057</v>
       </c>
       <c r="B117" t="n">
-        <v>0.9419180154800415</v>
+        <v>0.9419178366661072</v>
       </c>
       <c r="C117" t="n">
         <v>11.40600776672363</v>
@@ -2774,18 +2774,18 @@
         <v>30.36520957946777</v>
       </c>
       <c r="E117" t="n">
-        <v>-2.015465259552002</v>
+        <v>-2.015466928482056</v>
       </c>
       <c r="F117" t="n">
-        <v>-2.646555423736572</v>
+        <v>-2.646555662155151</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-8.135214805603027</v>
+        <v>-8.13521671295166</v>
       </c>
       <c r="B118" t="n">
-        <v>1.881794571876526</v>
+        <v>1.881794452667236</v>
       </c>
       <c r="C118" t="n">
         <v>12.11329174041748</v>
@@ -2794,18 +2794,18 @@
         <v>31.01923751831055</v>
       </c>
       <c r="E118" t="n">
-        <v>-1.854647159576416</v>
+        <v>-1.854646801948547</v>
       </c>
       <c r="F118" t="n">
-        <v>-2.10475492477417</v>
+        <v>-2.104755163192749</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-9.456294059753418</v>
+        <v>-9.456295967102051</v>
       </c>
       <c r="B119" t="n">
-        <v>3.643178462982178</v>
+        <v>3.643179416656494</v>
       </c>
       <c r="C119" t="n">
         <v>12.71645355224609</v>
@@ -2814,10 +2814,10 @@
         <v>31.65631866455078</v>
       </c>
       <c r="E119" t="n">
-        <v>0.1830459237098694</v>
+        <v>0.1830462217330933</v>
       </c>
       <c r="F119" t="n">
-        <v>-2.170740604400635</v>
+        <v>-2.170740842819214</v>
       </c>
     </row>
     <row r="120">
@@ -2828,36 +2828,36 @@
         <v>6.231581211090088</v>
       </c>
       <c r="C120" t="n">
-        <v>13.00448036193848</v>
+        <v>13.00448131561279</v>
       </c>
       <c r="D120" t="n">
         <v>32.23357391357422</v>
       </c>
       <c r="E120" t="n">
-        <v>3.402154445648193</v>
+        <v>3.402154684066772</v>
       </c>
       <c r="F120" t="n">
-        <v>-3.377328872680664</v>
+        <v>-3.377328634262085</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-10.93468952178955</v>
+        <v>-10.93469142913818</v>
       </c>
       <c r="B121" t="n">
         <v>9.66666316986084</v>
       </c>
       <c r="C121" t="n">
-        <v>12.62370109558105</v>
+        <v>12.62370014190674</v>
       </c>
       <c r="D121" t="n">
-        <v>32.76180267333984</v>
+        <v>32.76180648803711</v>
       </c>
       <c r="E121" t="n">
-        <v>7.14194917678833</v>
+        <v>7.141948699951172</v>
       </c>
       <c r="F121" t="n">
-        <v>-5.669342994689941</v>
+        <v>-5.669342517852783</v>
       </c>
     </row>
     <row r="122">
@@ -2871,7 +2871,7 @@
         <v>10.98014354705811</v>
       </c>
       <c r="D122" t="n">
-        <v>35.59557723999023</v>
+        <v>35.5955810546875</v>
       </c>
       <c r="E122" t="n">
         <v>11.8169002532959</v>
@@ -2888,13 +2888,13 @@
         <v>19.03135108947754</v>
       </c>
       <c r="C123" t="n">
-        <v>7.145895957946777</v>
+        <v>7.145896434783936</v>
       </c>
       <c r="D123" t="n">
         <v>35.63029098510742</v>
       </c>
       <c r="E123" t="n">
-        <v>15.15485858917236</v>
+        <v>15.15485763549805</v>
       </c>
       <c r="F123" t="n">
         <v>-8.394699096679688</v>
@@ -2908,7 +2908,7 @@
         <v>24.39792442321777</v>
       </c>
       <c r="C124" t="n">
-        <v>0.3149249851703644</v>
+        <v>0.3149249255657196</v>
       </c>
       <c r="D124" t="n">
         <v>35.29672241210938</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-6.977997779846191</v>
+        <v>-6.977999210357666</v>
       </c>
       <c r="B125" t="n">
         <v>29.73955345153809</v>
@@ -2937,12 +2937,12 @@
         <v>20.8059139251709</v>
       </c>
       <c r="F125" t="n">
-        <v>-6.079531669616699</v>
+        <v>-6.079532146453857</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-4.505127906799316</v>
+        <v>-4.505127429962158</v>
       </c>
       <c r="B126" t="n">
         <v>35.09157943725586</v>
@@ -2951,18 +2951,18 @@
         <v>-15.93817806243896</v>
       </c>
       <c r="D126" t="n">
-        <v>33.10154342651367</v>
+        <v>33.10154724121094</v>
       </c>
       <c r="E126" t="n">
         <v>22.39847373962402</v>
       </c>
       <c r="F126" t="n">
-        <v>-3.516439437866211</v>
+        <v>-3.51643967628479</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-1.396153688430786</v>
+        <v>-1.396151065826416</v>
       </c>
       <c r="B127" t="n">
         <v>40.80989456176758</v>
@@ -2971,7 +2971,7 @@
         <v>-18.16719818115234</v>
       </c>
       <c r="D127" t="n">
-        <v>31.16701507568359</v>
+        <v>31.16701698303223</v>
       </c>
       <c r="E127" t="n">
         <v>22.90609550476074</v>
@@ -2982,36 +2982,36 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2.366365194320679</v>
+        <v>2.3663649559021</v>
       </c>
       <c r="B128" t="n">
         <v>46.96034240722656</v>
       </c>
       <c r="C128" t="n">
-        <v>-15.93325328826904</v>
+        <v>-15.93325138092041</v>
       </c>
       <c r="D128" t="n">
-        <v>28.74524116516113</v>
+        <v>28.74524307250977</v>
       </c>
       <c r="E128" t="n">
         <v>22.43967628479004</v>
       </c>
       <c r="F128" t="n">
-        <v>0.9277579784393311</v>
+        <v>0.9277579188346863</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>6.582390785217285</v>
+        <v>6.582391262054443</v>
       </c>
       <c r="B129" t="n">
-        <v>52.80185317993164</v>
+        <v>52.80184936523438</v>
       </c>
       <c r="C129" t="n">
         <v>-12.10377597808838</v>
       </c>
       <c r="D129" t="n">
-        <v>25.9461669921875</v>
+        <v>25.94616889953613</v>
       </c>
       <c r="E129" t="n">
         <v>21.11116790771484</v>
@@ -3045,10 +3045,10 @@
         <v>15.04599761962891</v>
       </c>
       <c r="B131" t="n">
-        <v>59.98260116577148</v>
+        <v>59.98259735107422</v>
       </c>
       <c r="C131" t="n">
-        <v>-4.670529365539551</v>
+        <v>-4.670528888702393</v>
       </c>
       <c r="D131" t="n">
         <v>19.71154022216797</v>
@@ -3057,7 +3057,7 @@
         <v>15.97082328796387</v>
       </c>
       <c r="F131" t="n">
-        <v>3.661338806152344</v>
+        <v>3.661338567733765</v>
       </c>
     </row>
     <row r="132">
@@ -3068,7 +3068,7 @@
         <v>60.46043395996094</v>
       </c>
       <c r="C132" t="n">
-        <v>-1.584898471832275</v>
+        <v>-1.584898591041565</v>
       </c>
       <c r="D132" t="n">
         <v>16.54908752441406</v>
@@ -3085,13 +3085,13 @@
         <v>21.90056228637695</v>
       </c>
       <c r="B133" t="n">
-        <v>58.78124237060547</v>
+        <v>58.7812385559082</v>
       </c>
       <c r="C133" t="n">
         <v>0.9838740229606628</v>
       </c>
       <c r="D133" t="n">
-        <v>13.53957939147949</v>
+        <v>13.53958034515381</v>
       </c>
       <c r="E133" t="n">
         <v>9.315546035766602</v>
@@ -3111,10 +3111,10 @@
         <v>2.933851480484009</v>
       </c>
       <c r="D134" t="n">
-        <v>10.76827621459961</v>
+        <v>10.76827716827393</v>
       </c>
       <c r="E134" t="n">
-        <v>6.670467853546143</v>
+        <v>6.670468330383301</v>
       </c>
       <c r="F134" t="n">
         <v>3.584855556488037</v>
@@ -3125,7 +3125,7 @@
         <v>26.39323425292969</v>
       </c>
       <c r="B135" t="n">
-        <v>49.6650505065918</v>
+        <v>49.66505432128906</v>
       </c>
       <c r="C135" t="n">
         <v>4.161262989044189</v>
@@ -3134,10 +3134,10 @@
         <v>8.238372802734375</v>
       </c>
       <c r="E135" t="n">
-        <v>4.813408374786377</v>
+        <v>4.813408851623535</v>
       </c>
       <c r="F135" t="n">
-        <v>4.1109619140625</v>
+        <v>4.110961437225342</v>
       </c>
     </row>
     <row r="136">
@@ -3148,13 +3148,13 @@
         <v>42.70198059082031</v>
       </c>
       <c r="C136" t="n">
-        <v>4.564177513122559</v>
+        <v>4.564177989959717</v>
       </c>
       <c r="D136" t="n">
-        <v>5.868978500366211</v>
+        <v>5.868977546691895</v>
       </c>
       <c r="E136" t="n">
-        <v>3.620648860931396</v>
+        <v>3.620649099349976</v>
       </c>
       <c r="F136" t="n">
         <v>4.976856231689453</v>
@@ -3171,13 +3171,13 @@
         <v>3.94160270690918</v>
       </c>
       <c r="D137" t="n">
-        <v>3.520482063293457</v>
+        <v>3.520481109619141</v>
       </c>
       <c r="E137" t="n">
-        <v>2.80244779586792</v>
+        <v>2.802448034286499</v>
       </c>
       <c r="F137" t="n">
-        <v>6.032258033752441</v>
+        <v>6.032257556915283</v>
       </c>
     </row>
     <row r="138">
@@ -3194,27 +3194,27 @@
         <v>1.052264213562012</v>
       </c>
       <c r="E138" t="n">
-        <v>2.056178569793701</v>
+        <v>2.05617880821228</v>
       </c>
       <c r="F138" t="n">
-        <v>7.116895198822021</v>
+        <v>7.116894721984863</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>28.04783248901367</v>
+        <v>28.0478343963623</v>
       </c>
       <c r="B139" t="n">
         <v>17.96771049499512</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.3512796461582184</v>
+        <v>-0.3512795865535736</v>
       </c>
       <c r="D139" t="n">
         <v>-1.60366153717041</v>
       </c>
       <c r="E139" t="n">
-        <v>1.198741436004639</v>
+        <v>1.198739886283875</v>
       </c>
       <c r="F139" t="n">
         <v>8.126598358154297</v>
@@ -3228,16 +3228,16 @@
         <v>10.77225208282471</v>
       </c>
       <c r="C140" t="n">
-        <v>-2.090726375579834</v>
+        <v>-2.090726137161255</v>
       </c>
       <c r="D140" t="n">
-        <v>-4.394654273986816</v>
+        <v>-4.394652366638184</v>
       </c>
       <c r="E140" t="n">
-        <v>0.2495437264442444</v>
+        <v>0.2495440244674683</v>
       </c>
       <c r="F140" t="n">
-        <v>9.045050621032715</v>
+        <v>9.045049667358398</v>
       </c>
     </row>
     <row r="141">
@@ -3245,16 +3245,16 @@
         <v>27.80424690246582</v>
       </c>
       <c r="B141" t="n">
-        <v>4.871069431304932</v>
+        <v>4.871070384979248</v>
       </c>
       <c r="C141" t="n">
-        <v>-2.13569974899292</v>
+        <v>-2.135699987411499</v>
       </c>
       <c r="D141" t="n">
         <v>-7.160786628723145</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.5786251425743103</v>
+        <v>-0.5786248445510864</v>
       </c>
       <c r="F141" t="n">
         <v>9.931349754333496</v>
@@ -3265,16 +3265,16 @@
         <v>28.07055282592773</v>
       </c>
       <c r="B142" t="n">
-        <v>0.7866884469985962</v>
+        <v>0.7866901755332947</v>
       </c>
       <c r="C142" t="n">
-        <v>-1.026734113693237</v>
+        <v>-1.026734232902527</v>
       </c>
       <c r="D142" t="n">
         <v>-9.702609062194824</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.9846557974815369</v>
+        <v>-0.9846574068069458</v>
       </c>
       <c r="F142" t="n">
         <v>10.85061550140381</v>
@@ -3285,36 +3285,36 @@
         <v>28.51385307312012</v>
       </c>
       <c r="B143" t="n">
-        <v>-1.003869414329529</v>
+        <v>-1.003869533538818</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.2127651423215866</v>
+        <v>-0.2127651870250702</v>
       </c>
       <c r="D143" t="n">
         <v>-11.85473346710205</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.7114605307579041</v>
+        <v>-0.7114602327346802</v>
       </c>
       <c r="F143" t="n">
-        <v>11.77196502685547</v>
+        <v>11.77196598052979</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>28.97129058837891</v>
+        <v>28.97129249572754</v>
       </c>
       <c r="B144" t="n">
-        <v>-0.5029195547103882</v>
+        <v>-0.5029197335243225</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.853667676448822</v>
+        <v>-0.8536676168441772</v>
       </c>
       <c r="D144" t="n">
         <v>-13.51886463165283</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3758159279823303</v>
+        <v>0.3758162260055542</v>
       </c>
       <c r="F144" t="n">
         <v>12.52795505523682</v>
@@ -3322,19 +3322,19 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>29.36255836486816</v>
+        <v>29.36255645751953</v>
       </c>
       <c r="B145" t="n">
-        <v>1.839624047279358</v>
+        <v>1.839622974395752</v>
       </c>
       <c r="C145" t="n">
-        <v>-3.068986654281616</v>
+        <v>-3.068986415863037</v>
       </c>
       <c r="D145" t="n">
-        <v>-14.64296627044678</v>
+        <v>-14.64296817779541</v>
       </c>
       <c r="E145" t="n">
-        <v>2.299872875213623</v>
+        <v>2.299873113632202</v>
       </c>
       <c r="F145" t="n">
         <v>12.81040573120117</v>
@@ -3348,13 +3348,13 @@
         <v>5.257265567779541</v>
       </c>
       <c r="C146" t="n">
-        <v>-5.918110370635986</v>
+        <v>-5.918110847473145</v>
       </c>
       <c r="D146" t="n">
         <v>-15.17396450042725</v>
       </c>
       <c r="E146" t="n">
-        <v>5.042630672454834</v>
+        <v>5.042629241943359</v>
       </c>
       <c r="F146" t="n">
         <v>12.13060283660889</v>
@@ -3365,16 +3365,16 @@
         <v>29.99117279052734</v>
       </c>
       <c r="B147" t="n">
-        <v>9.069263458251953</v>
+        <v>9.06926155090332</v>
       </c>
       <c r="C147" t="n">
         <v>-8.310957908630371</v>
       </c>
       <c r="D147" t="n">
-        <v>-15.0294828414917</v>
+        <v>-15.02948665618896</v>
       </c>
       <c r="E147" t="n">
-        <v>8.58693790435791</v>
+        <v>8.586936950683594</v>
       </c>
       <c r="F147" t="n">
         <v>9.833248138427734</v>
@@ -3385,13 +3385,13 @@
         <v>31.54406356811523</v>
       </c>
       <c r="B148" t="n">
-        <v>9.519939422607422</v>
+        <v>9.519938468933105</v>
       </c>
       <c r="C148" t="n">
         <v>-5.253461837768555</v>
       </c>
       <c r="D148" t="n">
-        <v>-16.38406753540039</v>
+        <v>-16.38406562805176</v>
       </c>
       <c r="E148" t="n">
         <v>15.58547306060791</v>
@@ -3402,22 +3402,22 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>31.88261032104492</v>
+        <v>31.88261222839355</v>
       </c>
       <c r="B149" t="n">
         <v>13.56563663482666</v>
       </c>
       <c r="C149" t="n">
-        <v>-6.814529895782471</v>
+        <v>-6.814529418945312</v>
       </c>
       <c r="D149" t="n">
-        <v>-14.68702411651611</v>
+        <v>-14.68702602386475</v>
       </c>
       <c r="E149" t="n">
         <v>20.53302955627441</v>
       </c>
       <c r="F149" t="n">
-        <v>-3.462053775787354</v>
+        <v>-3.462053537368774</v>
       </c>
     </row>
     <row r="150">
@@ -3451,7 +3451,7 @@
         <v>-3.894246101379395</v>
       </c>
       <c r="D151" t="n">
-        <v>-9.042162895202637</v>
+        <v>-9.04216480255127</v>
       </c>
       <c r="E151" t="n">
         <v>32.63379287719727</v>
@@ -3462,13 +3462,13 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>29.98164176940918</v>
+        <v>29.98164367675781</v>
       </c>
       <c r="B152" t="n">
         <v>21.23181533813477</v>
       </c>
       <c r="C152" t="n">
-        <v>-1.49606728553772</v>
+        <v>-1.496067404747009</v>
       </c>
       <c r="D152" t="n">
         <v>-5.264573097229004</v>
@@ -3488,7 +3488,7 @@
         <v>20.17507171630859</v>
       </c>
       <c r="C153" t="n">
-        <v>0.5703038573265076</v>
+        <v>0.5703037977218628</v>
       </c>
       <c r="D153" t="n">
         <v>-1.041567802429199</v>
@@ -3517,7 +3517,7 @@
         <v>51.44086456298828</v>
       </c>
       <c r="F154" t="n">
-        <v>-7.191113471984863</v>
+        <v>-7.19111442565918</v>
       </c>
     </row>
     <row r="155">
@@ -3534,10 +3534,10 @@
         <v>7.778188705444336</v>
       </c>
       <c r="E155" t="n">
-        <v>54.73610305786133</v>
+        <v>54.73609924316406</v>
       </c>
       <c r="F155" t="n">
-        <v>-3.261296272277832</v>
+        <v>-3.261296033859253</v>
       </c>
     </row>
     <row r="156">
@@ -3548,10 +3548,10 @@
         <v>16.87634658813477</v>
       </c>
       <c r="C156" t="n">
-        <v>5.218241214752197</v>
+        <v>5.218241691589355</v>
       </c>
       <c r="D156" t="n">
-        <v>11.83971309661865</v>
+        <v>11.83971405029297</v>
       </c>
       <c r="E156" t="n">
         <v>55.75179290771484</v>
@@ -3637,12 +3637,12 @@
         <v>40.71825408935547</v>
       </c>
       <c r="F160" t="n">
-        <v>2.807422876358032</v>
+        <v>2.807422637939453</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>6.739657402038574</v>
+        <v>6.7396559715271</v>
       </c>
       <c r="B161" t="n">
         <v>3.490407466888428</v>
@@ -3651,24 +3651,24 @@
         <v>5.840417861938477</v>
       </c>
       <c r="D161" t="n">
-        <v>23.23067665100098</v>
+        <v>23.23067855834961</v>
       </c>
       <c r="E161" t="n">
         <v>33.95138168334961</v>
       </c>
       <c r="F161" t="n">
-        <v>2.88063383102417</v>
+        <v>2.880633592605591</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>4.034048080444336</v>
+        <v>4.034048557281494</v>
       </c>
       <c r="B162" t="n">
-        <v>1.854011178016663</v>
+        <v>1.854010105133057</v>
       </c>
       <c r="C162" t="n">
-        <v>6.303715705871582</v>
+        <v>6.303715229034424</v>
       </c>
       <c r="D162" t="n">
         <v>23.57231140136719</v>
@@ -3677,15 +3677,15 @@
         <v>26.44856643676758</v>
       </c>
       <c r="F162" t="n">
-        <v>2.463344812393188</v>
+        <v>2.463344573974609</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1.425791501998901</v>
+        <v>1.425792217254639</v>
       </c>
       <c r="B163" t="n">
-        <v>0.7336050271987915</v>
+        <v>0.7336048483848572</v>
       </c>
       <c r="C163" t="n">
         <v>7.104920387268066</v>
@@ -3697,15 +3697,15 @@
         <v>18.4015941619873</v>
       </c>
       <c r="F163" t="n">
-        <v>1.477619886398315</v>
+        <v>1.477619767189026</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>-1.0372154712677</v>
+        <v>-1.037214756011963</v>
       </c>
       <c r="B164" t="n">
-        <v>0.1136938259005547</v>
+        <v>0.1136936694383621</v>
       </c>
       <c r="C164" t="n">
         <v>8.180473327636719</v>
@@ -3717,35 +3717,35 @@
         <v>10.24388885498047</v>
       </c>
       <c r="F164" t="n">
-        <v>0.1576206833124161</v>
+        <v>0.1576207727193832</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>-3.284035921096802</v>
+        <v>-3.284033298492432</v>
       </c>
       <c r="B165" t="n">
-        <v>0.001717199920676649</v>
+        <v>0.001717048115096986</v>
       </c>
       <c r="C165" t="n">
         <v>9.489165306091309</v>
       </c>
       <c r="D165" t="n">
-        <v>22.33822631835938</v>
+        <v>22.33822822570801</v>
       </c>
       <c r="E165" t="n">
-        <v>2.711741924285889</v>
+        <v>2.711742162704468</v>
       </c>
       <c r="F165" t="n">
-        <v>-1.176342010498047</v>
+        <v>-1.176342248916626</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>-5.25831127166748</v>
+        <v>-5.258308887481689</v>
       </c>
       <c r="B166" t="n">
-        <v>0.3669420480728149</v>
+        <v>0.366941899061203</v>
       </c>
       <c r="C166" t="n">
         <v>10.97675132751465</v>
@@ -3754,7 +3754,7 @@
         <v>22.03657150268555</v>
       </c>
       <c r="E166" t="n">
-        <v>-3.21966028213501</v>
+        <v>-3.219660043716431</v>
       </c>
       <c r="F166" t="n">
         <v>-2.145746231079102</v>
@@ -3762,30 +3762,30 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>-6.93187427520752</v>
+        <v>-6.931873798370361</v>
       </c>
       <c r="B167" t="n">
-        <v>1.16355574131012</v>
+        <v>1.16355562210083</v>
       </c>
       <c r="C167" t="n">
-        <v>12.52114772796631</v>
+        <v>12.52114677429199</v>
       </c>
       <c r="D167" t="n">
         <v>22.16421890258789</v>
       </c>
       <c r="E167" t="n">
-        <v>-6.596498966217041</v>
+        <v>-6.596500396728516</v>
       </c>
       <c r="F167" t="n">
-        <v>-2.283126354217529</v>
+        <v>-2.28312611579895</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>-8.331479072570801</v>
+        <v>-8.331480979919434</v>
       </c>
       <c r="B168" t="n">
-        <v>2.322122097015381</v>
+        <v>2.322123050689697</v>
       </c>
       <c r="C168" t="n">
         <v>13.89237785339355</v>
@@ -3794,35 +3794,35 @@
         <v>22.73730087280273</v>
       </c>
       <c r="E168" t="n">
-        <v>-6.938131809234619</v>
+        <v>-6.938131332397461</v>
       </c>
       <c r="F168" t="n">
-        <v>-1.426787614822388</v>
+        <v>-1.426787376403809</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>-9.535000801086426</v>
+        <v>-9.535002708435059</v>
       </c>
       <c r="B169" t="n">
-        <v>3.765028476715088</v>
+        <v>3.765029430389404</v>
       </c>
       <c r="C169" t="n">
-        <v>14.7605562210083</v>
+        <v>14.76055717468262</v>
       </c>
       <c r="D169" t="n">
         <v>23.60786247253418</v>
       </c>
       <c r="E169" t="n">
-        <v>-4.543470859527588</v>
+        <v>-4.543468475341797</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.1620659679174423</v>
+        <v>-0.1620659977197647</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>-10.57363605499268</v>
+        <v>-10.57363796234131</v>
       </c>
       <c r="B170" t="n">
         <v>5.563311100006104</v>
@@ -3834,7 +3834,7 @@
         <v>24.52619743347168</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.4279865622520447</v>
+        <v>-0.4279881715774536</v>
       </c>
       <c r="F170" t="n">
         <v>0.3658528327941895</v>
@@ -3842,19 +3842,19 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>-11.30011081695557</v>
+        <v>-11.3001127243042</v>
       </c>
       <c r="B171" t="n">
         <v>8.095279693603516</v>
       </c>
       <c r="C171" t="n">
-        <v>14.3198299407959</v>
+        <v>14.31983089447021</v>
       </c>
       <c r="D171" t="n">
-        <v>25.2607421875</v>
+        <v>25.26074409484863</v>
       </c>
       <c r="E171" t="n">
-        <v>4.073113918304443</v>
+        <v>4.073112487792969</v>
       </c>
       <c r="F171" t="n">
         <v>-0.8365252017974854</v>
@@ -3868,16 +3868,16 @@
         <v>11.79491806030273</v>
       </c>
       <c r="C172" t="n">
-        <v>12.81716346740723</v>
+        <v>12.81716442108154</v>
       </c>
       <c r="D172" t="n">
-        <v>25.69960975646973</v>
+        <v>25.69961166381836</v>
       </c>
       <c r="E172" t="n">
         <v>8.02421760559082</v>
       </c>
       <c r="F172" t="n">
-        <v>-3.660946369171143</v>
+        <v>-3.660946130752563</v>
       </c>
     </row>
     <row r="173">
@@ -3902,7 +3902,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>-9.259343147277832</v>
+        <v>-9.259345054626465</v>
       </c>
       <c r="B174" t="n">
         <v>22.20937538146973</v>
@@ -3914,7 +3914,7 @@
         <v>32.64299774169922</v>
       </c>
       <c r="E174" t="n">
-        <v>11.38341236114502</v>
+        <v>11.3834114074707</v>
       </c>
       <c r="F174" t="n">
         <v>-8.159849166870117</v>
@@ -3922,7 +3922,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>-7.096270561218262</v>
+        <v>-7.096271991729736</v>
       </c>
       <c r="B175" t="n">
         <v>27.70474433898926</v>
@@ -3931,10 +3931,10 @@
         <v>-6.226450443267822</v>
       </c>
       <c r="D175" t="n">
-        <v>32.31375122070312</v>
+        <v>32.31375503540039</v>
       </c>
       <c r="E175" t="n">
-        <v>14.44857692718506</v>
+        <v>14.44857597351074</v>
       </c>
       <c r="F175" t="n">
         <v>-8.25111198425293</v>
@@ -3942,7 +3942,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>-4.484148979187012</v>
+        <v>-4.484146595001221</v>
       </c>
       <c r="B176" t="n">
         <v>32.8923454284668</v>
@@ -3957,12 +3957,12 @@
         <v>17.25416564941406</v>
       </c>
       <c r="F176" t="n">
-        <v>-6.346748352050781</v>
+        <v>-6.346749305725098</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>-1.416091203689575</v>
+        <v>-1.416090488433838</v>
       </c>
       <c r="B177" t="n">
         <v>38.13530731201172</v>
@@ -3977,15 +3977,15 @@
         <v>18.87170600891113</v>
       </c>
       <c r="F177" t="n">
-        <v>-3.829887866973877</v>
+        <v>-3.829888105392456</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2.237298727035522</v>
+        <v>2.237298488616943</v>
       </c>
       <c r="B178" t="n">
-        <v>43.9439811706543</v>
+        <v>43.94398498535156</v>
       </c>
       <c r="C178" t="n">
         <v>-19.91087913513184</v>
@@ -4002,7 +4002,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>6.468018531799316</v>
+        <v>6.468019008636475</v>
       </c>
       <c r="B179" t="n">
         <v>49.97467803955078</v>
@@ -4017,7 +4017,7 @@
         <v>17.6115550994873</v>
       </c>
       <c r="F179" t="n">
-        <v>0.1107643991708755</v>
+        <v>0.1107644960284233</v>
       </c>
     </row>
     <row r="180">
@@ -4037,7 +4037,7 @@
         <v>15.40421485900879</v>
       </c>
       <c r="F180" t="n">
-        <v>1.268120527267456</v>
+        <v>1.268120408058167</v>
       </c>
     </row>
     <row r="181">
@@ -4045,10 +4045,10 @@
         <v>15.29684925079346</v>
       </c>
       <c r="B181" t="n">
-        <v>58.52754592895508</v>
+        <v>58.52754211425781</v>
       </c>
       <c r="C181" t="n">
-        <v>-5.65667200088501</v>
+        <v>-5.656672477722168</v>
       </c>
       <c r="D181" t="n">
         <v>19.13573265075684</v>
@@ -4065,16 +4065,16 @@
         <v>19.12456130981445</v>
       </c>
       <c r="B182" t="n">
-        <v>59.81311798095703</v>
+        <v>59.81311416625977</v>
       </c>
       <c r="C182" t="n">
-        <v>-1.806278944015503</v>
+        <v>-1.806279063224792</v>
       </c>
       <c r="D182" t="n">
         <v>15.68352031707764</v>
       </c>
       <c r="E182" t="n">
-        <v>9.14877986907959</v>
+        <v>9.148778915405273</v>
       </c>
       <c r="F182" t="n">
         <v>1.710887551307678</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>22.31101417541504</v>
+        <v>22.31101608276367</v>
       </c>
       <c r="B183" t="n">
         <v>58.86860275268555</v>
@@ -4094,7 +4094,7 @@
         <v>12.30996417999268</v>
       </c>
       <c r="E183" t="n">
-        <v>5.72249174118042</v>
+        <v>5.722491264343262</v>
       </c>
       <c r="F183" t="n">
         <v>1.365616798400879</v>
@@ -4105,16 +4105,16 @@
         <v>24.83685302734375</v>
       </c>
       <c r="B184" t="n">
-        <v>55.77118682861328</v>
+        <v>55.77118301391602</v>
       </c>
       <c r="C184" t="n">
         <v>3.534459352493286</v>
       </c>
       <c r="D184" t="n">
-        <v>9.164272308349609</v>
+        <v>9.164273262023926</v>
       </c>
       <c r="E184" t="n">
-        <v>2.783320903778076</v>
+        <v>2.783321142196655</v>
       </c>
       <c r="F184" t="n">
         <v>1.266554474830627</v>
@@ -4125,16 +4125,16 @@
         <v>26.69604873657227</v>
       </c>
       <c r="B185" t="n">
-        <v>50.71401214599609</v>
+        <v>50.71400833129883</v>
       </c>
       <c r="C185" t="n">
         <v>4.55280876159668</v>
       </c>
       <c r="D185" t="n">
-        <v>6.332698822021484</v>
+        <v>6.332697868347168</v>
       </c>
       <c r="E185" t="n">
-        <v>0.7093310952186584</v>
+        <v>0.7093313932418823</v>
       </c>
       <c r="F185" t="n">
         <v>1.73780083656311</v>
@@ -4154,10 +4154,10 @@
         <v>3.81613826751709</v>
       </c>
       <c r="E186" t="n">
-        <v>-0.4160389304161072</v>
+        <v>-0.4160405397415161</v>
       </c>
       <c r="F186" t="n">
-        <v>2.777571439743042</v>
+        <v>2.777571201324463</v>
       </c>
     </row>
     <row r="187">
@@ -4174,10 +4174,10 @@
         <v>1.530478477478027</v>
       </c>
       <c r="E187" t="n">
-        <v>-0.7764496207237244</v>
+        <v>-0.7764493227005005</v>
       </c>
       <c r="F187" t="n">
-        <v>4.180874824523926</v>
+        <v>4.180874347686768</v>
       </c>
     </row>
     <row r="188">
@@ -4191,10 +4191,10 @@
         <v>2.734725952148438</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.6530733108520508</v>
+        <v>-0.653073251247406</v>
       </c>
       <c r="E188" t="n">
-        <v>-0.6808952689170837</v>
+        <v>-0.6808949708938599</v>
       </c>
       <c r="F188" t="n">
         <v>5.72688102722168</v>
@@ -4208,16 +4208,16 @@
         <v>17.97307205200195</v>
       </c>
       <c r="C189" t="n">
-        <v>0.359995573759079</v>
+        <v>0.3599956333637238</v>
       </c>
       <c r="D189" t="n">
-        <v>-2.848418235778809</v>
+        <v>-2.848420143127441</v>
       </c>
       <c r="E189" t="n">
-        <v>-0.4013561606407166</v>
+        <v>-0.4013558626174927</v>
       </c>
       <c r="F189" t="n">
-        <v>7.267461776733398</v>
+        <v>7.26746129989624</v>
       </c>
     </row>
     <row r="190">
@@ -4225,16 +4225,16 @@
         <v>27.27387237548828</v>
       </c>
       <c r="B190" t="n">
-        <v>10.13713264465332</v>
+        <v>10.137131690979</v>
       </c>
       <c r="C190" t="n">
         <v>-2.001528024673462</v>
       </c>
       <c r="D190" t="n">
-        <v>-5.111010551452637</v>
+        <v>-5.111008644104004</v>
       </c>
       <c r="E190" t="n">
-        <v>-0.09692806005477905</v>
+        <v>-0.09692776203155518</v>
       </c>
       <c r="F190" t="n">
         <v>8.719694137573242</v>
@@ -4254,7 +4254,7 @@
         <v>-7.423369407653809</v>
       </c>
       <c r="E191" t="n">
-        <v>0.1920333504676819</v>
+        <v>0.1920355558395386</v>
       </c>
       <c r="F191" t="n">
         <v>10.03079605102539</v>
@@ -4265,16 +4265,16 @@
         <v>27.34112739562988</v>
       </c>
       <c r="B192" t="n">
-        <v>-0.3549016714096069</v>
+        <v>-0.3549018204212189</v>
       </c>
       <c r="C192" t="n">
-        <v>-2.798229932785034</v>
+        <v>-2.798229694366455</v>
       </c>
       <c r="D192" t="n">
         <v>-9.715960502624512</v>
       </c>
       <c r="E192" t="n">
-        <v>0.504094660282135</v>
+        <v>0.5040949583053589</v>
       </c>
       <c r="F192" t="n">
         <v>11.13447856903076</v>
@@ -4285,16 +4285,16 @@
         <v>27.94517707824707</v>
       </c>
       <c r="B193" t="n">
-        <v>-2.091500759124756</v>
+        <v>-2.091498851776123</v>
       </c>
       <c r="C193" t="n">
-        <v>-1.59312105178833</v>
+        <v>-1.59312117099762</v>
       </c>
       <c r="D193" t="n">
         <v>-11.89795780181885</v>
       </c>
       <c r="E193" t="n">
-        <v>0.9314437508583069</v>
+        <v>0.9314440488815308</v>
       </c>
       <c r="F193" t="n">
         <v>11.957594871521</v>
@@ -4305,16 +4305,16 @@
         <v>28.60050201416016</v>
       </c>
       <c r="B194" t="n">
-        <v>-1.584760069847107</v>
+        <v>-1.584760189056396</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.2559510767459869</v>
+        <v>-0.2559510171413422</v>
       </c>
       <c r="D194" t="n">
         <v>-13.87221050262451</v>
       </c>
       <c r="E194" t="n">
-        <v>1.631898403167725</v>
+        <v>1.631898760795593</v>
       </c>
       <c r="F194" t="n">
         <v>12.46585655212402</v>
@@ -4325,7 +4325,7 @@
         <v>29.13460350036621</v>
       </c>
       <c r="B195" t="n">
-        <v>0.5982805490493774</v>
+        <v>0.5982822775840759</v>
       </c>
       <c r="C195" t="n">
         <v>0.6736176013946533</v>
@@ -4334,10 +4334,10 @@
         <v>-15.52835750579834</v>
       </c>
       <c r="E195" t="n">
-        <v>2.841630458831787</v>
+        <v>2.841628789901733</v>
       </c>
       <c r="F195" t="n">
-        <v>12.65200710296631</v>
+        <v>12.65200805664062</v>
       </c>
     </row>
     <row r="196">
@@ -4348,13 +4348,13 @@
         <v>3.644351482391357</v>
       </c>
       <c r="C196" t="n">
-        <v>0.4265215992927551</v>
+        <v>0.4265215694904327</v>
       </c>
       <c r="D196" t="n">
-        <v>-16.73695373535156</v>
+        <v>-16.73695182800293</v>
       </c>
       <c r="E196" t="n">
-        <v>4.801170825958252</v>
+        <v>4.801170349121094</v>
       </c>
       <c r="F196" t="n">
         <v>12.40149021148682</v>
@@ -4368,13 +4368,13 @@
         <v>6.670427799224854</v>
       </c>
       <c r="C197" t="n">
-        <v>-1.718868255615234</v>
+        <v>-1.718868374824524</v>
       </c>
       <c r="D197" t="n">
-        <v>-17.35958480834961</v>
+        <v>-17.35958290100098</v>
       </c>
       <c r="E197" t="n">
-        <v>7.625985622406006</v>
+        <v>7.625986099243164</v>
       </c>
       <c r="F197" t="n">
         <v>11.31737518310547</v>
@@ -4385,13 +4385,13 @@
         <v>29.68305587768555</v>
       </c>
       <c r="B198" t="n">
-        <v>9.641531944274902</v>
+        <v>9.641530990600586</v>
       </c>
       <c r="C198" t="n">
-        <v>-4.753839492797852</v>
+        <v>-4.753839015960693</v>
       </c>
       <c r="D198" t="n">
-        <v>-17.27353286743164</v>
+        <v>-17.27353096008301</v>
       </c>
       <c r="E198" t="n">
         <v>11.26139068603516</v>
@@ -4405,16 +4405,16 @@
         <v>32.72341537475586</v>
       </c>
       <c r="B199" t="n">
-        <v>8.115840911865234</v>
+        <v>8.115839004516602</v>
       </c>
       <c r="C199" t="n">
         <v>-4.783977031707764</v>
       </c>
       <c r="D199" t="n">
-        <v>-16.03171157836914</v>
+        <v>-16.03171348571777</v>
       </c>
       <c r="E199" t="n">
-        <v>12.90883827209473</v>
+        <v>12.90883731842041</v>
       </c>
       <c r="F199" t="n">
         <v>2.589628219604492</v>
@@ -4431,13 +4431,13 @@
         <v>-6.459099769592285</v>
       </c>
       <c r="D200" t="n">
-        <v>-14.21571254730225</v>
+        <v>-14.21571063995361</v>
       </c>
       <c r="E200" t="n">
         <v>18.38468551635742</v>
       </c>
       <c r="F200" t="n">
-        <v>-4.079713344573975</v>
+        <v>-4.079713821411133</v>
       </c>
     </row>
     <row r="201">
@@ -4462,7 +4462,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>33.33849334716797</v>
+        <v>33.3384895324707</v>
       </c>
       <c r="B202" t="n">
         <v>19.5012092590332</v>
@@ -4477,18 +4477,18 @@
         <v>30.4012508392334</v>
       </c>
       <c r="F202" t="n">
-        <v>-17.53884696960449</v>
+        <v>-17.53884506225586</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>31.99574089050293</v>
+        <v>31.99574279785156</v>
       </c>
       <c r="B203" t="n">
         <v>20.23374176025391</v>
       </c>
       <c r="C203" t="n">
-        <v>-2.289539813995361</v>
+        <v>-2.28954005241394</v>
       </c>
       <c r="D203" t="n">
         <v>-4.755084037780762</v>
@@ -4508,10 +4508,10 @@
         <v>19.42002105712891</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.1829331368207932</v>
+        <v>-0.1829331815242767</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.5478315353393555</v>
+        <v>-0.5478314757347107</v>
       </c>
       <c r="E204" t="n">
         <v>42.85980987548828</v>
@@ -4522,7 +4522,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>27.44333267211914</v>
+        <v>27.44333457946777</v>
       </c>
       <c r="B205" t="n">
         <v>17.82676696777344</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>24.69412803649902</v>
+        <v>24.69412994384766</v>
       </c>
       <c r="B206" t="n">
         <v>15.8731164932251</v>
@@ -4551,10 +4551,10 @@
         <v>2.432731151580811</v>
       </c>
       <c r="D206" t="n">
-        <v>8.617196083068848</v>
+        <v>8.617197036743164</v>
       </c>
       <c r="E206" t="n">
-        <v>52.35831832885742</v>
+        <v>52.35831451416016</v>
       </c>
       <c r="F206" t="n">
         <v>-8.143244743347168</v>
@@ -4565,7 +4565,7 @@
         <v>21.76468849182129</v>
       </c>
       <c r="B207" t="n">
-        <v>13.42293453216553</v>
+        <v>13.42293357849121</v>
       </c>
       <c r="C207" t="n">
         <v>2.914615869522095</v>
@@ -4574,10 +4574,10 @@
         <v>13.1414623260498</v>
       </c>
       <c r="E207" t="n">
-        <v>54.70961761474609</v>
+        <v>54.70961380004883</v>
       </c>
       <c r="F207" t="n">
-        <v>-4.752289772033691</v>
+        <v>-4.75229024887085</v>
       </c>
     </row>
     <row r="208">
@@ -4585,7 +4585,7 @@
         <v>18.69356155395508</v>
       </c>
       <c r="B208" t="n">
-        <v>10.34388446807861</v>
+        <v>10.3438835144043</v>
       </c>
       <c r="C208" t="n">
         <v>2.92203688621521</v>
@@ -4597,7 +4597,7 @@
         <v>55.22616195678711</v>
       </c>
       <c r="F208" t="n">
-        <v>-2.055549621582031</v>
+        <v>-2.055549383163452</v>
       </c>
     </row>
     <row r="209">
@@ -4605,7 +4605,7 @@
         <v>15.61940097808838</v>
       </c>
       <c r="B209" t="n">
-        <v>7.067325115203857</v>
+        <v>7.067324161529541</v>
       </c>
       <c r="C209" t="n">
         <v>2.754967212677002</v>
@@ -4614,10 +4614,10 @@
         <v>21.07096099853516</v>
       </c>
       <c r="E209" t="n">
-        <v>53.9926643371582</v>
+        <v>53.99266052246094</v>
       </c>
       <c r="F209" t="n">
-        <v>0.2048963457345963</v>
+        <v>0.2048963159322739</v>
       </c>
     </row>
     <row r="210">
@@ -4648,7 +4648,7 @@
         <v>2.210823535919189</v>
       </c>
       <c r="C211" t="n">
-        <v>3.171652317047119</v>
+        <v>3.17165207862854</v>
       </c>
       <c r="D211" t="n">
         <v>26.76634407043457</v>
@@ -4657,24 +4657,24 @@
         <v>46.96974182128906</v>
       </c>
       <c r="F211" t="n">
-        <v>3.746608257293701</v>
+        <v>3.746608018875122</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>7.427088260650635</v>
+        <v>7.427087306976318</v>
       </c>
       <c r="B212" t="n">
-        <v>0.8014646768569946</v>
+        <v>0.8014644980430603</v>
       </c>
       <c r="C212" t="n">
-        <v>3.840819120407104</v>
+        <v>3.840819358825684</v>
       </c>
       <c r="D212" t="n">
-        <v>28.62588310241699</v>
+        <v>28.62588500976562</v>
       </c>
       <c r="E212" t="n">
-        <v>41.46113586425781</v>
+        <v>41.46113204956055</v>
       </c>
       <c r="F212" t="n">
         <v>4.496410846710205</v>
@@ -4682,10 +4682,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>4.894728660583496</v>
+        <v>4.894728183746338</v>
       </c>
       <c r="B213" t="n">
-        <v>-0.2763780355453491</v>
+        <v>-0.2763762772083282</v>
       </c>
       <c r="C213" t="n">
         <v>4.592483997344971</v>
@@ -4697,21 +4697,21 @@
         <v>34.75399780273438</v>
       </c>
       <c r="F213" t="n">
-        <v>4.10507345199585</v>
+        <v>4.105072975158691</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>2.356503248214722</v>
+        <v>2.356503009796143</v>
       </c>
       <c r="B214" t="n">
-        <v>-1.20487916469574</v>
+        <v>-1.204879283905029</v>
       </c>
       <c r="C214" t="n">
         <v>5.3277268409729</v>
       </c>
       <c r="D214" t="n">
-        <v>30.36335754394531</v>
+        <v>30.36335945129395</v>
       </c>
       <c r="E214" t="n">
         <v>27.0286808013916</v>
@@ -4722,13 +4722,13 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>-0.1404249519109726</v>
+        <v>-0.1404252350330353</v>
       </c>
       <c r="B215" t="n">
-        <v>-1.95022714138031</v>
+        <v>-1.9502272605896</v>
       </c>
       <c r="C215" t="n">
-        <v>6.122318744659424</v>
+        <v>6.122319221496582</v>
       </c>
       <c r="D215" t="n">
         <v>30.44340896606445</v>
@@ -4737,75 +4737,75 @@
         <v>18.66259574890137</v>
       </c>
       <c r="F215" t="n">
-        <v>0.2759703397750854</v>
+        <v>0.275970458984375</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>-2.472937822341919</v>
+        <v>-2.472937107086182</v>
       </c>
       <c r="B216" t="n">
-        <v>-2.305814266204834</v>
+        <v>-2.305810451507568</v>
       </c>
       <c r="C216" t="n">
-        <v>7.148919582366943</v>
+        <v>7.148920059204102</v>
       </c>
       <c r="D216" t="n">
         <v>30.28093338012695</v>
       </c>
       <c r="E216" t="n">
-        <v>10.31049346923828</v>
+        <v>10.31049251556396</v>
       </c>
       <c r="F216" t="n">
-        <v>-1.903061628341675</v>
+        <v>-1.903061389923096</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>-4.500632286071777</v>
+        <v>-4.500633716583252</v>
       </c>
       <c r="B217" t="n">
-        <v>-2.01308012008667</v>
+        <v>-2.013082027435303</v>
       </c>
       <c r="C217" t="n">
-        <v>8.541281700134277</v>
+        <v>8.541282653808594</v>
       </c>
       <c r="D217" t="n">
         <v>30.15394401550293</v>
       </c>
       <c r="E217" t="n">
-        <v>2.915610790252686</v>
+        <v>2.915609121322632</v>
       </c>
       <c r="F217" t="n">
-        <v>-3.395564556121826</v>
+        <v>-3.395564794540405</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>-6.168215751647949</v>
+        <v>-6.168215274810791</v>
       </c>
       <c r="B218" t="n">
-        <v>-0.9690755605697632</v>
+        <v>-0.9690757393836975</v>
       </c>
       <c r="C218" t="n">
         <v>10.24686908721924</v>
       </c>
       <c r="D218" t="n">
-        <v>30.29035186767578</v>
+        <v>30.29035377502441</v>
       </c>
       <c r="E218" t="n">
-        <v>-2.425781726837158</v>
+        <v>-2.425783395767212</v>
       </c>
       <c r="F218" t="n">
-        <v>-3.991297245025635</v>
+        <v>-3.991297006607056</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>-7.530976295471191</v>
+        <v>-7.530977725982666</v>
       </c>
       <c r="B219" t="n">
-        <v>0.7058588266372681</v>
+        <v>0.7058605551719666</v>
       </c>
       <c r="C219" t="n">
         <v>11.99321937561035</v>
@@ -4814,10 +4814,10 @@
         <v>30.77606201171875</v>
       </c>
       <c r="E219" t="n">
-        <v>-4.842243671417236</v>
+        <v>-4.842243194580078</v>
       </c>
       <c r="F219" t="n">
-        <v>-3.744932174682617</v>
+        <v>-3.744931936264038</v>
       </c>
     </row>
     <row r="220">
@@ -4825,7 +4825,7 @@
         <v>-8.682629585266113</v>
       </c>
       <c r="B220" t="n">
-        <v>2.814560413360596</v>
+        <v>2.814561367034912</v>
       </c>
       <c r="C220" t="n">
         <v>13.38725090026855</v>
@@ -4834,18 +4834,18 @@
         <v>31.53286170959473</v>
       </c>
       <c r="E220" t="n">
-        <v>-4.160192966461182</v>
+        <v>-4.160192489624023</v>
       </c>
       <c r="F220" t="n">
-        <v>-3.045681953430176</v>
+        <v>-3.045682191848755</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>-9.620762825012207</v>
+        <v>-9.62076473236084</v>
       </c>
       <c r="B221" t="n">
-        <v>5.362066745758057</v>
+        <v>5.362067699432373</v>
       </c>
       <c r="C221" t="n">
         <v>14.10321140289307</v>
@@ -4854,10 +4854,10 @@
         <v>32.38537979125977</v>
       </c>
       <c r="E221" t="n">
-        <v>-1.087681293487549</v>
+        <v>-1.08768093585968</v>
       </c>
       <c r="F221" t="n">
-        <v>-2.715541839599609</v>
+        <v>-2.71554160118103</v>
       </c>
     </row>
     <row r="222">
@@ -4865,7 +4865,7 @@
         <v>-10.18505001068115</v>
       </c>
       <c r="B222" t="n">
-        <v>8.628351211547852</v>
+        <v>8.628350257873535</v>
       </c>
       <c r="C222" t="n">
         <v>13.9066333770752</v>
@@ -4874,10 +4874,10 @@
         <v>33.16251373291016</v>
       </c>
       <c r="E222" t="n">
-        <v>3.114234447479248</v>
+        <v>3.114234685897827</v>
       </c>
       <c r="F222" t="n">
-        <v>-3.691694736480713</v>
+        <v>-3.691694974899292</v>
       </c>
     </row>
     <row r="223">
@@ -4891,10 +4891,10 @@
         <v>12.39472103118896</v>
       </c>
       <c r="D223" t="n">
-        <v>33.78034210205078</v>
+        <v>33.78033828735352</v>
       </c>
       <c r="E223" t="n">
-        <v>7.368970394134521</v>
+        <v>7.368969917297363</v>
       </c>
       <c r="F223" t="n">
         <v>-6.174063682556152</v>
@@ -4902,7 +4902,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>-9.296059608459473</v>
+        <v>-9.296061515808105</v>
       </c>
       <c r="B224" t="n">
         <v>18.09382438659668</v>
@@ -4914,7 +4914,7 @@
         <v>36.696044921875</v>
       </c>
       <c r="E224" t="n">
-        <v>11.1909761428833</v>
+        <v>11.19097518920898</v>
       </c>
       <c r="F224" t="n">
         <v>-6.304224014282227</v>
@@ -4922,7 +4922,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>-7.674901008605957</v>
+        <v>-7.674902439117432</v>
       </c>
       <c r="B225" t="n">
         <v>23.70100975036621</v>
@@ -4934,7 +4934,7 @@
         <v>36.92168807983398</v>
       </c>
       <c r="E225" t="n">
-        <v>14.83047771453857</v>
+        <v>14.83047676086426</v>
       </c>
       <c r="F225" t="n">
         <v>-8.207394599914551</v>
@@ -4942,13 +4942,13 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>-5.440899848937988</v>
+        <v>-5.44089937210083</v>
       </c>
       <c r="B226" t="n">
         <v>29.23537445068359</v>
       </c>
       <c r="C226" t="n">
-        <v>-6.969194412231445</v>
+        <v>-6.969193935394287</v>
       </c>
       <c r="D226" t="n">
         <v>36.69089508056641</v>
@@ -4962,7 +4962,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>-2.660975694656372</v>
+        <v>-2.660976886749268</v>
       </c>
       <c r="B227" t="n">
         <v>34.73098373413086</v>
@@ -4982,7 +4982,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>0.727039098739624</v>
+        <v>0.7270388007164001</v>
       </c>
       <c r="B228" t="n">
         <v>40.63057708740234</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>4.714947700500488</v>
+        <v>4.71494722366333</v>
       </c>
       <c r="B229" t="n">
         <v>47.07179260253906</v>
@@ -5011,13 +5011,13 @@
         <v>-14.53153228759766</v>
       </c>
       <c r="D229" t="n">
-        <v>31.97977638244629</v>
+        <v>31.97977828979492</v>
       </c>
       <c r="E229" t="n">
         <v>20.37187767028809</v>
       </c>
       <c r="F229" t="n">
-        <v>-2.77977180480957</v>
+        <v>-2.779771089553833</v>
       </c>
     </row>
     <row r="230">
@@ -5025,13 +5025,13 @@
         <v>9.05533504486084</v>
       </c>
       <c r="B230" t="n">
-        <v>53.2828369140625</v>
+        <v>53.28283309936523</v>
       </c>
       <c r="C230" t="n">
         <v>-10.12814044952393</v>
       </c>
       <c r="D230" t="n">
-        <v>29.21370697021484</v>
+        <v>29.21370887756348</v>
       </c>
       <c r="E230" t="n">
         <v>18.75815200805664</v>
@@ -5051,13 +5051,13 @@
         <v>-5.716984272003174</v>
       </c>
       <c r="D231" t="n">
-        <v>26.18086242675781</v>
+        <v>26.18086433410645</v>
       </c>
       <c r="E231" t="n">
         <v>16.65291404724121</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.00533245736733079</v>
+        <v>-0.005332360975444317</v>
       </c>
     </row>
     <row r="232">
@@ -5065,7 +5065,7 @@
         <v>17.14870452880859</v>
       </c>
       <c r="B232" t="n">
-        <v>60.73695373535156</v>
+        <v>60.7369499206543</v>
       </c>
       <c r="C232" t="n">
         <v>-2.068775653839111</v>
@@ -5077,7 +5077,7 @@
         <v>14.27495861053467</v>
       </c>
       <c r="F232" t="n">
-        <v>0.6683195829391479</v>
+        <v>0.6683197021484375</v>
       </c>
     </row>
     <row r="233">
@@ -5088,7 +5088,7 @@
         <v>60.86723709106445</v>
       </c>
       <c r="C233" t="n">
-        <v>0.533854067325592</v>
+        <v>0.5338540077209473</v>
       </c>
       <c r="D233" t="n">
         <v>19.95163154602051</v>
@@ -5097,7 +5097,7 @@
         <v>11.73736763000488</v>
       </c>
       <c r="F233" t="n">
-        <v>0.9332634210586548</v>
+        <v>0.93326336145401</v>
       </c>
     </row>
     <row r="234">
@@ -5105,7 +5105,7 @@
         <v>22.93546867370605</v>
       </c>
       <c r="B234" t="n">
-        <v>58.57997131347656</v>
+        <v>58.5799674987793</v>
       </c>
       <c r="C234" t="n">
         <v>2.13553524017334</v>
@@ -5114,7 +5114,7 @@
         <v>16.92017936706543</v>
       </c>
       <c r="E234" t="n">
-        <v>9.248022079467773</v>
+        <v>9.248021125793457</v>
       </c>
       <c r="F234" t="n">
         <v>1.042618870735168</v>
@@ -5122,30 +5122,30 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>24.91757774353027</v>
+        <v>24.91757965087891</v>
       </c>
       <c r="B235" t="n">
-        <v>54.17562103271484</v>
+        <v>54.17561721801758</v>
       </c>
       <c r="C235" t="n">
-        <v>3.010587930679321</v>
+        <v>3.0105881690979</v>
       </c>
       <c r="D235" t="n">
         <v>14.00596809387207</v>
       </c>
       <c r="E235" t="n">
-        <v>7.093613147735596</v>
+        <v>7.093612670898438</v>
       </c>
       <c r="F235" t="n">
-        <v>1.315624713897705</v>
+        <v>1.315624594688416</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>26.29769134521484</v>
+        <v>26.29769325256348</v>
       </c>
       <c r="B236" t="n">
-        <v>48.02933502197266</v>
+        <v>48.02933883666992</v>
       </c>
       <c r="C236" t="n">
         <v>3.411523580551147</v>
@@ -5154,7 +5154,7 @@
         <v>11.22652244567871</v>
       </c>
       <c r="E236" t="n">
-        <v>5.457214832305908</v>
+        <v>5.45721435546875</v>
       </c>
       <c r="F236" t="n">
         <v>1.95520806312561</v>
@@ -5171,10 +5171,10 @@
         <v>3.351086616516113</v>
       </c>
       <c r="D237" t="n">
-        <v>8.558293342590332</v>
+        <v>8.558294296264648</v>
       </c>
       <c r="E237" t="n">
-        <v>4.313275814056396</v>
+        <v>4.313276290893555</v>
       </c>
       <c r="F237" t="n">
         <v>2.946658611297607</v>
@@ -5191,10 +5191,10 @@
         <v>2.600748538970947</v>
       </c>
       <c r="D238" t="n">
-        <v>5.930118560791016</v>
+        <v>5.930117607116699</v>
       </c>
       <c r="E238" t="n">
-        <v>3.478049755096436</v>
+        <v>3.478049993515015</v>
       </c>
       <c r="F238" t="n">
         <v>4.125571250915527</v>
@@ -5202,10 +5202,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>27.1884937286377</v>
+        <v>27.18849563598633</v>
       </c>
       <c r="B239" t="n">
-        <v>24.06142616271973</v>
+        <v>24.06142425537109</v>
       </c>
       <c r="C239" t="n">
         <v>0.9494385719299316</v>
@@ -5214,10 +5214,10 @@
         <v>3.244021415710449</v>
       </c>
       <c r="E239" t="n">
-        <v>2.722131252288818</v>
+        <v>2.72213339805603</v>
       </c>
       <c r="F239" t="n">
-        <v>5.272953510284424</v>
+        <v>5.272953033447266</v>
       </c>
     </row>
     <row r="240">
@@ -5228,13 +5228,13 @@
         <v>16.09529304504395</v>
       </c>
       <c r="C240" t="n">
-        <v>-1.3554847240448</v>
+        <v>-1.355484843254089</v>
       </c>
       <c r="D240" t="n">
-        <v>0.4227895736694336</v>
+        <v>0.4227877259254456</v>
       </c>
       <c r="E240" t="n">
-        <v>1.878974437713623</v>
+        <v>1.878974795341492</v>
       </c>
       <c r="F240" t="n">
         <v>6.249489784240723</v>
@@ -5254,7 +5254,7 @@
         <v>-2.540711402893066</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9102359414100647</v>
+        <v>0.9102362394332886</v>
       </c>
       <c r="F241" t="n">
         <v>7.068041801452637</v>
@@ -5262,22 +5262,22 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>26.32605743408203</v>
+        <v>26.32605934143066</v>
       </c>
       <c r="B242" t="n">
-        <v>3.313671588897705</v>
+        <v>3.313672542572021</v>
       </c>
       <c r="C242" t="n">
         <v>-3.967965602874756</v>
       </c>
       <c r="D242" t="n">
-        <v>-5.562165260314941</v>
+        <v>-5.562167167663574</v>
       </c>
       <c r="E242" t="n">
-        <v>-0.08888095617294312</v>
+        <v>-0.08888065814971924</v>
       </c>
       <c r="F242" t="n">
-        <v>7.768787384033203</v>
+        <v>7.768786907196045</v>
       </c>
     </row>
     <row r="243">
@@ -5285,16 +5285,16 @@
         <v>26.6735782623291</v>
       </c>
       <c r="B243" t="n">
-        <v>-0.5154222249984741</v>
+        <v>-0.5154204964637756</v>
       </c>
       <c r="C243" t="n">
-        <v>-3.133389472961426</v>
+        <v>-3.133388996124268</v>
       </c>
       <c r="D243" t="n">
         <v>-8.497763633728027</v>
       </c>
       <c r="E243" t="n">
-        <v>-0.9346889853477478</v>
+        <v>-0.9346886873245239</v>
       </c>
       <c r="F243" t="n">
         <v>8.368043899536133</v>
@@ -5305,16 +5305,16 @@
         <v>27.29908561706543</v>
       </c>
       <c r="B244" t="n">
-        <v>-2.156373500823975</v>
+        <v>-2.156371593475342</v>
       </c>
       <c r="C244" t="n">
-        <v>-1.871567249298096</v>
+        <v>-1.871567368507385</v>
       </c>
       <c r="D244" t="n">
         <v>-11.19789409637451</v>
       </c>
       <c r="E244" t="n">
-        <v>-1.421621799468994</v>
+        <v>-1.421621441841125</v>
       </c>
       <c r="F244" t="n">
         <v>8.86894702911377</v>
@@ -5325,16 +5325,16 @@
         <v>27.95905685424805</v>
       </c>
       <c r="B245" t="n">
-        <v>-1.769334197044373</v>
+        <v>-1.769334316253662</v>
       </c>
       <c r="C245" t="n">
-        <v>-1.282746076583862</v>
+        <v>-1.282746195793152</v>
       </c>
       <c r="D245" t="n">
         <v>-13.53405284881592</v>
       </c>
       <c r="E245" t="n">
-        <v>-1.350719928741455</v>
+        <v>-1.350719571113586</v>
       </c>
       <c r="F245" t="n">
         <v>9.24886417388916</v>
@@ -5345,19 +5345,19 @@
         <v>28.52372550964355</v>
       </c>
       <c r="B246" t="n">
-        <v>0.2792726755142212</v>
+        <v>0.2792725265026093</v>
       </c>
       <c r="C246" t="n">
-        <v>-1.847443580627441</v>
+        <v>-1.847443461418152</v>
       </c>
       <c r="D246" t="n">
-        <v>-15.39405727386475</v>
+        <v>-15.39406108856201</v>
       </c>
       <c r="E246" t="n">
-        <v>-0.5190243124961853</v>
+        <v>-0.5190259218215942</v>
       </c>
       <c r="F246" t="n">
-        <v>9.439069747924805</v>
+        <v>9.439068794250488</v>
       </c>
     </row>
     <row r="247">
@@ -5371,10 +5371,10 @@
         <v>-3.327019691467285</v>
       </c>
       <c r="D247" t="n">
-        <v>-16.66753005981445</v>
+        <v>-16.66752433776855</v>
       </c>
       <c r="E247" t="n">
-        <v>1.267756938934326</v>
+        <v>1.267757296562195</v>
       </c>
       <c r="F247" t="n">
         <v>9.326447486877441</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>29.39312362670898</v>
+        <v>29.39312553405762</v>
       </c>
       <c r="B248" t="n">
-        <v>7.358151912689209</v>
+        <v>7.358150959014893</v>
       </c>
       <c r="C248" t="n">
         <v>-5.071263313293457</v>
       </c>
       <c r="D248" t="n">
-        <v>-17.24724578857422</v>
+        <v>-17.24724006652832</v>
       </c>
       <c r="E248" t="n">
-        <v>4.134988307952881</v>
+        <v>4.134988784790039</v>
       </c>
       <c r="F248" t="n">
-        <v>8.633083343505859</v>
+        <v>8.633082389831543</v>
       </c>
     </row>
     <row r="249">
@@ -5411,27 +5411,27 @@
         <v>-6.292547225952148</v>
       </c>
       <c r="D249" t="n">
-        <v>-17.04879379272461</v>
+        <v>-17.04879188537598</v>
       </c>
       <c r="E249" t="n">
-        <v>8.071103096008301</v>
+        <v>8.071102142333984</v>
       </c>
       <c r="F249" t="n">
-        <v>6.696540355682373</v>
+        <v>6.696539878845215</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>31.66978645324707</v>
+        <v>31.6697883605957</v>
       </c>
       <c r="B250" t="n">
-        <v>9.356435775756836</v>
+        <v>9.35643482208252</v>
       </c>
       <c r="C250" t="n">
         <v>-3.321012496948242</v>
       </c>
       <c r="D250" t="n">
-        <v>-17.92427444458008</v>
+        <v>-17.92427253723145</v>
       </c>
       <c r="E250" t="n">
         <v>18.3529109954834</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>31.87593269348145</v>
+        <v>31.87593460083008</v>
       </c>
       <c r="B251" t="n">
         <v>12.98259449005127</v>
@@ -5451,7 +5451,7 @@
         <v>-5.858014106750488</v>
       </c>
       <c r="D251" t="n">
-        <v>-16.00893402099609</v>
+        <v>-16.00893211364746</v>
       </c>
       <c r="E251" t="n">
         <v>23.39445686340332</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>31.93228721618652</v>
+        <v>31.93228912353516</v>
       </c>
       <c r="B252" t="n">
         <v>16.9053840637207</v>
@@ -5508,10 +5508,10 @@
         <v>21.53725242614746</v>
       </c>
       <c r="C254" t="n">
-        <v>-1.859369993209839</v>
+        <v>-1.859370112419128</v>
       </c>
       <c r="D254" t="n">
-        <v>-5.58716869354248</v>
+        <v>-5.587170600891113</v>
       </c>
       <c r="E254" t="n">
         <v>43.60052871704102</v>
@@ -5522,22 +5522,22 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>27.82575416564941</v>
+        <v>27.82575607299805</v>
       </c>
       <c r="B255" t="n">
         <v>20.2386646270752</v>
       </c>
       <c r="C255" t="n">
-        <v>0.1563393622636795</v>
+        <v>0.1563394367694855</v>
       </c>
       <c r="D255" t="n">
-        <v>-0.9973249435424805</v>
+        <v>-0.9973248839378357</v>
       </c>
       <c r="E255" t="n">
-        <v>50.55424118041992</v>
+        <v>50.55423736572266</v>
       </c>
       <c r="F255" t="n">
-        <v>-10.69872283935547</v>
+        <v>-10.69872379302979</v>
       </c>
     </row>
     <row r="256">
@@ -5551,13 +5551,13 @@
         <v>1.591849207878113</v>
       </c>
       <c r="D256" t="n">
-        <v>3.693600654602051</v>
+        <v>3.693599700927734</v>
       </c>
       <c r="E256" t="n">
-        <v>55.79479598999023</v>
+        <v>55.79479217529297</v>
       </c>
       <c r="F256" t="n">
-        <v>-5.353937149047852</v>
+        <v>-5.35393762588501</v>
       </c>
     </row>
     <row r="257">
@@ -5568,13 +5568,13 @@
         <v>14.87725353240967</v>
       </c>
       <c r="C257" t="n">
-        <v>2.757955551147461</v>
+        <v>2.75795578956604</v>
       </c>
       <c r="D257" t="n">
         <v>8.169285774230957</v>
       </c>
       <c r="E257" t="n">
-        <v>58.60062026977539</v>
+        <v>58.60061645507812</v>
       </c>
       <c r="F257" t="n">
         <v>-0.8587443828582764</v>
@@ -5585,13 +5585,13 @@
         <v>18.97776985168457</v>
       </c>
       <c r="B258" t="n">
-        <v>13.11509895324707</v>
+        <v>13.11509799957275</v>
       </c>
       <c r="C258" t="n">
         <v>3.841182231903076</v>
       </c>
       <c r="D258" t="n">
-        <v>12.20143604278564</v>
+        <v>12.20143699645996</v>
       </c>
       <c r="E258" t="n">
         <v>58.77616882324219</v>
@@ -5611,13 +5611,13 @@
         <v>4.738645553588867</v>
       </c>
       <c r="D259" t="n">
-        <v>15.67985343933105</v>
+        <v>15.67985439300537</v>
       </c>
       <c r="E259" t="n">
-        <v>56.53317642211914</v>
+        <v>56.53317260742188</v>
       </c>
       <c r="F259" t="n">
-        <v>3.506303787231445</v>
+        <v>3.506303548812866</v>
       </c>
     </row>
     <row r="260">
@@ -5637,7 +5637,7 @@
         <v>52.38088226318359</v>
       </c>
       <c r="F260" t="n">
-        <v>4.035130977630615</v>
+        <v>4.035130500793457</v>
       </c>
     </row>
     <row r="261">
@@ -5662,7 +5662,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>8.672328948974609</v>
+        <v>8.672327995300293</v>
       </c>
       <c r="B262" t="n">
         <v>5.682637691497803</v>
@@ -5677,15 +5677,15 @@
         <v>40.2563362121582</v>
       </c>
       <c r="F262" t="n">
-        <v>4.190563678741455</v>
+        <v>4.190563201904297</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>5.844160079956055</v>
+        <v>5.844159603118896</v>
       </c>
       <c r="B263" t="n">
-        <v>3.595280170440674</v>
+        <v>3.59528112411499</v>
       </c>
       <c r="C263" t="n">
         <v>6.184038639068604</v>
@@ -5694,7 +5694,7 @@
         <v>23.26683044433594</v>
       </c>
       <c r="E263" t="n">
-        <v>32.77508163452148</v>
+        <v>32.77508544921875</v>
       </c>
       <c r="F263" t="n">
         <v>3.746766805648804</v>
@@ -5702,13 +5702,13 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>2.984752416610718</v>
+        <v>2.984753131866455</v>
       </c>
       <c r="B264" t="n">
-        <v>1.955737709999084</v>
+        <v>1.955738544464111</v>
       </c>
       <c r="C264" t="n">
-        <v>6.777115345001221</v>
+        <v>6.777114868164062</v>
       </c>
       <c r="D264" t="n">
         <v>23.59543800354004</v>
@@ -5722,10 +5722,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>0.1822297722101212</v>
+        <v>0.1822294890880585</v>
       </c>
       <c r="B265" t="n">
-        <v>0.8602758646011353</v>
+        <v>0.8602756857872009</v>
       </c>
       <c r="C265" t="n">
         <v>7.666539192199707</v>
@@ -5742,10 +5742,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>-2.444585084915161</v>
+        <v>-2.444584369659424</v>
       </c>
       <c r="B266" t="n">
-        <v>0.3979192972183228</v>
+        <v>0.3979191482067108</v>
       </c>
       <c r="C266" t="n">
         <v>8.844539642333984</v>
@@ -5757,15 +5757,15 @@
         <v>8.901814460754395</v>
       </c>
       <c r="F266" t="n">
-        <v>-0.0167310107499361</v>
+        <v>-0.01673091575503349</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>-4.782082557678223</v>
+        <v>-4.782082080841064</v>
       </c>
       <c r="B267" t="n">
-        <v>0.6112104654312134</v>
+        <v>0.6112102866172791</v>
       </c>
       <c r="C267" t="n">
         <v>10.2617712020874</v>
@@ -5774,7 +5774,7 @@
         <v>23.1527042388916</v>
       </c>
       <c r="E267" t="n">
-        <v>2.307258129119873</v>
+        <v>2.307258367538452</v>
       </c>
       <c r="F267" t="n">
         <v>-0.7932679653167725</v>
@@ -5782,10 +5782,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>-6.775271415710449</v>
+        <v>-6.775272846221924</v>
       </c>
       <c r="B268" t="n">
-        <v>1.412594437599182</v>
+        <v>1.412596225738525</v>
       </c>
       <c r="C268" t="n">
         <v>11.76390361785889</v>
@@ -5794,27 +5794,27 @@
         <v>23.20088577270508</v>
       </c>
       <c r="E268" t="n">
-        <v>-2.506289005279541</v>
+        <v>-2.506288766860962</v>
       </c>
       <c r="F268" t="n">
-        <v>-0.9441506862640381</v>
+        <v>-0.9441509246826172</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>-8.457688331604004</v>
+        <v>-8.457690238952637</v>
       </c>
       <c r="B269" t="n">
         <v>2.572008609771729</v>
       </c>
       <c r="C269" t="n">
-        <v>13.08506202697754</v>
+        <v>13.08506107330322</v>
       </c>
       <c r="D269" t="n">
         <v>23.49345016479492</v>
       </c>
       <c r="E269" t="n">
-        <v>-4.942520618438721</v>
+        <v>-4.942520141601562</v>
       </c>
       <c r="F269" t="n">
         <v>-0.5351746082305908</v>
@@ -5828,16 +5828,16 @@
         <v>3.869619846343994</v>
       </c>
       <c r="C270" t="n">
-        <v>13.97856330871582</v>
+        <v>13.97856426239014</v>
       </c>
       <c r="D270" t="n">
         <v>23.98394203186035</v>
       </c>
       <c r="E270" t="n">
-        <v>-4.872562885284424</v>
+        <v>-4.872562408447266</v>
       </c>
       <c r="F270" t="n">
-        <v>0.1904264837503433</v>
+        <v>0.1904264539480209</v>
       </c>
     </row>
     <row r="271">
@@ -5848,13 +5848,13 @@
         <v>5.337913036346436</v>
       </c>
       <c r="C271" t="n">
-        <v>14.42393970489502</v>
+        <v>14.42394065856934</v>
       </c>
       <c r="D271" t="n">
         <v>24.58280944824219</v>
       </c>
       <c r="E271" t="n">
-        <v>-2.732729434967041</v>
+        <v>-2.732731103897095</v>
       </c>
       <c r="F271" t="n">
         <v>0.7501280307769775</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>-12.15121746063232</v>
+        <v>-12.15121936798096</v>
       </c>
       <c r="B272" t="n">
         <v>7.319169521331787</v>
@@ -5874,10 +5874,10 @@
         <v>25.18586921691895</v>
       </c>
       <c r="E272" t="n">
-        <v>0.6705909371376038</v>
+        <v>0.6705931425094604</v>
       </c>
       <c r="F272" t="n">
-        <v>0.4851628541946411</v>
+        <v>0.4851627349853516</v>
       </c>
     </row>
     <row r="273">
@@ -5885,30 +5885,30 @@
         <v>-12.62585544586182</v>
       </c>
       <c r="B273" t="n">
-        <v>10.28879356384277</v>
+        <v>10.28879261016846</v>
       </c>
       <c r="C273" t="n">
-        <v>14.03341293334961</v>
+        <v>14.03341197967529</v>
       </c>
       <c r="D273" t="n">
-        <v>25.7301139831543</v>
+        <v>25.73011589050293</v>
       </c>
       <c r="E273" t="n">
-        <v>4.542938709259033</v>
+        <v>4.542939186096191</v>
       </c>
       <c r="F273" t="n">
-        <v>-1.09139609336853</v>
+        <v>-1.091395854949951</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>-12.36716938018799</v>
+        <v>-12.36716747283936</v>
       </c>
       <c r="B274" t="n">
         <v>14.52314949035645</v>
       </c>
       <c r="C274" t="n">
-        <v>12.35265064239502</v>
+        <v>12.35265159606934</v>
       </c>
       <c r="D274" t="n">
         <v>26.21180152893066</v>
@@ -5917,7 +5917,7 @@
         <v>8.490161895751953</v>
       </c>
       <c r="F274" t="n">
-        <v>-3.587117195129395</v>
+        <v>-3.587116956710815</v>
       </c>
     </row>
     <row r="275">
@@ -5931,18 +5931,18 @@
         <v>8.268256187438965</v>
       </c>
       <c r="D275" t="n">
-        <v>31.90181159973145</v>
+        <v>31.90181350708008</v>
       </c>
       <c r="E275" t="n">
-        <v>9.901644706726074</v>
+        <v>9.901643753051758</v>
       </c>
       <c r="F275" t="n">
-        <v>-3.978342056274414</v>
+        <v>-3.978342294692993</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>-9.380328178405762</v>
+        <v>-9.380330085754395</v>
       </c>
       <c r="B276" t="n">
         <v>25.51922607421875</v>
@@ -5962,10 +5962,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>-7.038327217102051</v>
+        <v>-7.038326740264893</v>
       </c>
       <c r="B277" t="n">
-        <v>31.05094909667969</v>
+        <v>31.05095100402832</v>
       </c>
       <c r="C277" t="n">
         <v>-8.73859977722168</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>-4.389912605285645</v>
+        <v>-4.389912128448486</v>
       </c>
       <c r="B278" t="n">
-        <v>36.28329467773438</v>
+        <v>36.28329849243164</v>
       </c>
       <c r="C278" t="n">
         <v>-15.86844348907471</v>
@@ -6002,13 +6002,13 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>-1.338902711868286</v>
+        <v>-1.338901996612549</v>
       </c>
       <c r="B279" t="n">
-        <v>41.59658432006836</v>
+        <v>41.59658813476562</v>
       </c>
       <c r="C279" t="n">
-        <v>-17.52121162414551</v>
+        <v>-17.52120971679688</v>
       </c>
       <c r="D279" t="n">
         <v>29.37483024597168</v>
@@ -6017,21 +6017,21 @@
         <v>20.1416187286377</v>
       </c>
       <c r="F279" t="n">
-        <v>-2.611788272857666</v>
+        <v>-2.611788034439087</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>2.27518630027771</v>
+        <v>2.275186061859131</v>
       </c>
       <c r="B280" t="n">
         <v>47.29164505004883</v>
       </c>
       <c r="C280" t="n">
-        <v>-14.71038341522217</v>
+        <v>-14.7103853225708</v>
       </c>
       <c r="D280" t="n">
-        <v>27.15071296691895</v>
+        <v>27.15071487426758</v>
       </c>
       <c r="E280" t="n">
         <v>19.93883895874023</v>
@@ -6042,27 +6042,27 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>6.418020248413086</v>
+        <v>6.418019771575928</v>
       </c>
       <c r="B281" t="n">
-        <v>52.91487121582031</v>
+        <v>52.91486740112305</v>
       </c>
       <c r="C281" t="n">
         <v>-10.16516590118408</v>
       </c>
       <c r="D281" t="n">
-        <v>24.37943458557129</v>
+        <v>24.37943649291992</v>
       </c>
       <c r="E281" t="n">
         <v>18.67798805236816</v>
       </c>
       <c r="F281" t="n">
-        <v>1.242243528366089</v>
+        <v>1.242243409156799</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>10.78283500671387</v>
+        <v>10.78283405303955</v>
       </c>
       <c r="B282" t="n">
         <v>57.51180648803711</v>
@@ -6088,7 +6088,7 @@
         <v>60.28279876708984</v>
       </c>
       <c r="C283" t="n">
-        <v>-1.677969932556152</v>
+        <v>-1.677970051765442</v>
       </c>
       <c r="D283" t="n">
         <v>18.06912994384766</v>
@@ -6097,7 +6097,7 @@
         <v>14.74167251586914</v>
       </c>
       <c r="F283" t="n">
-        <v>3.454236507415771</v>
+        <v>3.454236268997192</v>
       </c>
     </row>
     <row r="284">
@@ -6105,10 +6105,10 @@
         <v>18.52582550048828</v>
       </c>
       <c r="B284" t="n">
-        <v>60.81089019775391</v>
+        <v>60.81088638305664</v>
       </c>
       <c r="C284" t="n">
-        <v>1.485304713249207</v>
+        <v>1.485304594039917</v>
       </c>
       <c r="D284" t="n">
         <v>14.85952091217041</v>
@@ -6117,7 +6117,7 @@
         <v>12.25128364562988</v>
       </c>
       <c r="F284" t="n">
-        <v>3.900246858596802</v>
+        <v>3.900246620178223</v>
       </c>
     </row>
     <row r="285">
@@ -6125,19 +6125,19 @@
         <v>21.44092559814453</v>
       </c>
       <c r="B285" t="n">
-        <v>59.03470611572266</v>
+        <v>59.03470230102539</v>
       </c>
       <c r="C285" t="n">
-        <v>3.687251329421997</v>
+        <v>3.687251091003418</v>
       </c>
       <c r="D285" t="n">
         <v>11.71191692352295</v>
       </c>
       <c r="E285" t="n">
-        <v>9.486035346984863</v>
+        <v>9.486034393310547</v>
       </c>
       <c r="F285" t="n">
-        <v>3.948690891265869</v>
+        <v>3.94869065284729</v>
       </c>
     </row>
     <row r="286">
@@ -6154,7 +6154,7 @@
         <v>8.657866477966309</v>
       </c>
       <c r="E286" t="n">
-        <v>6.796084880828857</v>
+        <v>6.796085357666016</v>
       </c>
       <c r="F286" t="n">
         <v>3.950659275054932</v>
@@ -6174,10 +6174,10 @@
         <v>5.721749305725098</v>
       </c>
       <c r="E287" t="n">
-        <v>4.566328525543213</v>
+        <v>4.566328048706055</v>
       </c>
       <c r="F287" t="n">
-        <v>4.229508876800537</v>
+        <v>4.229508399963379</v>
       </c>
     </row>
     <row r="288">
@@ -6194,10 +6194,10 @@
         <v>2.917705535888672</v>
       </c>
       <c r="E288" t="n">
-        <v>2.998502254486084</v>
+        <v>2.998502492904663</v>
       </c>
       <c r="F288" t="n">
-        <v>4.915377616882324</v>
+        <v>4.915377140045166</v>
       </c>
     </row>
     <row r="289">
@@ -6208,13 +6208,13 @@
         <v>34.83768463134766</v>
       </c>
       <c r="C289" t="n">
-        <v>3.63729190826416</v>
+        <v>3.637292146682739</v>
       </c>
       <c r="D289" t="n">
-        <v>0.2260293811559677</v>
+        <v>0.2260294556617737</v>
       </c>
       <c r="E289" t="n">
-        <v>2.077577114105225</v>
+        <v>2.077577352523804</v>
       </c>
       <c r="F289" t="n">
         <v>6.00917387008667</v>
@@ -6222,7 +6222,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>27.07328224182129</v>
+        <v>27.07328033447266</v>
       </c>
       <c r="B290" t="n">
         <v>26.84604263305664</v>
@@ -6234,10 +6234,10 @@
         <v>-2.410183906555176</v>
       </c>
       <c r="E290" t="n">
-        <v>1.613036632537842</v>
+        <v>1.61303699016571</v>
       </c>
       <c r="F290" t="n">
-        <v>7.393527030944824</v>
+        <v>7.393526554107666</v>
       </c>
     </row>
     <row r="291">
@@ -6248,16 +6248,16 @@
         <v>19.14215469360352</v>
       </c>
       <c r="C291" t="n">
-        <v>0.704343318939209</v>
+        <v>0.7043432593345642</v>
       </c>
       <c r="D291" t="n">
         <v>-5.05064868927002</v>
       </c>
       <c r="E291" t="n">
-        <v>1.343421459197998</v>
+        <v>1.343419909477234</v>
       </c>
       <c r="F291" t="n">
-        <v>8.84004020690918</v>
+        <v>8.840039253234863</v>
       </c>
     </row>
     <row r="292">
@@ -6268,44 +6268,44 @@
         <v>11.99857044219971</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.1150013580918312</v>
+        <v>-0.1150012984871864</v>
       </c>
       <c r="D292" t="n">
         <v>-7.705105781555176</v>
       </c>
       <c r="E292" t="n">
-        <v>1.087508678436279</v>
+        <v>1.087509036064148</v>
       </c>
       <c r="F292" t="n">
-        <v>10.10252571105957</v>
+        <v>10.10252475738525</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>26.1852855682373</v>
+        <v>26.18528747558594</v>
       </c>
       <c r="B293" t="n">
         <v>5.646430492401123</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.277513176202774</v>
+        <v>-0.2775132358074188</v>
       </c>
       <c r="D293" t="n">
         <v>-10.306077003479</v>
       </c>
       <c r="E293" t="n">
-        <v>0.8509936928749084</v>
+        <v>0.8509958982467651</v>
       </c>
       <c r="F293" t="n">
-        <v>11.04039096832275</v>
+        <v>11.04039001464844</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>26.11285591125488</v>
+        <v>26.11285781860352</v>
       </c>
       <c r="B294" t="n">
-        <v>0.6741682291030884</v>
+        <v>0.6741699576377869</v>
       </c>
       <c r="C294" t="n">
         <v>-0.1022987142205238</v>
@@ -6314,10 +6314,10 @@
         <v>-12.73534679412842</v>
       </c>
       <c r="E294" t="n">
-        <v>0.8164916634559631</v>
+        <v>0.8164900541305542</v>
       </c>
       <c r="F294" t="n">
-        <v>11.6800422668457</v>
+        <v>11.68004131317139</v>
       </c>
     </row>
     <row r="295">
@@ -6334,7 +6334,7 @@
         <v>-14.87861919403076</v>
       </c>
       <c r="E295" t="n">
-        <v>1.230447292327881</v>
+        <v>1.230445742607117</v>
       </c>
       <c r="F295" t="n">
         <v>12.15431213378906</v>
@@ -6348,16 +6348,16 @@
         <v>-2.43464994430542</v>
       </c>
       <c r="C296" t="n">
-        <v>0.9026802778244019</v>
+        <v>0.9026802182197571</v>
       </c>
       <c r="D296" t="n">
-        <v>-16.65167236328125</v>
+        <v>-16.65167045593262</v>
       </c>
       <c r="E296" t="n">
-        <v>2.305284023284912</v>
+        <v>2.305284261703491</v>
       </c>
       <c r="F296" t="n">
-        <v>12.54055881500244</v>
+        <v>12.54055786132812</v>
       </c>
     </row>
     <row r="297">
@@ -6365,19 +6365,19 @@
         <v>27.35630035400391</v>
       </c>
       <c r="B297" t="n">
-        <v>-0.6113256216049194</v>
+        <v>-0.6113258004188538</v>
       </c>
       <c r="C297" t="n">
         <v>1.627059459686279</v>
       </c>
       <c r="D297" t="n">
-        <v>-18.02019500732422</v>
+        <v>-18.02019309997559</v>
       </c>
       <c r="E297" t="n">
-        <v>4.127233028411865</v>
+        <v>4.127233505249023</v>
       </c>
       <c r="F297" t="n">
-        <v>12.72392559051514</v>
+        <v>12.72392463684082</v>
       </c>
     </row>
     <row r="298">
@@ -6391,10 +6391,10 @@
         <v>1.70838725566864</v>
       </c>
       <c r="D298" t="n">
-        <v>-18.93483352661133</v>
+        <v>-18.9348316192627</v>
       </c>
       <c r="E298" t="n">
-        <v>6.708158016204834</v>
+        <v>6.708157539367676</v>
       </c>
       <c r="F298" t="n">
         <v>12.35292053222656</v>
@@ -6405,19 +6405,19 @@
         <v>27.7932243347168</v>
       </c>
       <c r="B299" t="n">
-        <v>5.071383953094482</v>
+        <v>5.071384906768799</v>
       </c>
       <c r="C299" t="n">
-        <v>0.1474976092576981</v>
+        <v>0.1474975645542145</v>
       </c>
       <c r="D299" t="n">
-        <v>-19.30395126342773</v>
+        <v>-19.3039493560791</v>
       </c>
       <c r="E299" t="n">
         <v>9.998783111572266</v>
       </c>
       <c r="F299" t="n">
-        <v>10.83739471435547</v>
+        <v>10.83739376068115</v>
       </c>
     </row>
     <row r="300">
@@ -6428,16 +6428,16 @@
         <v>7.407253742218018</v>
       </c>
       <c r="C300" t="n">
-        <v>-2.949343204498291</v>
+        <v>-2.949342727661133</v>
       </c>
       <c r="D300" t="n">
-        <v>-19.0037956237793</v>
+        <v>-19.00379371643066</v>
       </c>
       <c r="E300" t="n">
         <v>13.90792655944824</v>
       </c>
       <c r="F300" t="n">
-        <v>7.416305065155029</v>
+        <v>7.416304588317871</v>
       </c>
     </row>
     <row r="301">
@@ -6445,30 +6445,30 @@
         <v>31.08670043945312</v>
       </c>
       <c r="B301" t="n">
-        <v>9.238125801086426</v>
+        <v>9.238124847412109</v>
       </c>
       <c r="C301" t="n">
         <v>-3.012162685394287</v>
       </c>
       <c r="D301" t="n">
-        <v>-17.85517883300781</v>
+        <v>-17.85517692565918</v>
       </c>
       <c r="E301" t="n">
         <v>16.28764343261719</v>
       </c>
       <c r="F301" t="n">
-        <v>-0.6944398880004883</v>
+        <v>-0.6944396495819092</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>31.59165382385254</v>
+        <v>31.59165573120117</v>
       </c>
       <c r="B302" t="n">
         <v>13.06134128570557</v>
       </c>
       <c r="C302" t="n">
-        <v>-5.081531524658203</v>
+        <v>-5.081531047821045</v>
       </c>
       <c r="D302" t="n">
         <v>-15.53035640716553</v>
@@ -6494,7 +6494,7 @@
         <v>-12.30511379241943</v>
       </c>
       <c r="E303" t="n">
-        <v>27.8695182800293</v>
+        <v>27.86951637268066</v>
       </c>
       <c r="F303" t="n">
         <v>-15.69688892364502</v>
@@ -6502,13 +6502,13 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>31.55014991760254</v>
+        <v>31.55015182495117</v>
       </c>
       <c r="B304" t="n">
         <v>19.40524101257324</v>
       </c>
       <c r="C304" t="n">
-        <v>-4.682677745819092</v>
+        <v>-4.682677268981934</v>
       </c>
       <c r="D304" t="n">
         <v>-8.382142066955566</v>
@@ -6517,7 +6517,7 @@
         <v>34.65926361083984</v>
       </c>
       <c r="F304" t="n">
-        <v>-18.74748992919922</v>
+        <v>-18.74749183654785</v>
       </c>
     </row>
     <row r="305">
@@ -6531,13 +6531,13 @@
         <v>-3.121367454528809</v>
       </c>
       <c r="D305" t="n">
-        <v>-3.973158836364746</v>
+        <v>-3.973160743713379</v>
       </c>
       <c r="E305" t="n">
         <v>41.58562469482422</v>
       </c>
       <c r="F305" t="n">
-        <v>-17.43003082275391</v>
+        <v>-17.43003273010254</v>
       </c>
     </row>
     <row r="306">
@@ -6548,16 +6548,16 @@
         <v>18.78349304199219</v>
       </c>
       <c r="C306" t="n">
-        <v>-1.64630651473999</v>
+        <v>-1.646306872367859</v>
       </c>
       <c r="D306" t="n">
-        <v>0.7387876510620117</v>
+        <v>0.7387877106666565</v>
       </c>
       <c r="E306" t="n">
         <v>47.93990707397461</v>
       </c>
       <c r="F306" t="n">
-        <v>-13.67917156219482</v>
+        <v>-13.67917251586914</v>
       </c>
     </row>
     <row r="307">
@@ -6568,13 +6568,13 @@
         <v>16.41655158996582</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.386653333902359</v>
+        <v>-0.3866532742977142</v>
       </c>
       <c r="D307" t="n">
         <v>5.578110694885254</v>
       </c>
       <c r="E307" t="n">
-        <v>53.00543594360352</v>
+        <v>53.00543212890625</v>
       </c>
       <c r="F307" t="n">
         <v>-9.418597221374512</v>
@@ -6614,10 +6614,10 @@
         <v>14.86788082122803</v>
       </c>
       <c r="E309" t="n">
-        <v>57.64303588867188</v>
+        <v>57.64303207397461</v>
       </c>
       <c r="F309" t="n">
-        <v>-2.741374492645264</v>
+        <v>-2.741374254226685</v>
       </c>
     </row>
     <row r="310">
@@ -6625,16 +6625,16 @@
         <v>17.87735557556152</v>
       </c>
       <c r="B310" t="n">
-        <v>10.45798683166504</v>
+        <v>10.45798587799072</v>
       </c>
       <c r="C310" t="n">
-        <v>2.646105051040649</v>
+        <v>2.646105289459229</v>
       </c>
       <c r="D310" t="n">
         <v>18.93386268615723</v>
       </c>
       <c r="E310" t="n">
-        <v>57.0181770324707</v>
+        <v>57.01817321777344</v>
       </c>
       <c r="F310" t="n">
         <v>-0.4954097270965576</v>
@@ -6645,7 +6645,7 @@
         <v>15.22545909881592</v>
       </c>
       <c r="B311" t="n">
-        <v>8.244767189025879</v>
+        <v>8.244766235351562</v>
       </c>
       <c r="C311" t="n">
         <v>2.945981502532959</v>
@@ -6654,7 +6654,7 @@
         <v>22.4028148651123</v>
       </c>
       <c r="E311" t="n">
-        <v>54.56760406494141</v>
+        <v>54.56760025024414</v>
       </c>
       <c r="F311" t="n">
         <v>1.353364944458008</v>
@@ -6662,13 +6662,13 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>12.5055456161499</v>
+        <v>12.50554466247559</v>
       </c>
       <c r="B312" t="n">
         <v>5.696783542633057</v>
       </c>
       <c r="C312" t="n">
-        <v>2.958673477172852</v>
+        <v>2.958673238754272</v>
       </c>
       <c r="D312" t="n">
         <v>25.16475868225098</v>
@@ -6691,7 +6691,7 @@
         <v>3.033843278884888</v>
       </c>
       <c r="D313" t="n">
-        <v>27.15337371826172</v>
+        <v>27.15337562561035</v>
       </c>
       <c r="E313" t="n">
         <v>44.88462829589844</v>
@@ -6702,13 +6702,13 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>7.074122428894043</v>
+        <v>7.074121952056885</v>
       </c>
       <c r="B314" t="n">
-        <v>1.315016388893127</v>
+        <v>1.315016269683838</v>
       </c>
       <c r="C314" t="n">
-        <v>3.395411729812622</v>
+        <v>3.395411968231201</v>
       </c>
       <c r="D314" t="n">
         <v>28.35718727111816</v>
@@ -6722,19 +6722,19 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>4.494717597961426</v>
+        <v>4.494717121124268</v>
       </c>
       <c r="B315" t="n">
-        <v>0.06683599203824997</v>
+        <v>0.06683583557605743</v>
       </c>
       <c r="C315" t="n">
-        <v>4.07505464553833</v>
+        <v>4.075055122375488</v>
       </c>
       <c r="D315" t="n">
         <v>28.83552742004395</v>
       </c>
       <c r="E315" t="n">
-        <v>29.94781303405762</v>
+        <v>29.94781112670898</v>
       </c>
       <c r="F315" t="n">
         <v>2.958987712860107</v>
@@ -6742,13 +6742,13 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>2.043290853500366</v>
+        <v>2.043290615081787</v>
       </c>
       <c r="B316" t="n">
-        <v>-0.5185369253158569</v>
+        <v>-0.5185371041297913</v>
       </c>
       <c r="C316" t="n">
-        <v>5.040205001831055</v>
+        <v>5.040204524993896</v>
       </c>
       <c r="D316" t="n">
         <v>28.72806739807129</v>
@@ -6762,50 +6762,50 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>-0.2908270061016083</v>
+        <v>-0.2908263504505157</v>
       </c>
       <c r="B317" t="n">
-        <v>-0.5851091146469116</v>
+        <v>-0.5851092934608459</v>
       </c>
       <c r="C317" t="n">
-        <v>6.278819561004639</v>
+        <v>6.27881908416748</v>
       </c>
       <c r="D317" t="n">
-        <v>28.26858139038086</v>
+        <v>28.26858329772949</v>
       </c>
       <c r="E317" t="n">
-        <v>12.59984397888184</v>
+        <v>12.59984302520752</v>
       </c>
       <c r="F317" t="n">
-        <v>0.09127606451511383</v>
+        <v>0.09127604216337204</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>-2.513736009597778</v>
+        <v>-2.513737201690674</v>
       </c>
       <c r="B318" t="n">
-        <v>-0.2890008687973022</v>
+        <v>-0.2890010178089142</v>
       </c>
       <c r="C318" t="n">
-        <v>7.767562389373779</v>
+        <v>7.767562866210938</v>
       </c>
       <c r="D318" t="n">
-        <v>27.77482032775879</v>
+        <v>27.77482223510742</v>
       </c>
       <c r="E318" t="n">
-        <v>4.697786808013916</v>
+        <v>4.697787284851074</v>
       </c>
       <c r="F318" t="n">
-        <v>-1.157662391662598</v>
+        <v>-1.157662153244019</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>-4.596842765808105</v>
+        <v>-4.596842288970947</v>
       </c>
       <c r="B319" t="n">
-        <v>0.2924333810806274</v>
+        <v>0.2924351394176483</v>
       </c>
       <c r="C319" t="n">
         <v>9.412167549133301</v>
@@ -6814,30 +6814,30 @@
         <v>27.5660514831543</v>
       </c>
       <c r="E319" t="n">
-        <v>-1.4242844581604</v>
+        <v>-1.424286007881165</v>
       </c>
       <c r="F319" t="n">
-        <v>-2.020573139190674</v>
+        <v>-2.020572900772095</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>-6.494780540466309</v>
+        <v>-6.49478006362915</v>
       </c>
       <c r="B320" t="n">
-        <v>1.158592820167542</v>
+        <v>1.158592700958252</v>
       </c>
       <c r="C320" t="n">
-        <v>11.05802440643311</v>
+        <v>11.05802536010742</v>
       </c>
       <c r="D320" t="n">
         <v>27.82413673400879</v>
       </c>
       <c r="E320" t="n">
-        <v>-4.860735416412354</v>
+        <v>-4.860734939575195</v>
       </c>
       <c r="F320" t="n">
-        <v>-2.45328950881958</v>
+        <v>-2.453289747238159</v>
       </c>
     </row>
     <row r="321">
@@ -6851,13 +6851,13 @@
         <v>12.48443603515625</v>
       </c>
       <c r="D321" t="n">
-        <v>28.50441551208496</v>
+        <v>28.50441741943359</v>
       </c>
       <c r="E321" t="n">
-        <v>-5.260975360870361</v>
+        <v>-5.260976791381836</v>
       </c>
       <c r="F321" t="n">
-        <v>-2.448488712310791</v>
+        <v>-2.448487997055054</v>
       </c>
     </row>
     <row r="322">
@@ -6865,7 +6865,7 @@
         <v>-9.616084098815918</v>
       </c>
       <c r="B322" t="n">
-        <v>3.887897968292236</v>
+        <v>3.88789701461792</v>
       </c>
       <c r="C322" t="n">
         <v>13.44190311431885</v>
@@ -6874,15 +6874,15 @@
         <v>29.38434791564941</v>
       </c>
       <c r="E322" t="n">
-        <v>-3.072067737579346</v>
+        <v>-3.072067499160767</v>
       </c>
       <c r="F322" t="n">
-        <v>-2.232761859893799</v>
+        <v>-2.23276162147522</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>-10.72533893585205</v>
+        <v>-10.72534084320068</v>
       </c>
       <c r="B323" t="n">
         <v>5.991917133331299</v>
@@ -6891,33 +6891,33 @@
         <v>13.76377487182617</v>
       </c>
       <c r="D323" t="n">
-        <v>30.20112609863281</v>
+        <v>30.20112800598145</v>
       </c>
       <c r="E323" t="n">
-        <v>0.6637492775917053</v>
+        <v>0.6637495756149292</v>
       </c>
       <c r="F323" t="n">
-        <v>-2.4004225730896</v>
+        <v>-2.400422334671021</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>-11.32160472869873</v>
+        <v>-11.32160663604736</v>
       </c>
       <c r="B324" t="n">
-        <v>8.960597991943359</v>
+        <v>8.960597038269043</v>
       </c>
       <c r="C324" t="n">
-        <v>13.32777309417725</v>
+        <v>13.32777214050293</v>
       </c>
       <c r="D324" t="n">
-        <v>30.79345321655273</v>
+        <v>30.79345512390137</v>
       </c>
       <c r="E324" t="n">
-        <v>4.755143642425537</v>
+        <v>4.755143165588379</v>
       </c>
       <c r="F324" t="n">
-        <v>-3.626701354980469</v>
+        <v>-3.62670111656189</v>
       </c>
     </row>
     <row r="325">
@@ -6928,16 +6928,16 @@
         <v>13.06296539306641</v>
       </c>
       <c r="C325" t="n">
-        <v>11.76444721221924</v>
+        <v>11.76444816589355</v>
       </c>
       <c r="D325" t="n">
         <v>31.16432571411133</v>
       </c>
       <c r="E325" t="n">
-        <v>8.507850646972656</v>
+        <v>8.50784969329834</v>
       </c>
       <c r="F325" t="n">
-        <v>-5.855995178222656</v>
+        <v>-5.855995655059814</v>
       </c>
     </row>
     <row r="326">
@@ -6948,21 +6948,21 @@
         <v>18.18915748596191</v>
       </c>
       <c r="C326" t="n">
-        <v>8.210343360900879</v>
+        <v>8.210342407226562</v>
       </c>
       <c r="D326" t="n">
         <v>35.12921905517578</v>
       </c>
       <c r="E326" t="n">
-        <v>9.886086463928223</v>
+        <v>9.886085510253906</v>
       </c>
       <c r="F326" t="n">
-        <v>-2.825040340423584</v>
+        <v>-2.825040578842163</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>-8.46353816986084</v>
+        <v>-8.463540077209473</v>
       </c>
       <c r="B327" t="n">
         <v>23.76591110229492</v>
@@ -6977,21 +6977,21 @@
         <v>12.92237186431885</v>
       </c>
       <c r="F327" t="n">
-        <v>-5.510586261749268</v>
+        <v>-5.510586738586426</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>-6.209860801696777</v>
+        <v>-6.209860324859619</v>
       </c>
       <c r="B328" t="n">
-        <v>29.22015762329102</v>
+        <v>29.22015953063965</v>
       </c>
       <c r="C328" t="n">
-        <v>-7.456207752227783</v>
+        <v>-7.456206798553467</v>
       </c>
       <c r="D328" t="n">
-        <v>34.66277694702148</v>
+        <v>34.66277313232422</v>
       </c>
       <c r="E328" t="n">
         <v>16.15936851501465</v>
@@ -7002,7 +7002,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>-3.597981691360474</v>
+        <v>-3.597980976104736</v>
       </c>
       <c r="B329" t="n">
         <v>34.4768180847168</v>
@@ -7014,7 +7014,7 @@
         <v>33.97869873046875</v>
       </c>
       <c r="E329" t="n">
-        <v>19.26612091064453</v>
+        <v>19.26612281799316</v>
       </c>
       <c r="F329" t="n">
         <v>-5.942198276519775</v>
@@ -7022,7 +7022,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>-0.597454309463501</v>
+        <v>-0.597452700138092</v>
       </c>
       <c r="B330" t="n">
         <v>39.9274787902832</v>
@@ -7042,7 +7042,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2.85665488243103</v>
+        <v>2.856654644012451</v>
       </c>
       <c r="B331" t="n">
         <v>45.81814956665039</v>
@@ -7051,18 +7051,18 @@
         <v>-15.93201923370361</v>
       </c>
       <c r="D331" t="n">
-        <v>30.52179908752441</v>
+        <v>30.52180099487305</v>
       </c>
       <c r="E331" t="n">
-        <v>21.61802291870117</v>
+        <v>21.61802101135254</v>
       </c>
       <c r="F331" t="n">
-        <v>-1.96739387512207</v>
+        <v>-1.967394113540649</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>6.671505928039551</v>
+        <v>6.671505451202393</v>
       </c>
       <c r="B332" t="n">
         <v>51.62485885620117</v>
@@ -7077,7 +7077,7 @@
         <v>20.3947639465332</v>
       </c>
       <c r="F332" t="n">
-        <v>-0.207306370139122</v>
+        <v>-0.2073061615228653</v>
       </c>
     </row>
     <row r="333">
@@ -7091,13 +7091,13 @@
         <v>-6.182998657226562</v>
       </c>
       <c r="D333" t="n">
-        <v>24.4766845703125</v>
+        <v>24.47668647766113</v>
       </c>
       <c r="E333" t="n">
         <v>18.20417785644531</v>
       </c>
       <c r="F333" t="n">
-        <v>0.9674419164657593</v>
+        <v>0.9674418568611145</v>
       </c>
     </row>
     <row r="334">
@@ -7105,7 +7105,7 @@
         <v>14.29731559753418</v>
       </c>
       <c r="B334" t="n">
-        <v>59.27574920654297</v>
+        <v>59.2757453918457</v>
       </c>
       <c r="C334" t="n">
         <v>-2.070919752120972</v>
@@ -7114,10 +7114,10 @@
         <v>21.09543228149414</v>
       </c>
       <c r="E334" t="n">
-        <v>15.60926055908203</v>
+        <v>15.60925960540771</v>
       </c>
       <c r="F334" t="n">
-        <v>1.598337531089783</v>
+        <v>1.598337650299072</v>
       </c>
     </row>
     <row r="335">
@@ -7145,13 +7145,13 @@
         <v>20.49263000488281</v>
       </c>
       <c r="B336" t="n">
-        <v>58.6508903503418</v>
+        <v>58.65088653564453</v>
       </c>
       <c r="C336" t="n">
         <v>3.050923585891724</v>
       </c>
       <c r="D336" t="n">
-        <v>14.59097671508789</v>
+        <v>14.59097766876221</v>
       </c>
       <c r="E336" t="n">
         <v>10.36567115783691</v>
@@ -7165,16 +7165,16 @@
         <v>22.85014343261719</v>
       </c>
       <c r="B337" t="n">
-        <v>55.17966079711914</v>
+        <v>55.17965698242188</v>
       </c>
       <c r="C337" t="n">
         <v>4.08879566192627</v>
       </c>
       <c r="D337" t="n">
-        <v>11.62411975860596</v>
+        <v>11.62412071228027</v>
       </c>
       <c r="E337" t="n">
-        <v>8.174694061279297</v>
+        <v>8.174695014953613</v>
       </c>
       <c r="F337" t="n">
         <v>2.490543603897095</v>
@@ -7191,13 +7191,13 @@
         <v>4.264204978942871</v>
       </c>
       <c r="D338" t="n">
-        <v>8.840458869934082</v>
+        <v>8.840459823608398</v>
       </c>
       <c r="E338" t="n">
-        <v>6.516834735870361</v>
+        <v>6.516834259033203</v>
       </c>
       <c r="F338" t="n">
-        <v>3.392050743103027</v>
+        <v>3.392050504684448</v>
       </c>
     </row>
     <row r="339">
@@ -7211,10 +7211,10 @@
         <v>3.666229009628296</v>
       </c>
       <c r="D339" t="n">
-        <v>6.159235000610352</v>
+        <v>6.159235954284668</v>
       </c>
       <c r="E339" t="n">
-        <v>5.366410732269287</v>
+        <v>5.366410255432129</v>
       </c>
       <c r="F339" t="n">
         <v>4.711570739746094</v>
@@ -7225,7 +7225,7 @@
         <v>26.42049789428711</v>
       </c>
       <c r="B340" t="n">
-        <v>34.93935012817383</v>
+        <v>34.93934631347656</v>
       </c>
       <c r="C340" t="n">
         <v>2.283150911331177</v>
@@ -7234,10 +7234,10 @@
         <v>3.46970272064209</v>
       </c>
       <c r="E340" t="n">
-        <v>4.548820018768311</v>
+        <v>4.548820495605469</v>
       </c>
       <c r="F340" t="n">
-        <v>6.238395214080811</v>
+        <v>6.238394737243652</v>
       </c>
     </row>
     <row r="341">
@@ -7251,10 +7251,10 @@
         <v>0.2739945352077484</v>
       </c>
       <c r="D341" t="n">
-        <v>0.6750707626342773</v>
+        <v>0.6750727295875549</v>
       </c>
       <c r="E341" t="n">
-        <v>3.864814281463623</v>
+        <v>3.864812612533569</v>
       </c>
       <c r="F341" t="n">
         <v>7.750905513763428</v>
@@ -7268,13 +7268,13 @@
         <v>18.49092292785645</v>
       </c>
       <c r="C342" t="n">
-        <v>-1.708052396774292</v>
+        <v>-1.708052515983582</v>
       </c>
       <c r="D342" t="n">
-        <v>-2.266818046569824</v>
+        <v>-2.266816139221191</v>
       </c>
       <c r="E342" t="n">
-        <v>3.18481969833374</v>
+        <v>3.184818029403687</v>
       </c>
       <c r="F342" t="n">
         <v>9.176568031311035</v>
@@ -7285,24 +7285,24 @@
         <v>26.05327606201172</v>
       </c>
       <c r="B343" t="n">
-        <v>11.33625602722168</v>
+        <v>11.33625507354736</v>
       </c>
       <c r="C343" t="n">
         <v>-2.777345418930054</v>
       </c>
       <c r="D343" t="n">
-        <v>-5.323195457458496</v>
+        <v>-5.323197364807129</v>
       </c>
       <c r="E343" t="n">
-        <v>2.490951061248779</v>
+        <v>2.490949392318726</v>
       </c>
       <c r="F343" t="n">
-        <v>10.55712699890137</v>
+        <v>10.55712604522705</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>25.92457580566406</v>
+        <v>25.9245777130127</v>
       </c>
       <c r="B344" t="n">
         <v>5.423089504241943</v>
@@ -7314,7 +7314,7 @@
         <v>-8.385991096496582</v>
       </c>
       <c r="E344" t="n">
-        <v>1.876876354217529</v>
+        <v>1.876876711845398</v>
       </c>
       <c r="F344" t="n">
         <v>11.85321807861328</v>
@@ -7325,19 +7325,19 @@
         <v>26.04547691345215</v>
       </c>
       <c r="B345" t="n">
-        <v>1.197556138038635</v>
+        <v>1.197557926177979</v>
       </c>
       <c r="C345" t="n">
-        <v>-1.986711502075195</v>
+        <v>-1.986711621284485</v>
       </c>
       <c r="D345" t="n">
         <v>-11.30513477325439</v>
       </c>
       <c r="E345" t="n">
-        <v>1.49354887008667</v>
+        <v>1.493549227714539</v>
       </c>
       <c r="F345" t="n">
-        <v>12.93313217163086</v>
+        <v>12.93313312530518</v>
       </c>
     </row>
     <row r="346">
@@ -7345,16 +7345,16 @@
         <v>26.34553337097168</v>
       </c>
       <c r="B346" t="n">
-        <v>-0.9006665945053101</v>
+        <v>-0.9006667733192444</v>
       </c>
       <c r="C346" t="n">
-        <v>-1.429258823394775</v>
+        <v>-1.429258942604065</v>
       </c>
       <c r="D346" t="n">
         <v>-13.93363285064697</v>
       </c>
       <c r="E346" t="n">
-        <v>1.505536556243896</v>
+        <v>1.505535006523132</v>
       </c>
       <c r="F346" t="n">
         <v>13.67775630950928</v>
@@ -7365,16 +7365,16 @@
         <v>26.6917552947998</v>
       </c>
       <c r="B347" t="n">
-        <v>-0.8145784139633179</v>
+        <v>-0.8145785927772522</v>
       </c>
       <c r="C347" t="n">
-        <v>-1.07324743270874</v>
+        <v>-1.07324755191803</v>
       </c>
       <c r="D347" t="n">
-        <v>-16.15388870239258</v>
+        <v>-16.15388679504395</v>
       </c>
       <c r="E347" t="n">
-        <v>2.072434902191162</v>
+        <v>2.072435140609741</v>
       </c>
       <c r="F347" t="n">
         <v>13.98475742340088</v>
@@ -7385,36 +7385,36 @@
         <v>27.0377368927002</v>
       </c>
       <c r="B348" t="n">
-        <v>1.11769163608551</v>
+        <v>1.117689609527588</v>
       </c>
       <c r="C348" t="n">
         <v>-1.053805947303772</v>
       </c>
       <c r="D348" t="n">
-        <v>-17.88127899169922</v>
+        <v>-17.88127708435059</v>
       </c>
       <c r="E348" t="n">
-        <v>3.321691036224365</v>
+        <v>3.321691274642944</v>
       </c>
       <c r="F348" t="n">
-        <v>13.69215393066406</v>
+        <v>13.69215297698975</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>27.41770553588867</v>
+        <v>27.4177074432373</v>
       </c>
       <c r="B349" t="n">
-        <v>4.263927936553955</v>
+        <v>4.263928890228271</v>
       </c>
       <c r="C349" t="n">
-        <v>-1.944524049758911</v>
+        <v>-1.944524168968201</v>
       </c>
       <c r="D349" t="n">
-        <v>-19.03940582275391</v>
+        <v>-19.03940391540527</v>
       </c>
       <c r="E349" t="n">
-        <v>5.328329563140869</v>
+        <v>5.328330039978027</v>
       </c>
       <c r="F349" t="n">
         <v>12.51068115234375</v>
@@ -7425,16 +7425,16 @@
         <v>27.84372138977051</v>
       </c>
       <c r="B350" t="n">
-        <v>7.858651638031006</v>
+        <v>7.858650684356689</v>
       </c>
       <c r="C350" t="n">
         <v>-4.101238250732422</v>
       </c>
       <c r="D350" t="n">
-        <v>-19.52038955688477</v>
+        <v>-19.52038764953613</v>
       </c>
       <c r="E350" t="n">
-        <v>8.130464553833008</v>
+        <v>8.130465507507324</v>
       </c>
       <c r="F350" t="n">
         <v>10.05116844177246</v>
@@ -7445,16 +7445,16 @@
         <v>28.28158950805664</v>
       </c>
       <c r="B351" t="n">
-        <v>11.53035449981689</v>
+        <v>11.53035354614258</v>
       </c>
       <c r="C351" t="n">
-        <v>-6.544770240783691</v>
+        <v>-6.54477071762085</v>
       </c>
       <c r="D351" t="n">
-        <v>-19.17511749267578</v>
+        <v>-19.17511558532715</v>
       </c>
       <c r="E351" t="n">
-        <v>11.76816558837891</v>
+        <v>11.76816463470459</v>
       </c>
       <c r="F351" t="n">
         <v>5.797392845153809</v>
@@ -7465,10 +7465,10 @@
         <v>32.18456268310547</v>
       </c>
       <c r="B352" t="n">
-        <v>0.4702287912368774</v>
+        <v>0.4702286422252655</v>
       </c>
       <c r="C352" t="n">
-        <v>-5.446859836578369</v>
+        <v>-5.446859359741211</v>
       </c>
       <c r="D352" t="n">
         <v>-4.766512870788574</v>
@@ -7482,10 +7482,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>30.90678215026855</v>
+        <v>30.90678405761719</v>
       </c>
       <c r="B353" t="n">
-        <v>1.628517746925354</v>
+        <v>1.628519535064697</v>
       </c>
       <c r="C353" t="n">
         <v>-7.153579235076904</v>
@@ -7497,7 +7497,7 @@
         <v>24.97526550292969</v>
       </c>
       <c r="F353" t="n">
-        <v>7.456566333770752</v>
+        <v>7.456565856933594</v>
       </c>
     </row>
     <row r="354">
@@ -7505,7 +7505,7 @@
         <v>29.37425804138184</v>
       </c>
       <c r="B354" t="n">
-        <v>2.633836269378662</v>
+        <v>2.633837223052979</v>
       </c>
       <c r="C354" t="n">
         <v>-7.99292516708374</v>
@@ -7528,7 +7528,7 @@
         <v>3.36967134475708</v>
       </c>
       <c r="C355" t="n">
-        <v>-7.874219417572021</v>
+        <v>-7.874218463897705</v>
       </c>
       <c r="D355" t="n">
         <v>-1.554974555969238</v>
@@ -7537,7 +7537,7 @@
         <v>35.98350524902344</v>
       </c>
       <c r="F355" t="n">
-        <v>-4.798434257507324</v>
+        <v>-4.798434734344482</v>
       </c>
     </row>
     <row r="356">
@@ -7551,7 +7551,7 @@
         <v>-7.030215740203857</v>
       </c>
       <c r="D356" t="n">
-        <v>1.124111175537109</v>
+        <v>1.124112129211426</v>
       </c>
       <c r="E356" t="n">
         <v>42.61345291137695</v>
@@ -7565,7 +7565,7 @@
         <v>23.2596549987793</v>
       </c>
       <c r="B357" t="n">
-        <v>3.348803997039795</v>
+        <v>3.348804950714111</v>
       </c>
       <c r="C357" t="n">
         <v>-5.898867130279541</v>
@@ -7585,13 +7585,13 @@
         <v>20.79283332824707</v>
       </c>
       <c r="B358" t="n">
-        <v>2.588545322418213</v>
+        <v>2.588546276092529</v>
       </c>
       <c r="C358" t="n">
         <v>-4.782667636871338</v>
       </c>
       <c r="D358" t="n">
-        <v>8.314407348632812</v>
+        <v>8.314406394958496</v>
       </c>
       <c r="E358" t="n">
         <v>55.83676528930664</v>
@@ -7605,19 +7605,19 @@
         <v>18.25476455688477</v>
       </c>
       <c r="B359" t="n">
-        <v>1.52885115146637</v>
+        <v>1.52885103225708</v>
       </c>
       <c r="C359" t="n">
-        <v>-3.806578159332275</v>
+        <v>-3.806577682495117</v>
       </c>
       <c r="D359" t="n">
-        <v>12.33372211456299</v>
+        <v>12.3337230682373</v>
       </c>
       <c r="E359" t="n">
         <v>60.83515930175781</v>
       </c>
       <c r="F359" t="n">
-        <v>-13.25527000427246</v>
+        <v>-13.25526905059814</v>
       </c>
     </row>
     <row r="360">
@@ -7625,16 +7625,16 @@
         <v>15.75786018371582</v>
       </c>
       <c r="B360" t="n">
-        <v>0.4145323038101196</v>
+        <v>0.4145340621471405</v>
       </c>
       <c r="C360" t="n">
-        <v>-2.917726278305054</v>
+        <v>-2.917726039886475</v>
       </c>
       <c r="D360" t="n">
         <v>16.28795433044434</v>
       </c>
       <c r="E360" t="n">
-        <v>63.94037246704102</v>
+        <v>63.94036865234375</v>
       </c>
       <c r="F360" t="n">
         <v>-9.02980899810791</v>
@@ -7642,13 +7642,13 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>13.39148044586182</v>
+        <v>13.3914794921875</v>
       </c>
       <c r="B361" t="n">
-        <v>-0.5524476766586304</v>
+        <v>-0.5524478554725647</v>
       </c>
       <c r="C361" t="n">
-        <v>-1.998679399490356</v>
+        <v>-1.998679280281067</v>
       </c>
       <c r="D361" t="n">
         <v>19.99280166625977</v>
@@ -7665,39 +7665,39 @@
         <v>11.22716903686523</v>
       </c>
       <c r="B362" t="n">
-        <v>-1.225449919700623</v>
+        <v>-1.225450038909912</v>
       </c>
       <c r="C362" t="n">
-        <v>-0.9531592726707458</v>
+        <v>-0.9531592130661011</v>
       </c>
       <c r="D362" t="n">
         <v>23.31063270568848</v>
       </c>
       <c r="E362" t="n">
-        <v>63.98999786376953</v>
+        <v>63.98999404907227</v>
       </c>
       <c r="F362" t="n">
-        <v>-0.2534465789794922</v>
+        <v>-0.2534463405609131</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>9.282947540283203</v>
+        <v>9.282946586608887</v>
       </c>
       <c r="B363" t="n">
-        <v>-1.564141631126404</v>
+        <v>-1.564139842987061</v>
       </c>
       <c r="C363" t="n">
-        <v>0.2429277449846268</v>
+        <v>0.242927759885788</v>
       </c>
       <c r="D363" t="n">
-        <v>26.17411613464355</v>
+        <v>26.17411804199219</v>
       </c>
       <c r="E363" t="n">
-        <v>61.12539672851562</v>
+        <v>61.12539291381836</v>
       </c>
       <c r="F363" t="n">
-        <v>3.173304319381714</v>
+        <v>3.173304080963135</v>
       </c>
     </row>
     <row r="364">
@@ -7705,7 +7705,7 @@
         <v>7.528273105621338</v>
       </c>
       <c r="B364" t="n">
-        <v>-1.60957658290863</v>
+        <v>-1.60957670211792</v>
       </c>
       <c r="C364" t="n">
         <v>1.563114523887634</v>
@@ -7714,7 +7714,7 @@
         <v>28.53836441040039</v>
       </c>
       <c r="E364" t="n">
-        <v>56.63148880004883</v>
+        <v>56.63148498535156</v>
       </c>
       <c r="F364" t="n">
         <v>5.678918361663818</v>
@@ -7722,16 +7722,16 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>5.913900375366211</v>
+        <v>5.913900852203369</v>
       </c>
       <c r="B365" t="n">
-        <v>-1.425002455711365</v>
+        <v>-1.425002574920654</v>
       </c>
       <c r="C365" t="n">
         <v>2.978968143463135</v>
       </c>
       <c r="D365" t="n">
-        <v>30.33066749572754</v>
+        <v>30.33066940307617</v>
       </c>
       <c r="E365" t="n">
         <v>50.65621185302734</v>
@@ -7742,36 +7742,36 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>4.38072681427002</v>
+        <v>4.380726337432861</v>
       </c>
       <c r="B366" t="n">
-        <v>-1.092339873313904</v>
+        <v>-1.092338085174561</v>
       </c>
       <c r="C366" t="n">
         <v>4.459642887115479</v>
       </c>
       <c r="D366" t="n">
-        <v>31.5382194519043</v>
+        <v>31.53822135925293</v>
       </c>
       <c r="E366" t="n">
         <v>43.55517959594727</v>
       </c>
       <c r="F366" t="n">
-        <v>7.576860427856445</v>
+        <v>7.576859474182129</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>2.881196737289429</v>
+        <v>2.88119649887085</v>
       </c>
       <c r="B367" t="n">
-        <v>-0.6992944478988647</v>
+        <v>-0.6992946267127991</v>
       </c>
       <c r="C367" t="n">
-        <v>5.957253456115723</v>
+        <v>5.957253932952881</v>
       </c>
       <c r="D367" t="n">
-        <v>32.17497253417969</v>
+        <v>32.17497634887695</v>
       </c>
       <c r="E367" t="n">
         <v>35.74450302124023</v>
@@ -7782,30 +7782,30 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1.387698888778687</v>
+        <v>1.387698650360107</v>
       </c>
       <c r="B368" t="n">
-        <v>-0.3274492025375366</v>
+        <v>-0.3274493515491486</v>
       </c>
       <c r="C368" t="n">
-        <v>7.401836395263672</v>
+        <v>7.40183687210083</v>
       </c>
       <c r="D368" t="n">
         <v>32.27909851074219</v>
       </c>
       <c r="E368" t="n">
-        <v>27.66982269287109</v>
+        <v>27.66982078552246</v>
       </c>
       <c r="F368" t="n">
-        <v>5.788424491882324</v>
+        <v>5.788424015045166</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>-0.09775374084711075</v>
+        <v>-0.09775307774543762</v>
       </c>
       <c r="B369" t="n">
-        <v>-0.01871622540056705</v>
+        <v>-0.01871637813746929</v>
       </c>
       <c r="C369" t="n">
         <v>8.734431266784668</v>
@@ -7814,18 +7814,18 @@
         <v>32.00242233276367</v>
       </c>
       <c r="E369" t="n">
-        <v>19.82099723815918</v>
+        <v>19.82099533081055</v>
       </c>
       <c r="F369" t="n">
-        <v>4.218388557434082</v>
+        <v>4.218388080596924</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>-1.537333726882935</v>
+        <v>-1.537333011627197</v>
       </c>
       <c r="B370" t="n">
-        <v>0.2691351175308228</v>
+        <v>0.2691349685192108</v>
       </c>
       <c r="C370" t="n">
         <v>9.943787574768066</v>
@@ -7837,15 +7837,15 @@
         <v>12.7351713180542</v>
       </c>
       <c r="F370" t="n">
-        <v>2.890978336334229</v>
+        <v>2.890978097915649</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>-2.87389874458313</v>
+        <v>-2.873898029327393</v>
       </c>
       <c r="B371" t="n">
-        <v>0.6441751718521118</v>
+        <v>0.6441749930381775</v>
       </c>
       <c r="C371" t="n">
         <v>11.02846813201904</v>
@@ -7854,7 +7854,7 @@
         <v>30.99393463134766</v>
       </c>
       <c r="E371" t="n">
-        <v>7.153585910797119</v>
+        <v>7.153587341308594</v>
       </c>
       <c r="F371" t="n">
         <v>2.219315767288208</v>
@@ -7862,10 +7862,10 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>-4.061036109924316</v>
+        <v>-4.061039447784424</v>
       </c>
       <c r="B372" t="n">
-        <v>1.240339875221252</v>
+        <v>1.240339756011963</v>
       </c>
       <c r="C372" t="n">
         <v>11.96594429016113</v>
@@ -7874,7 +7874,7 @@
         <v>30.56024932861328</v>
       </c>
       <c r="E372" t="n">
-        <v>3.567990779876709</v>
+        <v>3.567991018295288</v>
       </c>
       <c r="F372" t="n">
         <v>2.097066164016724</v>
@@ -7882,10 +7882,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>-5.103541374206543</v>
+        <v>-5.103540897369385</v>
       </c>
       <c r="B373" t="n">
-        <v>2.135076999664307</v>
+        <v>2.135078907012939</v>
       </c>
       <c r="C373" t="n">
         <v>12.72584915161133</v>
@@ -7894,7 +7894,7 @@
         <v>30.24405097961426</v>
       </c>
       <c r="E373" t="n">
-        <v>2.108869075775146</v>
+        <v>2.108869314193726</v>
       </c>
       <c r="F373" t="n">
         <v>2.046056747436523</v>
@@ -7902,7 +7902,7 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>-6.03299617767334</v>
+        <v>-6.032995700836182</v>
       </c>
       <c r="B374" t="n">
         <v>3.360687732696533</v>
@@ -7911,10 +7911,10 @@
         <v>13.26511192321777</v>
       </c>
       <c r="D374" t="n">
-        <v>29.98687362670898</v>
+        <v>29.98687553405762</v>
       </c>
       <c r="E374" t="n">
-        <v>2.479588985443115</v>
+        <v>2.479589223861694</v>
       </c>
       <c r="F374" t="n">
         <v>1.349458336830139</v>
@@ -7922,7 +7922,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>-6.888833045959473</v>
+        <v>-6.888832569122314</v>
       </c>
       <c r="B375" t="n">
         <v>4.920792102813721</v>
@@ -7934,15 +7934,15 @@
         <v>29.67742347717285</v>
       </c>
       <c r="E375" t="n">
-        <v>3.815743923187256</v>
+        <v>3.815744161605835</v>
       </c>
       <c r="F375" t="n">
-        <v>-0.4979972839355469</v>
+        <v>-0.4979970455169678</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>-7.680294990539551</v>
+        <v>-7.680296421051025</v>
       </c>
       <c r="B376" t="n">
         <v>6.797675609588623</v>
@@ -7954,10 +7954,10 @@
         <v>29.22984886169434</v>
       </c>
       <c r="E376" t="n">
-        <v>5.452352046966553</v>
+        <v>5.452352523803711</v>
       </c>
       <c r="F376" t="n">
-        <v>-3.368998050689697</v>
+        <v>-3.368997812271118</v>
       </c>
     </row>
     <row r="377">
@@ -7965,7 +7965,7 @@
         <v>-8.333846092224121</v>
       </c>
       <c r="B377" t="n">
-        <v>9.057035446166992</v>
+        <v>9.057034492492676</v>
       </c>
       <c r="C377" t="n">
         <v>12.34715557098389</v>
@@ -7974,10 +7974,10 @@
         <v>32.72652816772461</v>
       </c>
       <c r="E377" t="n">
-        <v>3.954198360443115</v>
+        <v>3.954198598861694</v>
       </c>
       <c r="F377" t="n">
-        <v>-2.018710613250732</v>
+        <v>-2.018710374832153</v>
       </c>
     </row>
     <row r="378">
@@ -7985,24 +7985,24 @@
         <v>-8.65126895904541</v>
       </c>
       <c r="B378" t="n">
-        <v>11.8926362991333</v>
+        <v>11.89263534545898</v>
       </c>
       <c r="C378" t="n">
         <v>10.21060657501221</v>
       </c>
       <c r="D378" t="n">
-        <v>31.99587631225586</v>
+        <v>31.99587821960449</v>
       </c>
       <c r="E378" t="n">
-        <v>5.740691661834717</v>
+        <v>5.740692138671875</v>
       </c>
       <c r="F378" t="n">
-        <v>-4.987510681152344</v>
+        <v>-4.987511157989502</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>-8.401886940002441</v>
+        <v>-8.401888847351074</v>
       </c>
       <c r="B379" t="n">
         <v>15.4909029006958</v>
@@ -8014,7 +8014,7 @@
         <v>31.12182998657227</v>
       </c>
       <c r="E379" t="n">
-        <v>7.645551204681396</v>
+        <v>7.645550727844238</v>
       </c>
       <c r="F379" t="n">
         <v>-6.828047752380371</v>
@@ -8022,7 +8022,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>-7.352435111999512</v>
+        <v>-7.352436542510986</v>
       </c>
       <c r="B380" t="n">
         <v>20.05574989318848</v>
@@ -8042,16 +8042,16 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>-5.302992820739746</v>
+        <v>-5.302992343902588</v>
       </c>
       <c r="B381" t="n">
         <v>25.77397155761719</v>
       </c>
       <c r="C381" t="n">
-        <v>-5.712520599365234</v>
+        <v>-5.712520122528076</v>
       </c>
       <c r="D381" t="n">
-        <v>28.63880729675293</v>
+        <v>28.63880920410156</v>
       </c>
       <c r="E381" t="n">
         <v>10.726806640625</v>
@@ -8062,33 +8062,33 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>-2.29651951789856</v>
+        <v>-2.296520709991455</v>
       </c>
       <c r="B382" t="n">
         <v>32.53843688964844</v>
       </c>
       <c r="C382" t="n">
-        <v>-12.52554321289062</v>
+        <v>-12.52554225921631</v>
       </c>
       <c r="D382" t="n">
-        <v>26.89430809020996</v>
+        <v>26.89430999755859</v>
       </c>
       <c r="E382" t="n">
         <v>11.35634899139404</v>
       </c>
       <c r="F382" t="n">
-        <v>-3.928468227386475</v>
+        <v>-3.928467988967896</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1.51532244682312</v>
+        <v>1.515322208404541</v>
       </c>
       <c r="B383" t="n">
         <v>40.00061416625977</v>
       </c>
       <c r="C383" t="n">
-        <v>-17.64094734191895</v>
+        <v>-17.64094924926758</v>
       </c>
       <c r="D383" t="n">
         <v>24.83669471740723</v>
@@ -8097,12 +8097,12 @@
         <v>11.24954319000244</v>
       </c>
       <c r="F383" t="n">
-        <v>-2.108511447906494</v>
+        <v>-2.108511686325073</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>5.889498710632324</v>
+        <v>5.889498233795166</v>
       </c>
       <c r="B384" t="n">
         <v>47.47826385498047</v>
@@ -8125,19 +8125,19 @@
         <v>10.48462867736816</v>
       </c>
       <c r="B385" t="n">
-        <v>54.09918594360352</v>
+        <v>54.09918212890625</v>
       </c>
       <c r="C385" t="n">
-        <v>-17.9802303314209</v>
+        <v>-17.98023223876953</v>
       </c>
       <c r="D385" t="n">
-        <v>20.17119979858398</v>
+        <v>20.17120170593262</v>
       </c>
       <c r="E385" t="n">
-        <v>9.335122108459473</v>
+        <v>9.335121154785156</v>
       </c>
       <c r="F385" t="n">
-        <v>0.5427778959274292</v>
+        <v>0.5427780151367188</v>
       </c>
     </row>
     <row r="386">
@@ -8145,16 +8145,16 @@
         <v>15.02622032165527</v>
       </c>
       <c r="B386" t="n">
-        <v>59.16971206665039</v>
+        <v>59.16970825195312</v>
       </c>
       <c r="C386" t="n">
-        <v>-14.09178447723389</v>
+        <v>-14.0917854309082</v>
       </c>
       <c r="D386" t="n">
         <v>17.78373146057129</v>
       </c>
       <c r="E386" t="n">
-        <v>7.976321697235107</v>
+        <v>7.976322174072266</v>
       </c>
       <c r="F386" t="n">
         <v>1.485339164733887</v>
@@ -8165,16 +8165,16 @@
         <v>19.31408309936523</v>
       </c>
       <c r="B387" t="n">
-        <v>62.22658538818359</v>
+        <v>62.22658157348633</v>
       </c>
       <c r="C387" t="n">
-        <v>-9.21835994720459</v>
+        <v>-9.218358993530273</v>
       </c>
       <c r="D387" t="n">
         <v>15.4851770401001</v>
       </c>
       <c r="E387" t="n">
-        <v>6.659142017364502</v>
+        <v>6.65914249420166</v>
       </c>
       <c r="F387" t="n">
         <v>2.330123901367188</v>
@@ -8194,7 +8194,7 @@
         <v>13.34041690826416</v>
       </c>
       <c r="E388" t="n">
-        <v>5.584938526153564</v>
+        <v>5.58493709564209</v>
       </c>
       <c r="F388" t="n">
         <v>3.182194709777832</v>
@@ -8205,16 +8205,16 @@
         <v>26.69367599487305</v>
       </c>
       <c r="B389" t="n">
-        <v>62.29938125610352</v>
+        <v>62.29937744140625</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.4982364475727081</v>
+        <v>-0.4982365071773529</v>
       </c>
       <c r="D389" t="n">
         <v>11.38720321655273</v>
       </c>
       <c r="E389" t="n">
-        <v>4.879885196685791</v>
+        <v>4.879885673522949</v>
       </c>
       <c r="F389" t="n">
         <v>4.125606536865234</v>
@@ -8225,7 +8225,7 @@
         <v>29.6345100402832</v>
       </c>
       <c r="B390" t="n">
-        <v>59.57680892944336</v>
+        <v>59.57680511474609</v>
       </c>
       <c r="C390" t="n">
         <v>2.575315952301025</v>
@@ -8234,10 +8234,10 @@
         <v>9.631290435791016</v>
       </c>
       <c r="E390" t="n">
-        <v>4.592555522918701</v>
+        <v>4.592556953430176</v>
       </c>
       <c r="F390" t="n">
-        <v>5.233341217041016</v>
+        <v>5.233340740203857</v>
       </c>
     </row>
     <row r="391">
@@ -8254,7 +8254,7 @@
         <v>8.033862113952637</v>
       </c>
       <c r="E391" t="n">
-        <v>4.663746356964111</v>
+        <v>4.66374683380127</v>
       </c>
       <c r="F391" t="n">
         <v>6.500419616699219</v>
@@ -8262,7 +8262,7 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>33.74184036254883</v>
+        <v>33.74184417724609</v>
       </c>
       <c r="B392" t="n">
         <v>49.56372451782227</v>
@@ -8274,7 +8274,7 @@
         <v>6.547124862670898</v>
       </c>
       <c r="E392" t="n">
-        <v>5.00180196762085</v>
+        <v>5.001801490783691</v>
       </c>
       <c r="F392" t="n">
         <v>7.846288681030273</v>
@@ -8288,13 +8288,13 @@
         <v>42.72377777099609</v>
       </c>
       <c r="C393" t="n">
-        <v>6.306887626647949</v>
+        <v>6.306888103485107</v>
       </c>
       <c r="D393" t="n">
-        <v>5.113340377807617</v>
+        <v>5.113339424133301</v>
       </c>
       <c r="E393" t="n">
-        <v>5.475825786590576</v>
+        <v>5.475825309753418</v>
       </c>
       <c r="F393" t="n">
         <v>9.15485954284668</v>
@@ -8314,7 +8314,7 @@
         <v>3.693695068359375</v>
       </c>
       <c r="E394" t="n">
-        <v>5.973424434661865</v>
+        <v>5.973424911499023</v>
       </c>
       <c r="F394" t="n">
         <v>10.35428142547607</v>
@@ -8322,22 +8322,22 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>35.24254608154297</v>
+        <v>35.24254989624023</v>
       </c>
       <c r="B395" t="n">
         <v>26.83361053466797</v>
       </c>
       <c r="C395" t="n">
-        <v>4.673952579498291</v>
+        <v>4.673953056335449</v>
       </c>
       <c r="D395" t="n">
         <v>2.295432090759277</v>
       </c>
       <c r="E395" t="n">
-        <v>6.470982074737549</v>
+        <v>6.470980644226074</v>
       </c>
       <c r="F395" t="n">
-        <v>11.41268062591553</v>
+        <v>11.41267967224121</v>
       </c>
     </row>
     <row r="396">
@@ -8348,41 +8348,41 @@
         <v>18.53747749328613</v>
       </c>
       <c r="C396" t="n">
-        <v>3.561429977416992</v>
+        <v>3.561429738998413</v>
       </c>
       <c r="D396" t="n">
-        <v>0.9632272720336914</v>
+        <v>0.9632273316383362</v>
       </c>
       <c r="E396" t="n">
-        <v>7.037947177886963</v>
+        <v>7.037947654724121</v>
       </c>
       <c r="F396" t="n">
-        <v>12.31132316589355</v>
+        <v>12.31132411956787</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>34.10771179199219</v>
+        <v>34.10770797729492</v>
       </c>
       <c r="B397" t="n">
         <v>10.68671321868896</v>
       </c>
       <c r="C397" t="n">
-        <v>2.868483781814575</v>
+        <v>2.868484020233154</v>
       </c>
       <c r="D397" t="n">
-        <v>-0.2601118087768555</v>
+        <v>-0.2601136565208435</v>
       </c>
       <c r="E397" t="n">
-        <v>7.784332752227783</v>
+        <v>7.784333229064941</v>
       </c>
       <c r="F397" t="n">
-        <v>13.04566955566406</v>
+        <v>13.04567050933838</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>33.40517425537109</v>
+        <v>33.40517044067383</v>
       </c>
       <c r="B398" t="n">
         <v>4.010454654693604</v>
@@ -8405,7 +8405,7 @@
         <v>32.80168151855469</v>
       </c>
       <c r="B399" t="n">
-        <v>-0.6952069997787476</v>
+        <v>-0.6952090859413147</v>
       </c>
       <c r="C399" t="n">
         <v>2.392953872680664</v>
@@ -8448,10 +8448,10 @@
         <v>-2.635667324066162</v>
       </c>
       <c r="C401" t="n">
-        <v>-0.2177453488111496</v>
+        <v>-0.2177453935146332</v>
       </c>
       <c r="D401" t="n">
-        <v>-3.965996742248535</v>
+        <v>-3.965994834899902</v>
       </c>
       <c r="E401" t="n">
         <v>14.34756755828857</v>

--- a/Predictions/timestamp_rolling_gt_next_tick.xlsx
+++ b/Predictions/timestamp_rolling_gt_next_tick.xlsx
@@ -465,16 +465,16 @@
         <v>21.44140625</v>
       </c>
       <c r="B2" t="n">
-        <v>6.114814281463623</v>
+        <v>6.114813804626465</v>
       </c>
       <c r="C2" t="n">
-        <v>1.687668561935425</v>
+        <v>1.687668919563293</v>
       </c>
       <c r="D2" t="n">
         <v>16.07298469543457</v>
       </c>
       <c r="E2" t="n">
-        <v>55.25887680053711</v>
+        <v>55.25888061523438</v>
       </c>
       <c r="F2" t="n">
         <v>-4.423366069793701</v>
@@ -485,7 +485,7 @@
         <v>19.59602355957031</v>
       </c>
       <c r="B3" t="n">
-        <v>5.919833660125732</v>
+        <v>5.919834136962891</v>
       </c>
       <c r="C3" t="n">
         <v>2.981911897659302</v>
@@ -497,7 +497,7 @@
         <v>55.29248809814453</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.138886451721191</v>
+        <v>-1.138886570930481</v>
       </c>
     </row>
     <row r="4">
@@ -505,7 +505,7 @@
         <v>17.61653137207031</v>
       </c>
       <c r="B4" t="n">
-        <v>5.380170345306396</v>
+        <v>5.380170822143555</v>
       </c>
       <c r="C4" t="n">
         <v>3.968274831771851</v>
@@ -514,7 +514,7 @@
         <v>21.68654823303223</v>
       </c>
       <c r="E4" t="n">
-        <v>53.64463424682617</v>
+        <v>53.64463806152344</v>
       </c>
       <c r="F4" t="n">
         <v>2.17330527305603</v>
@@ -525,7 +525,7 @@
         <v>15.56411743164062</v>
       </c>
       <c r="B5" t="n">
-        <v>4.591304302215576</v>
+        <v>4.591303825378418</v>
       </c>
       <c r="C5" t="n">
         <v>4.773709297180176</v>
@@ -534,7 +534,7 @@
         <v>24.04980278015137</v>
       </c>
       <c r="E5" t="n">
-        <v>50.50603866577148</v>
+        <v>50.50604248046875</v>
       </c>
       <c r="F5" t="n">
         <v>4.971277236938477</v>
@@ -545,19 +545,19 @@
         <v>13.49853134155273</v>
       </c>
       <c r="B6" t="n">
-        <v>3.635779857635498</v>
+        <v>3.635779619216919</v>
       </c>
       <c r="C6" t="n">
-        <v>5.48799991607666</v>
+        <v>5.487999439239502</v>
       </c>
       <c r="D6" t="n">
-        <v>26.14765167236328</v>
+        <v>26.14764976501465</v>
       </c>
       <c r="E6" t="n">
-        <v>46.0722541809082</v>
+        <v>46.07225799560547</v>
       </c>
       <c r="F6" t="n">
-        <v>6.949480533599854</v>
+        <v>6.949481010437012</v>
       </c>
     </row>
     <row r="7">
@@ -565,16 +565,16 @@
         <v>11.46507358551025</v>
       </c>
       <c r="B7" t="n">
-        <v>2.587292194366455</v>
+        <v>2.587292671203613</v>
       </c>
       <c r="C7" t="n">
-        <v>6.158910751342773</v>
+        <v>6.158911228179932</v>
       </c>
       <c r="D7" t="n">
-        <v>27.96586418151855</v>
+        <v>27.96586608886719</v>
       </c>
       <c r="E7" t="n">
-        <v>40.49611663818359</v>
+        <v>40.49612045288086</v>
       </c>
       <c r="F7" t="n">
         <v>8.029861450195312</v>
@@ -585,7 +585,7 @@
         <v>9.480586051940918</v>
       </c>
       <c r="B8" t="n">
-        <v>1.515554904937744</v>
+        <v>1.515554547309875</v>
       </c>
       <c r="C8" t="n">
         <v>6.814531803131104</v>
@@ -594,7 +594,7 @@
         <v>29.4472770690918</v>
       </c>
       <c r="E8" t="n">
-        <v>33.95809173583984</v>
+        <v>33.95809555053711</v>
       </c>
       <c r="F8" t="n">
         <v>8.267264366149902</v>
@@ -602,16 +602,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7.545021057128906</v>
+        <v>7.545021533966064</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4990276992321014</v>
+        <v>0.4990287721157074</v>
       </c>
       <c r="C9" t="n">
-        <v>7.496321678161621</v>
+        <v>7.496322154998779</v>
       </c>
       <c r="D9" t="n">
-        <v>30.52943992614746</v>
+        <v>30.52943801879883</v>
       </c>
       <c r="E9" t="n">
         <v>26.73877334594727</v>
@@ -622,10 +622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5.665896892547607</v>
+        <v>5.665897369384766</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.3710818588733673</v>
+        <v>-0.3710817396640778</v>
       </c>
       <c r="C10" t="n">
         <v>8.258571624755859</v>
@@ -642,16 +642,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3.868793964385986</v>
+        <v>3.868793249130249</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.9978709816932678</v>
+        <v>-0.9978703260421753</v>
       </c>
       <c r="C11" t="n">
         <v>9.133468627929688</v>
       </c>
       <c r="D11" t="n">
-        <v>31.4458179473877</v>
+        <v>31.44581604003906</v>
       </c>
       <c r="E11" t="n">
         <v>11.62716579437256</v>
@@ -662,19 +662,19 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2.187931537628174</v>
+        <v>2.187931776046753</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.318831920623779</v>
+        <v>-1.318832278251648</v>
       </c>
       <c r="C12" t="n">
-        <v>10.08470821380615</v>
+        <v>10.08470916748047</v>
       </c>
       <c r="D12" t="n">
         <v>31.3984489440918</v>
       </c>
       <c r="E12" t="n">
-        <v>4.618947982788086</v>
+        <v>4.618947505950928</v>
       </c>
       <c r="F12" t="n">
         <v>4.522222995758057</v>
@@ -682,10 +682,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.6507658362388611</v>
+        <v>0.650766134262085</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.312886714935303</v>
+        <v>-1.312887072563171</v>
       </c>
       <c r="C13" t="n">
         <v>11.02143955230713</v>
@@ -694,7 +694,7 @@
         <v>31.20336723327637</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.256487011909485</v>
+        <v>-1.2564857006073</v>
       </c>
       <c r="F13" t="n">
         <v>4.039758205413818</v>
@@ -702,39 +702,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.7364144921302795</v>
+        <v>-0.7364132404327393</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.9886603951454163</v>
+        <v>-0.9886616468429565</v>
       </c>
       <c r="C14" t="n">
-        <v>11.8317928314209</v>
+        <v>11.83179378509521</v>
       </c>
       <c r="D14" t="n">
-        <v>30.99928665161133</v>
+        <v>30.9992847442627</v>
       </c>
       <c r="E14" t="n">
         <v>-5.457664489746094</v>
       </c>
       <c r="F14" t="n">
-        <v>4.073397636413574</v>
+        <v>4.073398113250732</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-1.997194766998291</v>
+        <v>-1.997194528579712</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.3740153610706329</v>
+        <v>-0.3740171492099762</v>
       </c>
       <c r="C15" t="n">
-        <v>12.39922714233398</v>
+        <v>12.3992280960083</v>
       </c>
       <c r="D15" t="n">
         <v>30.85886573791504</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.632524490356445</v>
+        <v>-7.632525444030762</v>
       </c>
       <c r="F15" t="n">
         <v>4.258270263671875</v>
@@ -742,19 +742,19 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-3.188065052032471</v>
+        <v>-3.188065767288208</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4734825789928436</v>
+        <v>0.473482221364975</v>
       </c>
       <c r="C16" t="n">
-        <v>12.64423179626465</v>
+        <v>12.64423274993896</v>
       </c>
       <c r="D16" t="n">
         <v>30.77327919006348</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.682722091674805</v>
+        <v>-7.682721614837646</v>
       </c>
       <c r="F16" t="n">
         <v>4.103097915649414</v>
@@ -762,33 +762,33 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-4.351274967193604</v>
+        <v>-4.351275444030762</v>
       </c>
       <c r="B17" t="n">
-        <v>1.528610706329346</v>
+        <v>1.528610825538635</v>
       </c>
       <c r="C17" t="n">
-        <v>12.49044704437256</v>
+        <v>12.49044799804688</v>
       </c>
       <c r="D17" t="n">
         <v>30.66972923278809</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.047765731811523</v>
+        <v>-6.047765254974365</v>
       </c>
       <c r="F17" t="n">
-        <v>3.160023212432861</v>
+        <v>3.16002345085144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-5.475904941558838</v>
+        <v>-5.475905418395996</v>
       </c>
       <c r="B18" t="n">
-        <v>2.834546566009521</v>
+        <v>2.834545612335205</v>
       </c>
       <c r="C18" t="n">
-        <v>11.8119592666626</v>
+        <v>11.81196022033691</v>
       </c>
       <c r="D18" t="n">
         <v>30.48380851745605</v>
@@ -802,39 +802,39 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-6.448917865753174</v>
+        <v>-6.448916435241699</v>
       </c>
       <c r="B19" t="n">
-        <v>4.556564807891846</v>
+        <v>4.556563854217529</v>
       </c>
       <c r="C19" t="n">
-        <v>10.3313102722168</v>
+        <v>10.33131122589111</v>
       </c>
       <c r="D19" t="n">
         <v>30.19507789611816</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06810939311981201</v>
+        <v>0.06810806691646576</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.259037256240845</v>
+        <v>-1.259037375450134</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-7.070194721221924</v>
+        <v>-7.070195198059082</v>
       </c>
       <c r="B20" t="n">
-        <v>6.916428089141846</v>
+        <v>6.916427612304688</v>
       </c>
       <c r="C20" t="n">
-        <v>7.71525764465332</v>
+        <v>7.715258121490479</v>
       </c>
       <c r="D20" t="n">
         <v>33.21461486816406</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9901658296585083</v>
+        <v>-0.9901650547981262</v>
       </c>
       <c r="F20" t="n">
         <v>1.466728448867798</v>
@@ -842,76 +842,76 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-7.093594074249268</v>
+        <v>-7.093592643737793</v>
       </c>
       <c r="B21" t="n">
-        <v>10.16660022735596</v>
+        <v>10.16660118103027</v>
       </c>
       <c r="C21" t="n">
-        <v>3.634465217590332</v>
+        <v>3.634465456008911</v>
       </c>
       <c r="D21" t="n">
         <v>32.7855110168457</v>
       </c>
       <c r="E21" t="n">
-        <v>2.011201620101929</v>
+        <v>2.011200666427612</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8537766933441162</v>
+        <v>-0.8537765145301819</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-6.299343585968018</v>
+        <v>-6.299344062805176</v>
       </c>
       <c r="B22" t="n">
         <v>14.49208736419678</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.859313368797302</v>
+        <v>-1.859313249588013</v>
       </c>
       <c r="D22" t="n">
         <v>32.17982864379883</v>
       </c>
       <c r="E22" t="n">
-        <v>4.955769538879395</v>
+        <v>4.955769062042236</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.485605001449585</v>
+        <v>-2.485605239868164</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-4.545923709869385</v>
+        <v>-4.545924186706543</v>
       </c>
       <c r="B23" t="n">
-        <v>19.91064834594727</v>
+        <v>19.9106502532959</v>
       </c>
       <c r="C23" t="n">
-        <v>-7.802365779876709</v>
+        <v>-7.802366256713867</v>
       </c>
       <c r="D23" t="n">
-        <v>31.4056224822998</v>
+        <v>31.40562057495117</v>
       </c>
       <c r="E23" t="n">
         <v>7.610507965087891</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.90172553062439</v>
+        <v>-2.901725769042969</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-1.95525598526001</v>
+        <v>-1.955256700515747</v>
       </c>
       <c r="B24" t="n">
-        <v>25.99744606018066</v>
+        <v>25.9974479675293</v>
       </c>
       <c r="C24" t="n">
         <v>-12.45679378509521</v>
       </c>
       <c r="D24" t="n">
-        <v>30.44404602050781</v>
+        <v>30.44404411315918</v>
       </c>
       <c r="E24" t="n">
         <v>9.75511360168457</v>
@@ -922,13 +922,13 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1.239973545074463</v>
+        <v>1.239973783493042</v>
       </c>
       <c r="B25" t="n">
         <v>32.04457092285156</v>
       </c>
       <c r="C25" t="n">
-        <v>-14.512770652771</v>
+        <v>-14.51277160644531</v>
       </c>
       <c r="D25" t="n">
         <v>29.25117301940918</v>
@@ -937,7 +937,7 @@
         <v>11.19117546081543</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4943320751190186</v>
+        <v>-0.4943321347236633</v>
       </c>
     </row>
     <row r="26">
@@ -945,16 +945,16 @@
         <v>4.734203815460205</v>
       </c>
       <c r="B26" t="n">
-        <v>37.17813110351562</v>
+        <v>37.17812728881836</v>
       </c>
       <c r="C26" t="n">
         <v>-13.66947078704834</v>
       </c>
       <c r="D26" t="n">
-        <v>27.81206893920898</v>
+        <v>27.81206703186035</v>
       </c>
       <c r="E26" t="n">
-        <v>11.90242004394531</v>
+        <v>11.902419090271</v>
       </c>
       <c r="F26" t="n">
         <v>1.313478827476501</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>8.234172821044922</v>
+        <v>8.234173774719238</v>
       </c>
       <c r="B27" t="n">
         <v>40.62228775024414</v>
@@ -977,7 +977,7 @@
         <v>12.00064373016357</v>
       </c>
       <c r="F27" t="n">
-        <v>2.994666814804077</v>
+        <v>2.994667053222656</v>
       </c>
     </row>
     <row r="28">
@@ -994,7 +994,7 @@
         <v>24.27787208557129</v>
       </c>
       <c r="E28" t="n">
-        <v>11.66229724884033</v>
+        <v>11.66229629516602</v>
       </c>
       <c r="F28" t="n">
         <v>4.432877063751221</v>
@@ -1025,7 +1025,7 @@
         <v>17.20433235168457</v>
       </c>
       <c r="B30" t="n">
-        <v>39.36635208129883</v>
+        <v>39.36634826660156</v>
       </c>
       <c r="C30" t="n">
         <v>1.327176213264465</v>
@@ -1037,27 +1037,27 @@
         <v>10.20353412628174</v>
       </c>
       <c r="F30" t="n">
-        <v>6.585166454315186</v>
+        <v>6.585166931152344</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>19.48697662353516</v>
+        <v>19.48697853088379</v>
       </c>
       <c r="B31" t="n">
         <v>35.61741256713867</v>
       </c>
       <c r="C31" t="n">
-        <v>3.879587650299072</v>
+        <v>3.879587411880493</v>
       </c>
       <c r="D31" t="n">
         <v>18.11552810668945</v>
       </c>
       <c r="E31" t="n">
-        <v>9.274946212768555</v>
+        <v>9.274945259094238</v>
       </c>
       <c r="F31" t="n">
-        <v>7.433788299560547</v>
+        <v>7.433788776397705</v>
       </c>
     </row>
     <row r="32">
@@ -1074,7 +1074,7 @@
         <v>16.00725746154785</v>
       </c>
       <c r="E32" t="n">
-        <v>8.332729339599609</v>
+        <v>8.332728385925293</v>
       </c>
       <c r="F32" t="n">
         <v>8.257535934448242</v>
@@ -1082,10 +1082,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>22.99178886413574</v>
+        <v>22.99179077148438</v>
       </c>
       <c r="B33" t="n">
-        <v>25.12253761291504</v>
+        <v>25.12253952026367</v>
       </c>
       <c r="C33" t="n">
         <v>5.949573040008545</v>
@@ -1102,19 +1102,19 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>24.2385368347168</v>
+        <v>24.23853492736816</v>
       </c>
       <c r="B34" t="n">
-        <v>19.04565238952637</v>
+        <v>19.045654296875</v>
       </c>
       <c r="C34" t="n">
-        <v>5.74301815032959</v>
+        <v>5.743017673492432</v>
       </c>
       <c r="D34" t="n">
-        <v>11.93467330932617</v>
+        <v>11.93467235565186</v>
       </c>
       <c r="E34" t="n">
-        <v>6.658356666564941</v>
+        <v>6.658355712890625</v>
       </c>
       <c r="F34" t="n">
         <v>10.03778266906738</v>
@@ -1125,7 +1125,7 @@
         <v>25.19003677368164</v>
       </c>
       <c r="B35" t="n">
-        <v>12.75738906860352</v>
+        <v>12.75739002227783</v>
       </c>
       <c r="C35" t="n">
         <v>5.093740940093994</v>
@@ -1134,30 +1134,30 @@
         <v>10.06984519958496</v>
       </c>
       <c r="E35" t="n">
-        <v>6.036589622497559</v>
+        <v>6.036590099334717</v>
       </c>
       <c r="F35" t="n">
-        <v>11.03246116638184</v>
+        <v>11.03246212005615</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>25.90891265869141</v>
+        <v>25.90891075134277</v>
       </c>
       <c r="B36" t="n">
         <v>6.407106876373291</v>
       </c>
       <c r="C36" t="n">
-        <v>4.375017166137695</v>
+        <v>4.375016689300537</v>
       </c>
       <c r="D36" t="n">
         <v>8.393510818481445</v>
       </c>
       <c r="E36" t="n">
-        <v>5.639286994934082</v>
+        <v>5.639286518096924</v>
       </c>
       <c r="F36" t="n">
-        <v>12.10856056213379</v>
+        <v>12.10856151580811</v>
       </c>
     </row>
     <row r="37">
@@ -1165,13 +1165,13 @@
         <v>26.47961616516113</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1908764392137527</v>
+        <v>0.1908765733242035</v>
       </c>
       <c r="C37" t="n">
-        <v>3.902754306793213</v>
+        <v>3.902754068374634</v>
       </c>
       <c r="D37" t="n">
-        <v>6.927595138549805</v>
+        <v>6.927595615386963</v>
       </c>
       <c r="E37" t="n">
         <v>5.495574951171875</v>
@@ -1185,7 +1185,7 @@
         <v>27.01716804504395</v>
       </c>
       <c r="B38" t="n">
-        <v>-5.453994274139404</v>
+        <v>-5.453994750976562</v>
       </c>
       <c r="C38" t="n">
         <v>3.77524209022522</v>
@@ -1205,16 +1205,16 @@
         <v>27.63172721862793</v>
       </c>
       <c r="B39" t="n">
-        <v>-9.883689880371094</v>
+        <v>-9.88369083404541</v>
       </c>
       <c r="C39" t="n">
         <v>3.769729852676392</v>
       </c>
       <c r="D39" t="n">
-        <v>4.520417213439941</v>
+        <v>4.5204176902771</v>
       </c>
       <c r="E39" t="n">
-        <v>5.964939117431641</v>
+        <v>5.964939594268799</v>
       </c>
       <c r="F39" t="n">
         <v>15.62326335906982</v>
@@ -1225,19 +1225,19 @@
         <v>28.34905624389648</v>
       </c>
       <c r="B40" t="n">
-        <v>-12.51373863220215</v>
+        <v>-12.5137357711792</v>
       </c>
       <c r="C40" t="n">
-        <v>3.639243125915527</v>
+        <v>3.639242887496948</v>
       </c>
       <c r="D40" t="n">
-        <v>3.458948135375977</v>
+        <v>3.458949327468872</v>
       </c>
       <c r="E40" t="n">
         <v>6.569222450256348</v>
       </c>
       <c r="F40" t="n">
-        <v>16.68514633178711</v>
+        <v>16.68514442443848</v>
       </c>
     </row>
     <row r="41">
@@ -1245,39 +1245,39 @@
         <v>29.06997489929199</v>
       </c>
       <c r="B41" t="n">
-        <v>-13.12063217163086</v>
+        <v>-13.12063121795654</v>
       </c>
       <c r="C41" t="n">
-        <v>3.326799869537354</v>
+        <v>3.326799631118774</v>
       </c>
       <c r="D41" t="n">
-        <v>2.391517639160156</v>
+        <v>2.391517877578735</v>
       </c>
       <c r="E41" t="n">
-        <v>7.4278564453125</v>
+        <v>7.427855491638184</v>
       </c>
       <c r="F41" t="n">
-        <v>17.55253219604492</v>
+        <v>17.55253410339355</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>29.58150672912598</v>
+        <v>29.58150482177734</v>
       </c>
       <c r="B42" t="n">
-        <v>-11.96098899841309</v>
+        <v>-11.96098804473877</v>
       </c>
       <c r="C42" t="n">
         <v>2.848669290542603</v>
       </c>
       <c r="D42" t="n">
-        <v>1.275003433227539</v>
+        <v>1.275003790855408</v>
       </c>
       <c r="E42" t="n">
-        <v>8.586715698242188</v>
+        <v>8.586714744567871</v>
       </c>
       <c r="F42" t="n">
-        <v>18.14740943908691</v>
+        <v>18.14740753173828</v>
       </c>
     </row>
     <row r="43">
@@ -1285,16 +1285,16 @@
         <v>29.70211601257324</v>
       </c>
       <c r="B43" t="n">
-        <v>-9.792625427246094</v>
+        <v>-9.79262638092041</v>
       </c>
       <c r="C43" t="n">
         <v>2.015948534011841</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1299048066139221</v>
+        <v>0.1299050599336624</v>
       </c>
       <c r="E43" t="n">
-        <v>10.13568115234375</v>
+        <v>10.13568019866943</v>
       </c>
       <c r="F43" t="n">
         <v>18.32455444335938</v>
@@ -1305,36 +1305,36 @@
         <v>29.37685966491699</v>
       </c>
       <c r="B44" t="n">
-        <v>-7.267554759979248</v>
+        <v>-7.26755428314209</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4735918343067169</v>
+        <v>0.4735919833183289</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.9172829985618591</v>
+        <v>-0.9172837138175964</v>
       </c>
       <c r="E44" t="n">
         <v>12.25109195709229</v>
       </c>
       <c r="F44" t="n">
-        <v>17.73883819580078</v>
+        <v>17.73883628845215</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>28.68072700500488</v>
+        <v>28.68072509765625</v>
       </c>
       <c r="B45" t="n">
-        <v>-4.764203548431396</v>
+        <v>-4.764203071594238</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.753300547599792</v>
+        <v>-1.753300666809082</v>
       </c>
       <c r="D45" t="n">
-        <v>-1.645216941833496</v>
+        <v>-1.645217537879944</v>
       </c>
       <c r="E45" t="n">
-        <v>15.12150096893311</v>
+        <v>15.12150192260742</v>
       </c>
       <c r="F45" t="n">
         <v>15.94101715087891</v>
@@ -1345,19 +1345,19 @@
         <v>30.15432929992676</v>
       </c>
       <c r="B46" t="n">
-        <v>-2.595841884613037</v>
+        <v>-2.595842361450195</v>
       </c>
       <c r="C46" t="n">
-        <v>0.576015830039978</v>
+        <v>0.5760158896446228</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3660592436790466</v>
+        <v>-0.3660580515861511</v>
       </c>
       <c r="E46" t="n">
         <v>19.6419792175293</v>
       </c>
       <c r="F46" t="n">
-        <v>13.92293930053711</v>
+        <v>13.92294025421143</v>
       </c>
     </row>
     <row r="47">
@@ -1365,19 +1365,19 @@
         <v>29.13036918640137</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.6823936104774475</v>
+        <v>-0.6823934316635132</v>
       </c>
       <c r="C47" t="n">
         <v>-1.754701256752014</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1451043486595154</v>
+        <v>-0.1451040953397751</v>
       </c>
       <c r="E47" t="n">
         <v>23.73296546936035</v>
       </c>
       <c r="F47" t="n">
-        <v>8.997271537780762</v>
+        <v>8.997270584106445</v>
       </c>
     </row>
     <row r="48">
@@ -1385,13 +1385,13 @@
         <v>27.92717742919922</v>
       </c>
       <c r="B48" t="n">
-        <v>0.9289059042930603</v>
+        <v>0.9289065599441528</v>
       </c>
       <c r="C48" t="n">
-        <v>-3.433582782745361</v>
+        <v>-3.43358325958252</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9709063172340393</v>
+        <v>0.9709065556526184</v>
       </c>
       <c r="E48" t="n">
         <v>28.96307373046875</v>
@@ -1405,33 +1405,33 @@
         <v>26.66284942626953</v>
       </c>
       <c r="B49" t="n">
-        <v>2.388296604156494</v>
+        <v>2.388295650482178</v>
       </c>
       <c r="C49" t="n">
-        <v>-3.697185039520264</v>
+        <v>-3.697184801101685</v>
       </c>
       <c r="D49" t="n">
-        <v>2.996949195861816</v>
+        <v>2.996949434280396</v>
       </c>
       <c r="E49" t="n">
         <v>35.18606567382812</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.792515993118286</v>
+        <v>-3.792515754699707</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>25.37053871154785</v>
+        <v>25.37053680419922</v>
       </c>
       <c r="B50" t="n">
-        <v>3.774512767791748</v>
+        <v>3.77451229095459</v>
       </c>
       <c r="C50" t="n">
-        <v>-2.612247705459595</v>
+        <v>-2.612247943878174</v>
       </c>
       <c r="D50" t="n">
-        <v>5.746724128723145</v>
+        <v>5.746723651885986</v>
       </c>
       <c r="E50" t="n">
         <v>41.77863693237305</v>
@@ -1448,7 +1448,7 @@
         <v>4.945450305938721</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.829651951789856</v>
+        <v>-0.8296518921852112</v>
       </c>
       <c r="D51" t="n">
         <v>8.90379524230957</v>
@@ -1465,16 +1465,16 @@
         <v>22.42062377929688</v>
       </c>
       <c r="B52" t="n">
-        <v>5.629170894622803</v>
+        <v>5.629171371459961</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9590094089508057</v>
+        <v>0.9590093493461609</v>
       </c>
       <c r="D52" t="n">
         <v>12.17672157287598</v>
       </c>
       <c r="E52" t="n">
-        <v>52.34543609619141</v>
+        <v>52.34543991088867</v>
       </c>
       <c r="F52" t="n">
         <v>-8.828831672668457</v>
@@ -1485,19 +1485,19 @@
         <v>20.62509536743164</v>
       </c>
       <c r="B53" t="n">
-        <v>5.73495626449585</v>
+        <v>5.734955787658691</v>
       </c>
       <c r="C53" t="n">
-        <v>2.428501844406128</v>
+        <v>2.428502321243286</v>
       </c>
       <c r="D53" t="n">
         <v>15.33739948272705</v>
       </c>
       <c r="E53" t="n">
-        <v>54.76484298706055</v>
+        <v>54.76484680175781</v>
       </c>
       <c r="F53" t="n">
-        <v>-6.0260910987854</v>
+        <v>-6.026090621948242</v>
       </c>
     </row>
     <row r="54">
@@ -1505,7 +1505,7 @@
         <v>18.62551498413086</v>
       </c>
       <c r="B54" t="n">
-        <v>5.347177028656006</v>
+        <v>5.347176551818848</v>
       </c>
       <c r="C54" t="n">
         <v>3.584700345993042</v>
@@ -1517,7 +1517,7 @@
         <v>55.08745956420898</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.492030382156372</v>
+        <v>-2.492030143737793</v>
       </c>
     </row>
     <row r="55">
@@ -1545,7 +1545,7 @@
         <v>14.29183292388916</v>
       </c>
       <c r="B56" t="n">
-        <v>3.753099918365479</v>
+        <v>3.753099679946899</v>
       </c>
       <c r="C56" t="n">
         <v>5.384245872497559</v>
@@ -1554,10 +1554,10 @@
         <v>23.41858291625977</v>
       </c>
       <c r="E56" t="n">
-        <v>50.66776275634766</v>
+        <v>50.66776657104492</v>
       </c>
       <c r="F56" t="n">
-        <v>3.945389986038208</v>
+        <v>3.945390224456787</v>
       </c>
     </row>
     <row r="57">
@@ -1565,10 +1565,10 @@
         <v>12.11798667907715</v>
       </c>
       <c r="B57" t="n">
-        <v>2.83628511428833</v>
+        <v>2.836285591125488</v>
       </c>
       <c r="C57" t="n">
-        <v>6.182946681976318</v>
+        <v>6.182945728302002</v>
       </c>
       <c r="D57" t="n">
         <v>25.62238502502441</v>
@@ -1577,7 +1577,7 @@
         <v>46.47842025756836</v>
       </c>
       <c r="F57" t="n">
-        <v>6.130642890930176</v>
+        <v>6.130643367767334</v>
       </c>
     </row>
     <row r="58">
@@ -1585,7 +1585,7 @@
         <v>10.01347827911377</v>
       </c>
       <c r="B58" t="n">
-        <v>1.952127933502197</v>
+        <v>1.952127575874329</v>
       </c>
       <c r="C58" t="n">
         <v>6.964168071746826</v>
@@ -1597,7 +1597,7 @@
         <v>41.25951385498047</v>
       </c>
       <c r="F58" t="n">
-        <v>7.542942523956299</v>
+        <v>7.542943000793457</v>
       </c>
     </row>
     <row r="59">
@@ -1605,16 +1605,16 @@
         <v>7.990589141845703</v>
       </c>
       <c r="B59" t="n">
-        <v>1.112545490264893</v>
+        <v>1.112545132637024</v>
       </c>
       <c r="C59" t="n">
-        <v>7.732068538665771</v>
+        <v>7.732067584991455</v>
       </c>
       <c r="D59" t="n">
         <v>29.14215469360352</v>
       </c>
       <c r="E59" t="n">
-        <v>35.14380264282227</v>
+        <v>35.14380645751953</v>
       </c>
       <c r="F59" t="n">
         <v>8.173214912414551</v>
@@ -1625,16 +1625,16 @@
         <v>6.044664859771729</v>
       </c>
       <c r="B60" t="n">
-        <v>0.3263134658336639</v>
+        <v>0.3263121545314789</v>
       </c>
       <c r="C60" t="n">
-        <v>8.491707801818848</v>
+        <v>8.491708755493164</v>
       </c>
       <c r="D60" t="n">
         <v>30.31995010375977</v>
       </c>
       <c r="E60" t="n">
-        <v>28.28813743591309</v>
+        <v>28.28813934326172</v>
       </c>
       <c r="F60" t="n">
         <v>8.010414123535156</v>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4.175992488861084</v>
+        <v>4.175993919372559</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.3612914383411407</v>
+        <v>-0.3612922728061676</v>
       </c>
       <c r="C61" t="n">
         <v>9.256365776062012</v>
@@ -1657,15 +1657,15 @@
         <v>21.00459289550781</v>
       </c>
       <c r="F61" t="n">
-        <v>7.246137142181396</v>
+        <v>7.246137619018555</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2.404323101043701</v>
+        <v>2.40432333946228</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.8600307106971741</v>
+        <v>-0.8600310087203979</v>
       </c>
       <c r="C62" t="n">
         <v>10.03280925750732</v>
@@ -1677,15 +1677,15 @@
         <v>13.69804668426514</v>
       </c>
       <c r="F62" t="n">
-        <v>6.251384258270264</v>
+        <v>6.251384735107422</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.7545866370201111</v>
+        <v>0.7545859813690186</v>
       </c>
       <c r="B63" t="n">
-        <v>-1.079461574554443</v>
+        <v>-1.079460024833679</v>
       </c>
       <c r="C63" t="n">
         <v>10.7972936630249</v>
@@ -1702,19 +1702,19 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-0.7457318902015686</v>
+        <v>-0.7457306385040283</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.9319091439247131</v>
+        <v>-0.931909441947937</v>
       </c>
       <c r="C64" t="n">
-        <v>11.49567031860352</v>
+        <v>11.49567127227783</v>
       </c>
       <c r="D64" t="n">
         <v>31.60845565795898</v>
       </c>
       <c r="E64" t="n">
-        <v>1.060096621513367</v>
+        <v>1.060097813606262</v>
       </c>
       <c r="F64" t="n">
         <v>5.136619567871094</v>
@@ -1722,19 +1722,19 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-2.090734958648682</v>
+        <v>-2.090733766555786</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.3694434463977814</v>
+        <v>-0.3694423735141754</v>
       </c>
       <c r="C65" t="n">
-        <v>12.05819702148438</v>
+        <v>12.05819892883301</v>
       </c>
       <c r="D65" t="n">
-        <v>31.61435699462891</v>
+        <v>31.61435508728027</v>
       </c>
       <c r="E65" t="n">
-        <v>-3.233217477798462</v>
+        <v>-3.233218669891357</v>
       </c>
       <c r="F65" t="n">
         <v>5.258789539337158</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-3.311525821685791</v>
+        <v>-3.311526536941528</v>
       </c>
       <c r="B66" t="n">
-        <v>0.5874485373497009</v>
+        <v>0.5874491930007935</v>
       </c>
       <c r="C66" t="n">
         <v>12.41564559936523</v>
@@ -1762,16 +1762,16 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-4.46544885635376</v>
+        <v>-4.465447425842285</v>
       </c>
       <c r="B67" t="n">
-        <v>1.867310047149658</v>
+        <v>1.867310643196106</v>
       </c>
       <c r="C67" t="n">
-        <v>12.48532295227051</v>
+        <v>12.48532390594482</v>
       </c>
       <c r="D67" t="n">
-        <v>31.77260589599609</v>
+        <v>31.77260398864746</v>
       </c>
       <c r="E67" t="n">
         <v>-6.210098266601562</v>
@@ -1782,19 +1782,19 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-5.599361896514893</v>
+        <v>-5.599360466003418</v>
       </c>
       <c r="B68" t="n">
-        <v>3.371727466583252</v>
+        <v>3.371726989746094</v>
       </c>
       <c r="C68" t="n">
-        <v>12.17688655853271</v>
+        <v>12.17688751220703</v>
       </c>
       <c r="D68" t="n">
         <v>31.84543418884277</v>
       </c>
       <c r="E68" t="n">
-        <v>-4.995517730712891</v>
+        <v>-4.995518207550049</v>
       </c>
       <c r="F68" t="n">
         <v>5.067599773406982</v>
@@ -1802,13 +1802,13 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-6.687912464141846</v>
+        <v>-6.687911033630371</v>
       </c>
       <c r="B69" t="n">
-        <v>5.096287250518799</v>
+        <v>5.096286296844482</v>
       </c>
       <c r="C69" t="n">
-        <v>11.30015659332275</v>
+        <v>11.30015754699707</v>
       </c>
       <c r="D69" t="n">
         <v>31.82487487792969</v>
@@ -1817,27 +1817,27 @@
         <v>-2.51228928565979</v>
       </c>
       <c r="F69" t="n">
-        <v>3.378950834274292</v>
+        <v>3.378951072692871</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-7.606743335723877</v>
+        <v>-7.606743812561035</v>
       </c>
       <c r="B70" t="n">
         <v>7.166304111480713</v>
       </c>
       <c r="C70" t="n">
-        <v>9.52202033996582</v>
+        <v>9.522021293640137</v>
       </c>
       <c r="D70" t="n">
-        <v>31.66789627075195</v>
+        <v>31.66789436340332</v>
       </c>
       <c r="E70" t="n">
-        <v>0.7786329984664917</v>
+        <v>0.7786332368850708</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8097212314605713</v>
+        <v>0.8097211122512817</v>
       </c>
     </row>
     <row r="71">
@@ -1854,7 +1854,7 @@
         <v>34.27399444580078</v>
       </c>
       <c r="E71" t="n">
-        <v>0.4575155973434448</v>
+        <v>0.4575164318084717</v>
       </c>
       <c r="F71" t="n">
         <v>1.409748196601868</v>
@@ -1862,30 +1862,30 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-8.007962226867676</v>
+        <v>-8.007960319519043</v>
       </c>
       <c r="B72" t="n">
         <v>13.46810722351074</v>
       </c>
       <c r="C72" t="n">
-        <v>1.531050682067871</v>
+        <v>1.531050801277161</v>
       </c>
       <c r="D72" t="n">
         <v>33.96356964111328</v>
       </c>
       <c r="E72" t="n">
-        <v>3.732045888900757</v>
+        <v>3.732045650482178</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.345711708068848</v>
+        <v>-1.345711588859558</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-7.028366565704346</v>
+        <v>-7.028367042541504</v>
       </c>
       <c r="B73" t="n">
-        <v>18.24349975585938</v>
+        <v>18.24350166320801</v>
       </c>
       <c r="C73" t="n">
         <v>-4.702480316162109</v>
@@ -1894,21 +1894,21 @@
         <v>33.5078125</v>
       </c>
       <c r="E73" t="n">
-        <v>7.01633358001709</v>
+        <v>7.016332626342773</v>
       </c>
       <c r="F73" t="n">
-        <v>-3.118787527084351</v>
+        <v>-3.118787288665771</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-5.141279697418213</v>
+        <v>-5.141278266906738</v>
       </c>
       <c r="B74" t="n">
-        <v>24.08427619934082</v>
+        <v>24.08427810668945</v>
       </c>
       <c r="C74" t="n">
-        <v>-10.97702980041504</v>
+        <v>-10.97702884674072</v>
       </c>
       <c r="D74" t="n">
         <v>32.89920806884766</v>
@@ -1917,18 +1917,18 @@
         <v>10.08639812469482</v>
       </c>
       <c r="F74" t="n">
-        <v>-3.212769269943237</v>
+        <v>-3.212769031524658</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-2.45647668838501</v>
+        <v>-2.456476449966431</v>
       </c>
       <c r="B75" t="n">
-        <v>30.4969539642334</v>
+        <v>30.49695587158203</v>
       </c>
       <c r="C75" t="n">
-        <v>-15.45810222625732</v>
+        <v>-15.45810031890869</v>
       </c>
       <c r="D75" t="n">
         <v>32.0859489440918</v>
@@ -1937,44 +1937,44 @@
         <v>12.66594886779785</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.800117969512939</v>
+        <v>-1.800118327140808</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.7708210349082947</v>
+        <v>0.7708213329315186</v>
       </c>
       <c r="B76" t="n">
-        <v>36.64367294311523</v>
+        <v>36.6436767578125</v>
       </c>
       <c r="C76" t="n">
-        <v>-16.9205493927002</v>
+        <v>-16.92055130004883</v>
       </c>
       <c r="D76" t="n">
         <v>31.00295448303223</v>
       </c>
       <c r="E76" t="n">
-        <v>14.49637031555176</v>
+        <v>14.49636936187744</v>
       </c>
       <c r="F76" t="n">
-        <v>0.330622673034668</v>
+        <v>0.3306227326393127</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4.227010250091553</v>
+        <v>4.227009773254395</v>
       </c>
       <c r="B77" t="n">
         <v>41.55078887939453</v>
       </c>
       <c r="C77" t="n">
-        <v>-15.10958194732666</v>
+        <v>-15.10958099365234</v>
       </c>
       <c r="D77" t="n">
         <v>29.62570190429688</v>
       </c>
       <c r="E77" t="n">
-        <v>15.5088586807251</v>
+        <v>15.50885772705078</v>
       </c>
       <c r="F77" t="n">
         <v>2.451910257339478</v>
@@ -1982,19 +1982,19 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>7.626901626586914</v>
+        <v>7.626902103424072</v>
       </c>
       <c r="B78" t="n">
         <v>44.61349105834961</v>
       </c>
       <c r="C78" t="n">
-        <v>-11.02766704559326</v>
+        <v>-11.02766609191895</v>
       </c>
       <c r="D78" t="n">
         <v>27.96556663513184</v>
       </c>
       <c r="E78" t="n">
-        <v>15.79403400421143</v>
+        <v>15.79403495788574</v>
       </c>
       <c r="F78" t="n">
         <v>4.256207466125488</v>
@@ -2005,7 +2005,7 @@
         <v>10.79610252380371</v>
       </c>
       <c r="B79" t="n">
-        <v>45.61873626708984</v>
+        <v>45.61873245239258</v>
       </c>
       <c r="C79" t="n">
         <v>-6.132650375366211</v>
@@ -2014,7 +2014,7 @@
         <v>26.05494689941406</v>
       </c>
       <c r="E79" t="n">
-        <v>15.49099063873291</v>
+        <v>15.49099159240723</v>
       </c>
       <c r="F79" t="n">
         <v>5.696433544158936</v>
@@ -2025,7 +2025,7 @@
         <v>13.64182281494141</v>
       </c>
       <c r="B80" t="n">
-        <v>44.71590042114258</v>
+        <v>44.71589660644531</v>
       </c>
       <c r="C80" t="n">
         <v>-1.666900992393494</v>
@@ -2034,10 +2034,10 @@
         <v>23.95768737792969</v>
       </c>
       <c r="E80" t="n">
-        <v>14.75194454193115</v>
+        <v>14.75194549560547</v>
       </c>
       <c r="F80" t="n">
-        <v>6.825350761413574</v>
+        <v>6.825351238250732</v>
       </c>
     </row>
     <row r="81">
@@ -2048,7 +2048,7 @@
         <v>42.21905136108398</v>
       </c>
       <c r="C81" t="n">
-        <v>1.825234413146973</v>
+        <v>1.825234532356262</v>
       </c>
       <c r="D81" t="n">
         <v>21.72864723205566</v>
@@ -2057,7 +2057,7 @@
         <v>13.68058681488037</v>
       </c>
       <c r="F81" t="n">
-        <v>7.69713830947876</v>
+        <v>7.697139263153076</v>
       </c>
     </row>
     <row r="82">
@@ -2065,7 +2065,7 @@
         <v>18.22812461853027</v>
       </c>
       <c r="B82" t="n">
-        <v>38.35565567016602</v>
+        <v>38.35565185546875</v>
       </c>
       <c r="C82" t="n">
         <v>4.212202072143555</v>
@@ -2117,7 +2117,7 @@
         <v>9.737434387207031</v>
       </c>
       <c r="F84" t="n">
-        <v>9.694578170776367</v>
+        <v>9.694579124450684</v>
       </c>
     </row>
     <row r="85">
@@ -2128,7 +2128,7 @@
         <v>20.94418334960938</v>
       </c>
       <c r="C85" t="n">
-        <v>6.267776489257812</v>
+        <v>6.267776012420654</v>
       </c>
       <c r="D85" t="n">
         <v>12.81669998168945</v>
@@ -2145,10 +2145,10 @@
         <v>23.17848205566406</v>
       </c>
       <c r="B86" t="n">
-        <v>14.20132446289062</v>
+        <v>14.20132541656494</v>
       </c>
       <c r="C86" t="n">
-        <v>5.743066787719727</v>
+        <v>5.743066310882568</v>
       </c>
       <c r="D86" t="n">
         <v>10.96358776092529</v>
@@ -2165,16 +2165,16 @@
         <v>23.70354652404785</v>
       </c>
       <c r="B87" t="n">
-        <v>7.590355396270752</v>
+        <v>7.590354919433594</v>
       </c>
       <c r="C87" t="n">
-        <v>4.921989917755127</v>
+        <v>4.921989440917969</v>
       </c>
       <c r="D87" t="n">
-        <v>9.37242603302002</v>
+        <v>9.372425079345703</v>
       </c>
       <c r="E87" t="n">
-        <v>6.997740745544434</v>
+        <v>6.99774169921875</v>
       </c>
       <c r="F87" t="n">
         <v>12.13063812255859</v>
@@ -2182,10 +2182,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>24.09939384460449</v>
+        <v>24.09939193725586</v>
       </c>
       <c r="B88" t="n">
-        <v>1.376961231231689</v>
+        <v>1.376961827278137</v>
       </c>
       <c r="C88" t="n">
         <v>4.189527988433838</v>
@@ -2197,7 +2197,7 @@
         <v>6.761260032653809</v>
       </c>
       <c r="F88" t="n">
-        <v>13.22688961029053</v>
+        <v>13.22689056396484</v>
       </c>
     </row>
     <row r="89">
@@ -2205,19 +2205,19 @@
         <v>24.48716354370117</v>
       </c>
       <c r="B89" t="n">
-        <v>-4.144860744476318</v>
+        <v>-4.14486026763916</v>
       </c>
       <c r="C89" t="n">
-        <v>3.816786289215088</v>
+        <v>3.816786050796509</v>
       </c>
       <c r="D89" t="n">
-        <v>6.950642585754395</v>
+        <v>6.950643062591553</v>
       </c>
       <c r="E89" t="n">
         <v>6.922660827636719</v>
       </c>
       <c r="F89" t="n">
-        <v>14.44065189361572</v>
+        <v>14.44065284729004</v>
       </c>
     </row>
     <row r="90">
@@ -2225,10 +2225,10 @@
         <v>24.97182655334473</v>
       </c>
       <c r="B90" t="n">
-        <v>-8.541332244873047</v>
+        <v>-8.54133129119873</v>
       </c>
       <c r="C90" t="n">
-        <v>3.695663452148438</v>
+        <v>3.695663690567017</v>
       </c>
       <c r="D90" t="n">
         <v>6.029208183288574</v>
@@ -2242,22 +2242,22 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>25.58839988708496</v>
+        <v>25.58839797973633</v>
       </c>
       <c r="B91" t="n">
-        <v>-11.32310676574707</v>
+        <v>-11.32310581207275</v>
       </c>
       <c r="C91" t="n">
-        <v>3.506877422332764</v>
+        <v>3.506877183914185</v>
       </c>
       <c r="D91" t="n">
-        <v>5.184595108032227</v>
+        <v>5.184594631195068</v>
       </c>
       <c r="E91" t="n">
-        <v>8.341655731201172</v>
+        <v>8.341654777526855</v>
       </c>
       <c r="F91" t="n">
-        <v>16.86196517944336</v>
+        <v>16.86196327209473</v>
       </c>
     </row>
     <row r="92">
@@ -2265,19 +2265,19 @@
         <v>26.26418876647949</v>
       </c>
       <c r="B92" t="n">
-        <v>-12.14970970153809</v>
+        <v>-12.14970874786377</v>
       </c>
       <c r="C92" t="n">
-        <v>3.128812789916992</v>
+        <v>3.128813028335571</v>
       </c>
       <c r="D92" t="n">
-        <v>4.322244644165039</v>
+        <v>4.322245121002197</v>
       </c>
       <c r="E92" t="n">
-        <v>9.470157623291016</v>
+        <v>9.470156669616699</v>
       </c>
       <c r="F92" t="n">
-        <v>17.86553955078125</v>
+        <v>17.86553764343262</v>
       </c>
     </row>
     <row r="93">
@@ -2285,19 +2285,19 @@
         <v>26.84214401245117</v>
       </c>
       <c r="B93" t="n">
-        <v>-11.31028747558594</v>
+        <v>-11.31028652191162</v>
       </c>
       <c r="C93" t="n">
         <v>2.702703237533569</v>
       </c>
       <c r="D93" t="n">
-        <v>3.356195449829102</v>
+        <v>3.356194734573364</v>
       </c>
       <c r="E93" t="n">
         <v>10.81924057006836</v>
       </c>
       <c r="F93" t="n">
-        <v>18.59156227111816</v>
+        <v>18.59156036376953</v>
       </c>
     </row>
     <row r="94">
@@ -2305,19 +2305,19 @@
         <v>27.18791198730469</v>
       </c>
       <c r="B94" t="n">
-        <v>-9.345296859741211</v>
+        <v>-9.345297813415527</v>
       </c>
       <c r="C94" t="n">
         <v>2.156238794326782</v>
       </c>
       <c r="D94" t="n">
-        <v>2.262473106384277</v>
+        <v>2.26247239112854</v>
       </c>
       <c r="E94" t="n">
         <v>12.38584804534912</v>
       </c>
       <c r="F94" t="n">
-        <v>18.88569831848145</v>
+        <v>18.88569450378418</v>
       </c>
     </row>
     <row r="95">
@@ -2325,19 +2325,19 @@
         <v>27.25304985046387</v>
       </c>
       <c r="B95" t="n">
-        <v>-6.806542873382568</v>
+        <v>-6.806541442871094</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9915872812271118</v>
+        <v>0.9915873408317566</v>
       </c>
       <c r="D95" t="n">
-        <v>1.125807762145996</v>
+        <v>1.125809073448181</v>
       </c>
       <c r="E95" t="n">
-        <v>14.24045467376709</v>
+        <v>14.24045562744141</v>
       </c>
       <c r="F95" t="n">
-        <v>18.49200057983398</v>
+        <v>18.49199867248535</v>
       </c>
     </row>
     <row r="96">
@@ -2345,39 +2345,39 @@
         <v>27.07552146911621</v>
       </c>
       <c r="B96" t="n">
-        <v>-4.052876949310303</v>
+        <v>-4.052877426147461</v>
       </c>
       <c r="C96" t="n">
-        <v>-1.081645369529724</v>
+        <v>-1.081645488739014</v>
       </c>
       <c r="D96" t="n">
-        <v>0.1440916657447815</v>
+        <v>0.1440919190645218</v>
       </c>
       <c r="E96" t="n">
-        <v>16.55619621276855</v>
+        <v>16.55619430541992</v>
       </c>
       <c r="F96" t="n">
-        <v>17.02069282531738</v>
+        <v>17.02069091796875</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>32.71094512939453</v>
+        <v>32.7109489440918</v>
       </c>
       <c r="B97" t="n">
-        <v>5.448960781097412</v>
+        <v>5.448960304260254</v>
       </c>
       <c r="C97" t="n">
-        <v>-6.057275295257568</v>
+        <v>-6.057275772094727</v>
       </c>
       <c r="D97" t="n">
-        <v>-14.11501789093018</v>
+        <v>-14.11501693725586</v>
       </c>
       <c r="E97" t="n">
         <v>12.89249706268311</v>
       </c>
       <c r="F97" t="n">
-        <v>5.304746150970459</v>
+        <v>5.304746627807617</v>
       </c>
     </row>
     <row r="98">
@@ -2388,16 +2388,16 @@
         <v>9.642598152160645</v>
       </c>
       <c r="C98" t="n">
-        <v>-9.472084045410156</v>
+        <v>-9.47208309173584</v>
       </c>
       <c r="D98" t="n">
-        <v>-12.37170124053955</v>
+        <v>-12.37170219421387</v>
       </c>
       <c r="E98" t="n">
         <v>17.87347030639648</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.463012933731079</v>
+        <v>-1.463013052940369</v>
       </c>
     </row>
     <row r="99">
@@ -2411,7 +2411,7 @@
         <v>-9.790581703186035</v>
       </c>
       <c r="D99" t="n">
-        <v>-9.813044548034668</v>
+        <v>-9.813045501708984</v>
       </c>
       <c r="E99" t="n">
         <v>23.45887565612793</v>
@@ -2425,19 +2425,19 @@
         <v>34.17300796508789</v>
       </c>
       <c r="B100" t="n">
-        <v>18.1113224029541</v>
+        <v>18.11132431030273</v>
       </c>
       <c r="C100" t="n">
-        <v>-7.310548305511475</v>
+        <v>-7.310549259185791</v>
       </c>
       <c r="D100" t="n">
-        <v>-6.529208183288574</v>
+        <v>-6.529208660125732</v>
       </c>
       <c r="E100" t="n">
-        <v>29.64704132080078</v>
+        <v>29.64704322814941</v>
       </c>
       <c r="F100" t="n">
-        <v>-14.00612926483154</v>
+        <v>-14.00612831115723</v>
       </c>
     </row>
     <row r="101">
@@ -2445,13 +2445,13 @@
         <v>33.53760528564453</v>
       </c>
       <c r="B101" t="n">
-        <v>20.47041893005371</v>
+        <v>20.47042083740234</v>
       </c>
       <c r="C101" t="n">
         <v>-4.028501987457275</v>
       </c>
       <c r="D101" t="n">
-        <v>-2.674740791320801</v>
+        <v>-2.674740552902222</v>
       </c>
       <c r="E101" t="n">
         <v>36.34217834472656</v>
@@ -2468,27 +2468,27 @@
         <v>20.80165100097656</v>
       </c>
       <c r="C102" t="n">
-        <v>-1.427673697471619</v>
+        <v>-1.427673816680908</v>
       </c>
       <c r="D102" t="n">
-        <v>1.544735908508301</v>
+        <v>1.544735312461853</v>
       </c>
       <c r="E102" t="n">
         <v>43.04413986206055</v>
       </c>
       <c r="F102" t="n">
-        <v>-12.00063896179199</v>
+        <v>-12.00063800811768</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>29.93349266052246</v>
+        <v>29.93349456787109</v>
       </c>
       <c r="B103" t="n">
         <v>19.66530990600586</v>
       </c>
       <c r="C103" t="n">
-        <v>0.2927733957767487</v>
+        <v>0.292773425579071</v>
       </c>
       <c r="D103" t="n">
         <v>5.893322944641113</v>
@@ -2497,7 +2497,7 @@
         <v>48.86608123779297</v>
       </c>
       <c r="F103" t="n">
-        <v>-8.133773803710938</v>
+        <v>-8.133772850036621</v>
       </c>
     </row>
     <row r="104">
@@ -2508,16 +2508,16 @@
         <v>17.99419403076172</v>
       </c>
       <c r="C104" t="n">
-        <v>1.68007755279541</v>
+        <v>1.6800776720047</v>
       </c>
       <c r="D104" t="n">
-        <v>10.14219951629639</v>
+        <v>10.14219856262207</v>
       </c>
       <c r="E104" t="n">
-        <v>53.00614547729492</v>
+        <v>53.00614929199219</v>
       </c>
       <c r="F104" t="n">
-        <v>-4.409515380859375</v>
+        <v>-4.409514904022217</v>
       </c>
     </row>
     <row r="105">
@@ -2537,15 +2537,15 @@
         <v>55.07503509521484</v>
       </c>
       <c r="F105" t="n">
-        <v>-1.389777898788452</v>
+        <v>-1.389777779579163</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>21.40399360656738</v>
+        <v>21.40399169921875</v>
       </c>
       <c r="B106" t="n">
-        <v>14.00260829925537</v>
+        <v>14.00260925292969</v>
       </c>
       <c r="C106" t="n">
         <v>3.857009649276733</v>
@@ -2554,7 +2554,7 @@
         <v>17.67443466186523</v>
       </c>
       <c r="E106" t="n">
-        <v>55.03853988647461</v>
+        <v>55.03854370117188</v>
       </c>
       <c r="F106" t="n">
         <v>0.8124593496322632</v>
@@ -2565,7 +2565,7 @@
         <v>18.18756294250488</v>
       </c>
       <c r="B107" t="n">
-        <v>11.06383609771729</v>
+        <v>11.0638370513916</v>
       </c>
       <c r="C107" t="n">
         <v>4.040149211883545</v>
@@ -2574,10 +2574,10 @@
         <v>20.77007102966309</v>
       </c>
       <c r="E107" t="n">
-        <v>53.06144714355469</v>
+        <v>53.06145095825195</v>
       </c>
       <c r="F107" t="n">
-        <v>2.335421085357666</v>
+        <v>2.335420846939087</v>
       </c>
     </row>
     <row r="108">
@@ -2588,13 +2588,13 @@
         <v>7.74692964553833</v>
       </c>
       <c r="C108" t="n">
-        <v>3.790030956268311</v>
+        <v>3.790030717849731</v>
       </c>
       <c r="D108" t="n">
         <v>23.35972023010254</v>
       </c>
       <c r="E108" t="n">
-        <v>49.40789794921875</v>
+        <v>49.40790176391602</v>
       </c>
       <c r="F108" t="n">
         <v>3.344803333282471</v>
@@ -2605,24 +2605,24 @@
         <v>11.83092212677002</v>
       </c>
       <c r="B109" t="n">
-        <v>4.829379558563232</v>
+        <v>4.829380512237549</v>
       </c>
       <c r="C109" t="n">
-        <v>3.679421901702881</v>
+        <v>3.67942214012146</v>
       </c>
       <c r="D109" t="n">
         <v>25.42351341247559</v>
       </c>
       <c r="E109" t="n">
-        <v>44.37055587768555</v>
+        <v>44.37055969238281</v>
       </c>
       <c r="F109" t="n">
-        <v>3.821094989776611</v>
+        <v>3.82109522819519</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>9.006787300109863</v>
+        <v>9.00678825378418</v>
       </c>
       <c r="B110" t="n">
         <v>2.785033702850342</v>
@@ -2631,10 +2631,10 @@
         <v>4.032492160797119</v>
       </c>
       <c r="D110" t="n">
-        <v>26.95767593383789</v>
+        <v>26.95767402648926</v>
       </c>
       <c r="E110" t="n">
-        <v>38.24296569824219</v>
+        <v>38.24296951293945</v>
       </c>
       <c r="F110" t="n">
         <v>3.589543342590332</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>6.481892108917236</v>
+        <v>6.481892585754395</v>
       </c>
       <c r="B111" t="n">
-        <v>1.641087055206299</v>
+        <v>1.641085743904114</v>
       </c>
       <c r="C111" t="n">
         <v>4.870926380157471</v>
@@ -2662,13 +2662,13 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>4.177308559417725</v>
+        <v>4.177309036254883</v>
       </c>
       <c r="B112" t="n">
-        <v>1.156832218170166</v>
+        <v>1.156831860542297</v>
       </c>
       <c r="C112" t="n">
-        <v>6.054930686950684</v>
+        <v>6.054930210113525</v>
       </c>
       <c r="D112" t="n">
         <v>28.59935569763184</v>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1.974236965179443</v>
+        <v>1.974237203598022</v>
       </c>
       <c r="B113" t="n">
-        <v>1.000515460968018</v>
+        <v>1.000515103340149</v>
       </c>
       <c r="C113" t="n">
         <v>7.37754487991333</v>
@@ -2697,18 +2697,18 @@
         <v>16.89493179321289</v>
       </c>
       <c r="F113" t="n">
-        <v>-1.267461538314819</v>
+        <v>-1.267461657524109</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-0.2144036591053009</v>
+        <v>-0.2144043296575546</v>
       </c>
       <c r="B114" t="n">
-        <v>0.9009289145469666</v>
+        <v>0.9009281396865845</v>
       </c>
       <c r="C114" t="n">
-        <v>8.644564628601074</v>
+        <v>8.644565582275391</v>
       </c>
       <c r="D114" t="n">
         <v>29.11742973327637</v>
@@ -2717,35 +2717,35 @@
         <v>10.12013053894043</v>
       </c>
       <c r="F114" t="n">
-        <v>-2.764822721481323</v>
+        <v>-2.764822483062744</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-2.402330875396729</v>
+        <v>-2.402331590652466</v>
       </c>
       <c r="B115" t="n">
-        <v>0.7573532462120056</v>
+        <v>0.7573539018630981</v>
       </c>
       <c r="C115" t="n">
-        <v>9.740625381469727</v>
+        <v>9.740626335144043</v>
       </c>
       <c r="D115" t="n">
         <v>29.37329864501953</v>
       </c>
       <c r="E115" t="n">
-        <v>4.297740936279297</v>
+        <v>4.29773998260498</v>
       </c>
       <c r="F115" t="n">
-        <v>-3.387938737869263</v>
+        <v>-3.387938976287842</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-4.526888370513916</v>
+        <v>-4.526888847351074</v>
       </c>
       <c r="B116" t="n">
-        <v>0.6776184439659119</v>
+        <v>0.677618145942688</v>
       </c>
       <c r="C116" t="n">
         <v>10.64062023162842</v>
@@ -2754,75 +2754,75 @@
         <v>29.78906440734863</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0726240873336792</v>
+        <v>0.07262407243251801</v>
       </c>
       <c r="F116" t="n">
-        <v>-3.230351686477661</v>
+        <v>-3.23035192489624</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-6.476080417633057</v>
+        <v>-6.476080894470215</v>
       </c>
       <c r="B117" t="n">
-        <v>0.9419178366661072</v>
+        <v>0.9419180154800415</v>
       </c>
       <c r="C117" t="n">
-        <v>11.40600776672363</v>
+        <v>11.40600872039795</v>
       </c>
       <c r="D117" t="n">
         <v>30.36520957946777</v>
       </c>
       <c r="E117" t="n">
-        <v>-2.015466928482056</v>
+        <v>-2.015465497970581</v>
       </c>
       <c r="F117" t="n">
-        <v>-2.646555662155151</v>
+        <v>-2.646555423736572</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-8.13521671295166</v>
+        <v>-8.135214805603027</v>
       </c>
       <c r="B118" t="n">
-        <v>1.881794452667236</v>
+        <v>1.881794095039368</v>
       </c>
       <c r="C118" t="n">
-        <v>12.11329174041748</v>
+        <v>12.1132926940918</v>
       </c>
       <c r="D118" t="n">
         <v>31.01923751831055</v>
       </c>
       <c r="E118" t="n">
-        <v>-1.854646801948547</v>
+        <v>-1.854647040367126</v>
       </c>
       <c r="F118" t="n">
-        <v>-2.104755163192749</v>
+        <v>-2.10475492477417</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-9.456295967102051</v>
+        <v>-9.456294059753418</v>
       </c>
       <c r="B119" t="n">
-        <v>3.643179416656494</v>
+        <v>3.643179178237915</v>
       </c>
       <c r="C119" t="n">
-        <v>12.71645355224609</v>
+        <v>12.71645450592041</v>
       </c>
       <c r="D119" t="n">
         <v>31.65631866455078</v>
       </c>
       <c r="E119" t="n">
-        <v>0.1830462217330933</v>
+        <v>0.1830466836690903</v>
       </c>
       <c r="F119" t="n">
-        <v>-2.170740842819214</v>
+        <v>-2.170740604400635</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-10.41243267059326</v>
+        <v>-10.41243076324463</v>
       </c>
       <c r="B120" t="n">
         <v>6.231581211090088</v>
@@ -2831,13 +2831,13 @@
         <v>13.00448131561279</v>
       </c>
       <c r="D120" t="n">
-        <v>32.23357391357422</v>
+        <v>32.23357772827148</v>
       </c>
       <c r="E120" t="n">
-        <v>3.402154684066772</v>
+        <v>3.402154445648193</v>
       </c>
       <c r="F120" t="n">
-        <v>-3.377328634262085</v>
+        <v>-3.377328872680664</v>
       </c>
     </row>
     <row r="121">
@@ -2848,7 +2848,7 @@
         <v>9.66666316986084</v>
       </c>
       <c r="C121" t="n">
-        <v>12.62370014190674</v>
+        <v>12.62370204925537</v>
       </c>
       <c r="D121" t="n">
         <v>32.76180648803711</v>
@@ -2868,16 +2868,16 @@
         <v>13.98578262329102</v>
       </c>
       <c r="C122" t="n">
-        <v>10.98014354705811</v>
+        <v>10.98014450073242</v>
       </c>
       <c r="D122" t="n">
         <v>35.5955810546875</v>
       </c>
       <c r="E122" t="n">
-        <v>11.8169002532959</v>
+        <v>11.81689929962158</v>
       </c>
       <c r="F122" t="n">
-        <v>-6.743443489074707</v>
+        <v>-6.743442535400391</v>
       </c>
     </row>
     <row r="123">
@@ -2888,7 +2888,7 @@
         <v>19.03135108947754</v>
       </c>
       <c r="C123" t="n">
-        <v>7.145896434783936</v>
+        <v>7.145895481109619</v>
       </c>
       <c r="D123" t="n">
         <v>35.63029098510742</v>
@@ -2905,10 +2905,10 @@
         <v>-8.885464668273926</v>
       </c>
       <c r="B124" t="n">
-        <v>24.39792442321777</v>
+        <v>24.39792633056641</v>
       </c>
       <c r="C124" t="n">
-        <v>0.3149249255657196</v>
+        <v>0.3149248957633972</v>
       </c>
       <c r="D124" t="n">
         <v>35.29672241210938</v>
@@ -2922,13 +2922,13 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-6.977999210357666</v>
+        <v>-6.977997779846191</v>
       </c>
       <c r="B125" t="n">
-        <v>29.73955345153809</v>
+        <v>29.73955535888672</v>
       </c>
       <c r="C125" t="n">
-        <v>-8.618704795837402</v>
+        <v>-8.618703842163086</v>
       </c>
       <c r="D125" t="n">
         <v>34.47843551635742</v>
@@ -2937,18 +2937,18 @@
         <v>20.8059139251709</v>
       </c>
       <c r="F125" t="n">
-        <v>-6.079532146453857</v>
+        <v>-6.079531669616699</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-4.505127429962158</v>
+        <v>-4.505125999450684</v>
       </c>
       <c r="B126" t="n">
         <v>35.09157943725586</v>
       </c>
       <c r="C126" t="n">
-        <v>-15.93817806243896</v>
+        <v>-15.93817710876465</v>
       </c>
       <c r="D126" t="n">
         <v>33.10154724121094</v>
@@ -2957,12 +2957,12 @@
         <v>22.39847373962402</v>
       </c>
       <c r="F126" t="n">
-        <v>-3.51643967628479</v>
+        <v>-3.516439437866211</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-1.396151065826416</v>
+        <v>-1.396151781082153</v>
       </c>
       <c r="B127" t="n">
         <v>40.80989456176758</v>
@@ -2977,18 +2977,18 @@
         <v>22.90609550476074</v>
       </c>
       <c r="F127" t="n">
-        <v>-1.082040071487427</v>
+        <v>-1.082040190696716</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2.3663649559021</v>
+        <v>2.366365194320679</v>
       </c>
       <c r="B128" t="n">
         <v>46.96034240722656</v>
       </c>
       <c r="C128" t="n">
-        <v>-15.93325138092041</v>
+        <v>-15.93325233459473</v>
       </c>
       <c r="D128" t="n">
         <v>28.74524307250977</v>
@@ -2997,7 +2997,7 @@
         <v>22.43967628479004</v>
       </c>
       <c r="F128" t="n">
-        <v>0.9277579188346863</v>
+        <v>0.9277579784393311</v>
       </c>
     </row>
     <row r="129">
@@ -3011,7 +3011,7 @@
         <v>-12.10377597808838</v>
       </c>
       <c r="D129" t="n">
-        <v>25.94616889953613</v>
+        <v>25.9461669921875</v>
       </c>
       <c r="E129" t="n">
         <v>21.11116790771484</v>
@@ -3048,7 +3048,7 @@
         <v>59.98259735107422</v>
       </c>
       <c r="C131" t="n">
-        <v>-4.670528888702393</v>
+        <v>-4.670529365539551</v>
       </c>
       <c r="D131" t="n">
         <v>19.71154022216797</v>
@@ -3057,7 +3057,7 @@
         <v>15.97082328796387</v>
       </c>
       <c r="F131" t="n">
-        <v>3.661338567733765</v>
+        <v>3.661338806152344</v>
       </c>
     </row>
     <row r="132">
@@ -3065,10 +3065,10 @@
         <v>18.74056243896484</v>
       </c>
       <c r="B132" t="n">
-        <v>60.46043395996094</v>
+        <v>60.4604377746582</v>
       </c>
       <c r="C132" t="n">
-        <v>-1.584898591041565</v>
+        <v>-1.584898471832275</v>
       </c>
       <c r="D132" t="n">
         <v>16.54908752441406</v>
@@ -3077,7 +3077,7 @@
         <v>12.57655620574951</v>
       </c>
       <c r="F132" t="n">
-        <v>3.573920488357544</v>
+        <v>3.573920726776123</v>
       </c>
     </row>
     <row r="133">
@@ -3091,10 +3091,10 @@
         <v>0.9838740229606628</v>
       </c>
       <c r="D133" t="n">
-        <v>13.53958034515381</v>
+        <v>13.53957939147949</v>
       </c>
       <c r="E133" t="n">
-        <v>9.315546035766602</v>
+        <v>9.315545082092285</v>
       </c>
       <c r="F133" t="n">
         <v>3.446647882461548</v>
@@ -3125,16 +3125,16 @@
         <v>26.39323425292969</v>
       </c>
       <c r="B135" t="n">
-        <v>49.66505432128906</v>
+        <v>49.6650505065918</v>
       </c>
       <c r="C135" t="n">
-        <v>4.161262989044189</v>
+        <v>4.161262512207031</v>
       </c>
       <c r="D135" t="n">
         <v>8.238372802734375</v>
       </c>
       <c r="E135" t="n">
-        <v>4.813408851623535</v>
+        <v>4.813408374786377</v>
       </c>
       <c r="F135" t="n">
         <v>4.110961437225342</v>
@@ -3145,16 +3145,16 @@
         <v>27.6330451965332</v>
       </c>
       <c r="B136" t="n">
-        <v>42.70198059082031</v>
+        <v>42.70197677612305</v>
       </c>
       <c r="C136" t="n">
-        <v>4.564177989959717</v>
+        <v>4.564177513122559</v>
       </c>
       <c r="D136" t="n">
-        <v>5.868977546691895</v>
+        <v>5.868978500366211</v>
       </c>
       <c r="E136" t="n">
-        <v>3.620649099349976</v>
+        <v>3.620649814605713</v>
       </c>
       <c r="F136" t="n">
         <v>4.976856231689453</v>
@@ -3165,19 +3165,19 @@
         <v>28.21785545349121</v>
       </c>
       <c r="B137" t="n">
-        <v>34.6121940612793</v>
+        <v>34.61219024658203</v>
       </c>
       <c r="C137" t="n">
-        <v>3.94160270690918</v>
+        <v>3.941602945327759</v>
       </c>
       <c r="D137" t="n">
-        <v>3.520481109619141</v>
+        <v>3.52048134803772</v>
       </c>
       <c r="E137" t="n">
-        <v>2.802448034286499</v>
+        <v>2.80244779586792</v>
       </c>
       <c r="F137" t="n">
-        <v>6.032257556915283</v>
+        <v>6.032258033752441</v>
       </c>
     </row>
     <row r="138">
@@ -3185,16 +3185,16 @@
         <v>28.27294540405273</v>
       </c>
       <c r="B138" t="n">
-        <v>26.09273529052734</v>
+        <v>26.09273719787598</v>
       </c>
       <c r="C138" t="n">
-        <v>2.113990545272827</v>
+        <v>2.113991022109985</v>
       </c>
       <c r="D138" t="n">
-        <v>1.052264213562012</v>
+        <v>1.052263617515564</v>
       </c>
       <c r="E138" t="n">
-        <v>2.05617880821228</v>
+        <v>2.056179046630859</v>
       </c>
       <c r="F138" t="n">
         <v>7.116894721984863</v>
@@ -3202,19 +3202,19 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>28.0478343963623</v>
+        <v>28.04783248901367</v>
       </c>
       <c r="B139" t="n">
         <v>17.96771049499512</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.3512795865535736</v>
+        <v>-0.3512795567512512</v>
       </c>
       <c r="D139" t="n">
-        <v>-1.60366153717041</v>
+        <v>-1.603662133216858</v>
       </c>
       <c r="E139" t="n">
-        <v>1.198739886283875</v>
+        <v>1.198741316795349</v>
       </c>
       <c r="F139" t="n">
         <v>8.126598358154297</v>
@@ -3228,13 +3228,13 @@
         <v>10.77225208282471</v>
       </c>
       <c r="C140" t="n">
-        <v>-2.090726137161255</v>
+        <v>-2.090726375579834</v>
       </c>
       <c r="D140" t="n">
-        <v>-4.394652366638184</v>
+        <v>-4.394652843475342</v>
       </c>
       <c r="E140" t="n">
-        <v>0.2495440244674683</v>
+        <v>0.249543771147728</v>
       </c>
       <c r="F140" t="n">
         <v>9.045049667358398</v>
@@ -3245,16 +3245,16 @@
         <v>27.80424690246582</v>
       </c>
       <c r="B141" t="n">
-        <v>4.871070384979248</v>
+        <v>4.871069431304932</v>
       </c>
       <c r="C141" t="n">
         <v>-2.135699987411499</v>
       </c>
       <c r="D141" t="n">
-        <v>-7.160786628723145</v>
+        <v>-7.160787105560303</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.5786248445510864</v>
+        <v>-0.5786239504814148</v>
       </c>
       <c r="F141" t="n">
         <v>9.931349754333496</v>
@@ -3265,16 +3265,16 @@
         <v>28.07055282592773</v>
       </c>
       <c r="B142" t="n">
-        <v>0.7866901755332947</v>
+        <v>0.7866889238357544</v>
       </c>
       <c r="C142" t="n">
-        <v>-1.026734232902527</v>
+        <v>-1.026734113693237</v>
       </c>
       <c r="D142" t="n">
-        <v>-9.702609062194824</v>
+        <v>-9.702610015869141</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.9846574068069458</v>
+        <v>-0.9846556782722473</v>
       </c>
       <c r="F142" t="n">
         <v>10.85061550140381</v>
@@ -3285,16 +3285,16 @@
         <v>28.51385307312012</v>
       </c>
       <c r="B143" t="n">
-        <v>-1.003869533538818</v>
+        <v>-1.003868937492371</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.2127651870250702</v>
+        <v>-0.2127652913331985</v>
       </c>
       <c r="D143" t="n">
-        <v>-11.85473346710205</v>
+        <v>-11.85473442077637</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.7114602327346802</v>
+        <v>-0.711459219455719</v>
       </c>
       <c r="F143" t="n">
         <v>11.77196598052979</v>
@@ -3302,19 +3302,19 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>28.97129249572754</v>
+        <v>28.97129058837891</v>
       </c>
       <c r="B144" t="n">
-        <v>-0.5029197335243225</v>
+        <v>-0.5029195547103882</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.8536676168441772</v>
+        <v>-0.8536675572395325</v>
       </c>
       <c r="D144" t="n">
-        <v>-13.51886463165283</v>
+        <v>-13.51886367797852</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3758162260055542</v>
+        <v>0.3758165836334229</v>
       </c>
       <c r="F144" t="n">
         <v>12.52795505523682</v>
@@ -3325,39 +3325,39 @@
         <v>29.36255645751953</v>
       </c>
       <c r="B145" t="n">
-        <v>1.839622974395752</v>
+        <v>1.8396235704422</v>
       </c>
       <c r="C145" t="n">
-        <v>-3.068986415863037</v>
+        <v>-3.068986654281616</v>
       </c>
       <c r="D145" t="n">
-        <v>-14.64296817779541</v>
+        <v>-14.64296722412109</v>
       </c>
       <c r="E145" t="n">
-        <v>2.299873113632202</v>
+        <v>2.299871921539307</v>
       </c>
       <c r="F145" t="n">
-        <v>12.81040573120117</v>
+        <v>12.81040668487549</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>29.6961727142334</v>
+        <v>29.69617080688477</v>
       </c>
       <c r="B146" t="n">
-        <v>5.257265567779541</v>
+        <v>5.257266044616699</v>
       </c>
       <c r="C146" t="n">
         <v>-5.918110847473145</v>
       </c>
       <c r="D146" t="n">
-        <v>-15.17396450042725</v>
+        <v>-15.17396354675293</v>
       </c>
       <c r="E146" t="n">
-        <v>5.042629241943359</v>
+        <v>5.042630195617676</v>
       </c>
       <c r="F146" t="n">
-        <v>12.13060283660889</v>
+        <v>12.1306037902832</v>
       </c>
     </row>
     <row r="147">
@@ -3365,13 +3365,13 @@
         <v>29.99117279052734</v>
       </c>
       <c r="B147" t="n">
-        <v>9.06926155090332</v>
+        <v>9.069262504577637</v>
       </c>
       <c r="C147" t="n">
-        <v>-8.310957908630371</v>
+        <v>-8.310956954956055</v>
       </c>
       <c r="D147" t="n">
-        <v>-15.02948665618896</v>
+        <v>-15.02948379516602</v>
       </c>
       <c r="E147" t="n">
         <v>8.586936950683594</v>
@@ -3385,7 +3385,7 @@
         <v>31.54406356811523</v>
       </c>
       <c r="B148" t="n">
-        <v>9.519938468933105</v>
+        <v>9.519939422607422</v>
       </c>
       <c r="C148" t="n">
         <v>-5.253461837768555</v>
@@ -3394,7 +3394,7 @@
         <v>-16.38406562805176</v>
       </c>
       <c r="E148" t="n">
-        <v>15.58547306060791</v>
+        <v>15.58547210693359</v>
       </c>
       <c r="F148" t="n">
         <v>3.728344440460205</v>
@@ -3408,16 +3408,16 @@
         <v>13.56563663482666</v>
       </c>
       <c r="C149" t="n">
-        <v>-6.814529418945312</v>
+        <v>-6.814529895782471</v>
       </c>
       <c r="D149" t="n">
-        <v>-14.68702602386475</v>
+        <v>-14.68702507019043</v>
       </c>
       <c r="E149" t="n">
         <v>20.53302955627441</v>
       </c>
       <c r="F149" t="n">
-        <v>-3.462053537368774</v>
+        <v>-3.462053775787354</v>
       </c>
     </row>
     <row r="150">
@@ -3428,16 +3428,16 @@
         <v>17.58968925476074</v>
       </c>
       <c r="C150" t="n">
-        <v>-6.087905406951904</v>
+        <v>-6.087905883789062</v>
       </c>
       <c r="D150" t="n">
-        <v>-12.21683406829834</v>
+        <v>-12.21683502197266</v>
       </c>
       <c r="E150" t="n">
         <v>26.19644546508789</v>
       </c>
       <c r="F150" t="n">
-        <v>-10.8934326171875</v>
+        <v>-10.89343166351318</v>
       </c>
     </row>
     <row r="151">
@@ -3451,10 +3451,10 @@
         <v>-3.894246101379395</v>
       </c>
       <c r="D151" t="n">
-        <v>-9.04216480255127</v>
+        <v>-9.042163848876953</v>
       </c>
       <c r="E151" t="n">
-        <v>32.63379287719727</v>
+        <v>32.63379669189453</v>
       </c>
       <c r="F151" t="n">
         <v>-15.12951183319092</v>
@@ -3462,19 +3462,19 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>29.98164367675781</v>
+        <v>29.98164176940918</v>
       </c>
       <c r="B152" t="n">
         <v>21.23181533813477</v>
       </c>
       <c r="C152" t="n">
-        <v>-1.496067404747009</v>
+        <v>-1.496067523956299</v>
       </c>
       <c r="D152" t="n">
-        <v>-5.264573097229004</v>
+        <v>-5.264573574066162</v>
       </c>
       <c r="E152" t="n">
-        <v>39.5506706237793</v>
+        <v>39.55067443847656</v>
       </c>
       <c r="F152" t="n">
         <v>-14.74899578094482</v>
@@ -3482,22 +3482,22 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>27.88022232055664</v>
+        <v>27.88022422790527</v>
       </c>
       <c r="B153" t="n">
-        <v>20.17507171630859</v>
+        <v>20.17507362365723</v>
       </c>
       <c r="C153" t="n">
-        <v>0.5703037977218628</v>
+        <v>0.5703038573265076</v>
       </c>
       <c r="D153" t="n">
-        <v>-1.041567802429199</v>
+        <v>-1.041566491127014</v>
       </c>
       <c r="E153" t="n">
-        <v>46.14776611328125</v>
+        <v>46.14776992797852</v>
       </c>
       <c r="F153" t="n">
-        <v>-11.42673778533936</v>
+        <v>-11.42673683166504</v>
       </c>
     </row>
     <row r="154">
@@ -3511,13 +3511,13 @@
         <v>2.348687410354614</v>
       </c>
       <c r="D154" t="n">
-        <v>3.397652626037598</v>
+        <v>3.397652864456177</v>
       </c>
       <c r="E154" t="n">
-        <v>51.44086456298828</v>
+        <v>51.44086837768555</v>
       </c>
       <c r="F154" t="n">
-        <v>-7.19111442565918</v>
+        <v>-7.191113471984863</v>
       </c>
     </row>
     <row r="155">
@@ -3525,19 +3525,19 @@
         <v>23.05442810058594</v>
       </c>
       <c r="B155" t="n">
-        <v>17.74554443359375</v>
+        <v>17.74554634094238</v>
       </c>
       <c r="C155" t="n">
         <v>3.941469430923462</v>
       </c>
       <c r="D155" t="n">
-        <v>7.778188705444336</v>
+        <v>7.778189182281494</v>
       </c>
       <c r="E155" t="n">
-        <v>54.73609924316406</v>
+        <v>54.73610305786133</v>
       </c>
       <c r="F155" t="n">
-        <v>-3.261296033859253</v>
+        <v>-3.261296272277832</v>
       </c>
     </row>
     <row r="156">
@@ -3545,10 +3545,10 @@
         <v>20.6888542175293</v>
       </c>
       <c r="B156" t="n">
-        <v>16.87634658813477</v>
+        <v>16.8763484954834</v>
       </c>
       <c r="C156" t="n">
-        <v>5.218241691589355</v>
+        <v>5.218240737915039</v>
       </c>
       <c r="D156" t="n">
         <v>11.83971405029297</v>
@@ -3557,7 +3557,7 @@
         <v>55.75179290771484</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.3778262138366699</v>
+        <v>-0.3778262734413147</v>
       </c>
     </row>
     <row r="157">
@@ -3574,7 +3574,7 @@
         <v>15.39380836486816</v>
       </c>
       <c r="E157" t="n">
-        <v>54.52459335327148</v>
+        <v>54.52459716796875</v>
       </c>
       <c r="F157" t="n">
         <v>1.284101843833923</v>
@@ -3588,7 +3588,7 @@
         <v>12.19329643249512</v>
       </c>
       <c r="C158" t="n">
-        <v>6.097338676452637</v>
+        <v>6.097338199615479</v>
       </c>
       <c r="D158" t="n">
         <v>18.33919906616211</v>
@@ -3614,7 +3614,7 @@
         <v>20.63563919067383</v>
       </c>
       <c r="E159" t="n">
-        <v>46.60110473632812</v>
+        <v>46.60110855102539</v>
       </c>
       <c r="F159" t="n">
         <v>2.507671356201172</v>
@@ -3634,7 +3634,7 @@
         <v>22.26494598388672</v>
       </c>
       <c r="E160" t="n">
-        <v>40.71825408935547</v>
+        <v>40.71825790405273</v>
       </c>
       <c r="F160" t="n">
         <v>2.807422637939453</v>
@@ -3642,53 +3642,53 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>6.7396559715271</v>
+        <v>6.739656925201416</v>
       </c>
       <c r="B161" t="n">
         <v>3.490407466888428</v>
       </c>
       <c r="C161" t="n">
-        <v>5.840417861938477</v>
+        <v>5.840417385101318</v>
       </c>
       <c r="D161" t="n">
         <v>23.23067855834961</v>
       </c>
       <c r="E161" t="n">
-        <v>33.95138168334961</v>
+        <v>33.95138549804688</v>
       </c>
       <c r="F161" t="n">
-        <v>2.880633592605591</v>
+        <v>2.88063383102417</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>4.034048557281494</v>
+        <v>4.034049034118652</v>
       </c>
       <c r="B162" t="n">
-        <v>1.854010105133057</v>
+        <v>1.854010224342346</v>
       </c>
       <c r="C162" t="n">
         <v>6.303715229034424</v>
       </c>
       <c r="D162" t="n">
-        <v>23.57231140136719</v>
+        <v>23.57231330871582</v>
       </c>
       <c r="E162" t="n">
         <v>26.44856643676758</v>
       </c>
       <c r="F162" t="n">
-        <v>2.463344573974609</v>
+        <v>2.463344812393188</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1.425792217254639</v>
+        <v>1.425791501998901</v>
       </c>
       <c r="B163" t="n">
-        <v>0.7336048483848572</v>
+        <v>0.7336055040359497</v>
       </c>
       <c r="C163" t="n">
-        <v>7.104920387268066</v>
+        <v>7.104920864105225</v>
       </c>
       <c r="D163" t="n">
         <v>23.39044952392578</v>
@@ -3702,13 +3702,13 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>-1.037214756011963</v>
+        <v>-1.037214517593384</v>
       </c>
       <c r="B164" t="n">
-        <v>0.1136936694383621</v>
+        <v>0.1136942803859711</v>
       </c>
       <c r="C164" t="n">
-        <v>8.180473327636719</v>
+        <v>8.180474281311035</v>
       </c>
       <c r="D164" t="n">
         <v>22.88499069213867</v>
@@ -3717,35 +3717,35 @@
         <v>10.24388885498047</v>
       </c>
       <c r="F164" t="n">
-        <v>0.1576207727193832</v>
+        <v>0.1576207131147385</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>-3.284033298492432</v>
+        <v>-3.284034967422485</v>
       </c>
       <c r="B165" t="n">
-        <v>0.001717048115096986</v>
+        <v>0.001715275808237493</v>
       </c>
       <c r="C165" t="n">
-        <v>9.489165306091309</v>
+        <v>9.489166259765625</v>
       </c>
       <c r="D165" t="n">
         <v>22.33822822570801</v>
       </c>
       <c r="E165" t="n">
-        <v>2.711742162704468</v>
+        <v>2.711741209030151</v>
       </c>
       <c r="F165" t="n">
-        <v>-1.176342248916626</v>
+        <v>-1.176342129707336</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>-5.258308887481689</v>
+        <v>-5.25831127166748</v>
       </c>
       <c r="B166" t="n">
-        <v>0.366941899061203</v>
+        <v>0.3669415414333344</v>
       </c>
       <c r="C166" t="n">
         <v>10.97675132751465</v>
@@ -3754,7 +3754,7 @@
         <v>22.03657150268555</v>
       </c>
       <c r="E166" t="n">
-        <v>-3.219660043716431</v>
+        <v>-3.219659090042114</v>
       </c>
       <c r="F166" t="n">
         <v>-2.145746231079102</v>
@@ -3762,30 +3762,30 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>-6.931873798370361</v>
+        <v>-6.931876182556152</v>
       </c>
       <c r="B167" t="n">
-        <v>1.16355562210083</v>
+        <v>1.16355574131012</v>
       </c>
       <c r="C167" t="n">
-        <v>12.52114677429199</v>
+        <v>12.52114868164062</v>
       </c>
       <c r="D167" t="n">
         <v>22.16421890258789</v>
       </c>
       <c r="E167" t="n">
-        <v>-6.596500396728516</v>
+        <v>-6.596498966217041</v>
       </c>
       <c r="F167" t="n">
-        <v>-2.28312611579895</v>
+        <v>-2.283126354217529</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>-8.331480979919434</v>
+        <v>-8.331479072570801</v>
       </c>
       <c r="B168" t="n">
-        <v>2.322123050689697</v>
+        <v>2.322122573852539</v>
       </c>
       <c r="C168" t="n">
         <v>13.89237785339355</v>
@@ -3794,18 +3794,18 @@
         <v>22.73730087280273</v>
       </c>
       <c r="E168" t="n">
-        <v>-6.938131332397461</v>
+        <v>-6.938131809234619</v>
       </c>
       <c r="F168" t="n">
-        <v>-1.426787376403809</v>
+        <v>-1.426787734031677</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>-9.535002708435059</v>
+        <v>-9.535000801086426</v>
       </c>
       <c r="B169" t="n">
-        <v>3.765029430389404</v>
+        <v>3.765028715133667</v>
       </c>
       <c r="C169" t="n">
         <v>14.76055717468262</v>
@@ -3814,50 +3814,50 @@
         <v>23.60786247253418</v>
       </c>
       <c r="E169" t="n">
-        <v>-4.543468475341797</v>
+        <v>-4.54347038269043</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.1620659977197647</v>
+        <v>-0.162066176533699</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>-10.57363796234131</v>
+        <v>-10.57363605499268</v>
       </c>
       <c r="B170" t="n">
         <v>5.563311100006104</v>
       </c>
       <c r="C170" t="n">
-        <v>14.90998363494873</v>
+        <v>14.90998458862305</v>
       </c>
       <c r="D170" t="n">
         <v>24.52619743347168</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.4279881715774536</v>
+        <v>-0.4279866814613342</v>
       </c>
       <c r="F170" t="n">
-        <v>0.3658528327941895</v>
+        <v>0.3658528923988342</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>-11.3001127243042</v>
+        <v>-11.30011081695557</v>
       </c>
       <c r="B171" t="n">
         <v>8.095279693603516</v>
       </c>
       <c r="C171" t="n">
-        <v>14.31983089447021</v>
+        <v>14.3198299407959</v>
       </c>
       <c r="D171" t="n">
         <v>25.26074409484863</v>
       </c>
       <c r="E171" t="n">
-        <v>4.073112487792969</v>
+        <v>4.073112964630127</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.8365252017974854</v>
+        <v>-0.8365252614021301</v>
       </c>
     </row>
     <row r="172">
@@ -3868,7 +3868,7 @@
         <v>11.79491806030273</v>
       </c>
       <c r="C172" t="n">
-        <v>12.81716442108154</v>
+        <v>12.81716346740723</v>
       </c>
       <c r="D172" t="n">
         <v>25.69961166381836</v>
@@ -3877,7 +3877,7 @@
         <v>8.02421760559082</v>
       </c>
       <c r="F172" t="n">
-        <v>-3.660946130752563</v>
+        <v>-3.660946369171143</v>
       </c>
     </row>
     <row r="173">
@@ -3888,33 +3888,33 @@
         <v>16.67897987365723</v>
       </c>
       <c r="C173" t="n">
-        <v>9.598138809204102</v>
+        <v>9.598139762878418</v>
       </c>
       <c r="D173" t="n">
-        <v>32.68849563598633</v>
+        <v>32.68849945068359</v>
       </c>
       <c r="E173" t="n">
-        <v>8.486339569091797</v>
+        <v>8.48633861541748</v>
       </c>
       <c r="F173" t="n">
-        <v>-5.689915180206299</v>
+        <v>-5.689914226531982</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>-9.259345054626465</v>
+        <v>-9.259343147277832</v>
       </c>
       <c r="B174" t="n">
-        <v>22.20937538146973</v>
+        <v>22.20937728881836</v>
       </c>
       <c r="C174" t="n">
-        <v>3.373810291290283</v>
+        <v>3.373810052871704</v>
       </c>
       <c r="D174" t="n">
         <v>32.64299774169922</v>
       </c>
       <c r="E174" t="n">
-        <v>11.3834114074707</v>
+        <v>11.38341236114502</v>
       </c>
       <c r="F174" t="n">
         <v>-8.159849166870117</v>
@@ -3922,33 +3922,33 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>-7.096271991729736</v>
+        <v>-7.096268653869629</v>
       </c>
       <c r="B175" t="n">
         <v>27.70474433898926</v>
       </c>
       <c r="C175" t="n">
-        <v>-6.226450443267822</v>
+        <v>-6.22645092010498</v>
       </c>
       <c r="D175" t="n">
-        <v>32.31375503540039</v>
+        <v>32.31375122070312</v>
       </c>
       <c r="E175" t="n">
-        <v>14.44857597351074</v>
+        <v>14.44857692718506</v>
       </c>
       <c r="F175" t="n">
-        <v>-8.25111198425293</v>
+        <v>-8.251111030578613</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>-4.484146595001221</v>
+        <v>-4.484148979187012</v>
       </c>
       <c r="B176" t="n">
         <v>32.8923454284668</v>
       </c>
       <c r="C176" t="n">
-        <v>-16.23049163818359</v>
+        <v>-16.23049354553223</v>
       </c>
       <c r="D176" t="n">
         <v>31.57661247253418</v>
@@ -3957,12 +3957,12 @@
         <v>17.25416564941406</v>
       </c>
       <c r="F176" t="n">
-        <v>-6.346749305725098</v>
+        <v>-6.346748352050781</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>-1.416090488433838</v>
+        <v>-1.416091203689575</v>
       </c>
       <c r="B177" t="n">
         <v>38.13530731201172</v>
@@ -3977,18 +3977,18 @@
         <v>18.87170600891113</v>
       </c>
       <c r="F177" t="n">
-        <v>-3.829888105392456</v>
+        <v>-3.829888343811035</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2.237298488616943</v>
+        <v>2.237297773361206</v>
       </c>
       <c r="B178" t="n">
-        <v>43.94398498535156</v>
+        <v>43.9439811706543</v>
       </c>
       <c r="C178" t="n">
-        <v>-19.91087913513184</v>
+        <v>-19.91088104248047</v>
       </c>
       <c r="D178" t="n">
         <v>28.22435760498047</v>
@@ -3997,18 +3997,18 @@
         <v>18.90406799316406</v>
       </c>
       <c r="F178" t="n">
-        <v>-1.596175909042358</v>
+        <v>-1.596176028251648</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>6.468019008636475</v>
+        <v>6.468019485473633</v>
       </c>
       <c r="B179" t="n">
-        <v>49.97467803955078</v>
+        <v>49.97467422485352</v>
       </c>
       <c r="C179" t="n">
-        <v>-15.13061809539795</v>
+        <v>-15.13061714172363</v>
       </c>
       <c r="D179" t="n">
         <v>25.58613395690918</v>
@@ -4017,18 +4017,18 @@
         <v>17.6115550994873</v>
       </c>
       <c r="F179" t="n">
-        <v>0.1107644960284233</v>
+        <v>0.1107644364237785</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>10.96612358093262</v>
+        <v>10.96612453460693</v>
       </c>
       <c r="B180" t="n">
-        <v>55.12076187133789</v>
+        <v>55.12075805664062</v>
       </c>
       <c r="C180" t="n">
-        <v>-10.08662223815918</v>
+        <v>-10.08662128448486</v>
       </c>
       <c r="D180" t="n">
         <v>22.49532127380371</v>
@@ -4057,7 +4057,7 @@
         <v>12.51554584503174</v>
       </c>
       <c r="F181" t="n">
-        <v>1.792785048484802</v>
+        <v>1.792785167694092</v>
       </c>
     </row>
     <row r="182">
@@ -4068,10 +4068,10 @@
         <v>59.81311416625977</v>
       </c>
       <c r="C182" t="n">
-        <v>-1.806279063224792</v>
+        <v>-1.806279182434082</v>
       </c>
       <c r="D182" t="n">
-        <v>15.68352031707764</v>
+        <v>15.68352127075195</v>
       </c>
       <c r="E182" t="n">
         <v>9.148778915405273</v>
@@ -4082,13 +4082,13 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>22.31101608276367</v>
+        <v>22.31101417541504</v>
       </c>
       <c r="B183" t="n">
         <v>58.86860275268555</v>
       </c>
       <c r="C183" t="n">
-        <v>1.378900766372681</v>
+        <v>1.378900647163391</v>
       </c>
       <c r="D183" t="n">
         <v>12.30996417999268</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>24.83685302734375</v>
+        <v>24.83685111999512</v>
       </c>
       <c r="B184" t="n">
         <v>55.77118301391602</v>
@@ -4111,10 +4111,10 @@
         <v>3.534459352493286</v>
       </c>
       <c r="D184" t="n">
-        <v>9.164273262023926</v>
+        <v>9.164272308349609</v>
       </c>
       <c r="E184" t="n">
-        <v>2.783321142196655</v>
+        <v>2.783321380615234</v>
       </c>
       <c r="F184" t="n">
         <v>1.266554474830627</v>
@@ -4131,10 +4131,10 @@
         <v>4.55280876159668</v>
       </c>
       <c r="D185" t="n">
-        <v>6.332697868347168</v>
+        <v>6.332698345184326</v>
       </c>
       <c r="E185" t="n">
-        <v>0.7093313932418823</v>
+        <v>0.7093322277069092</v>
       </c>
       <c r="F185" t="n">
         <v>1.73780083656311</v>
@@ -4148,16 +4148,16 @@
         <v>43.93780517578125</v>
       </c>
       <c r="C186" t="n">
-        <v>4.741434574127197</v>
+        <v>4.741434097290039</v>
       </c>
       <c r="D186" t="n">
-        <v>3.81613826751709</v>
+        <v>3.816138505935669</v>
       </c>
       <c r="E186" t="n">
-        <v>-0.4160405397415161</v>
+        <v>-0.4160407781600952</v>
       </c>
       <c r="F186" t="n">
-        <v>2.777571201324463</v>
+        <v>2.777571439743042</v>
       </c>
     </row>
     <row r="187">
@@ -4165,19 +4165,19 @@
         <v>28.36192321777344</v>
       </c>
       <c r="B187" t="n">
-        <v>35.76748275756836</v>
+        <v>35.76747894287109</v>
       </c>
       <c r="C187" t="n">
         <v>4.211514472961426</v>
       </c>
       <c r="D187" t="n">
-        <v>1.530478477478027</v>
+        <v>1.530478835105896</v>
       </c>
       <c r="E187" t="n">
-        <v>-0.7764493227005005</v>
+        <v>-0.7764489054679871</v>
       </c>
       <c r="F187" t="n">
-        <v>4.180874347686768</v>
+        <v>4.180874824523926</v>
       </c>
     </row>
     <row r="188">
@@ -4188,13 +4188,13 @@
         <v>26.79880714416504</v>
       </c>
       <c r="C188" t="n">
-        <v>2.734725952148438</v>
+        <v>2.734726190567017</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.653073251247406</v>
+        <v>-0.6530730128288269</v>
       </c>
       <c r="E188" t="n">
-        <v>-0.6808949708938599</v>
+        <v>-0.6808953881263733</v>
       </c>
       <c r="F188" t="n">
         <v>5.72688102722168</v>
@@ -4208,16 +4208,16 @@
         <v>17.97307205200195</v>
       </c>
       <c r="C189" t="n">
-        <v>0.3599956333637238</v>
+        <v>0.3599957823753357</v>
       </c>
       <c r="D189" t="n">
-        <v>-2.848420143127441</v>
+        <v>-2.848418951034546</v>
       </c>
       <c r="E189" t="n">
-        <v>-0.4013558626174927</v>
+        <v>-0.4013574719429016</v>
       </c>
       <c r="F189" t="n">
-        <v>7.26746129989624</v>
+        <v>7.267462253570557</v>
       </c>
     </row>
     <row r="190">
@@ -4225,19 +4225,19 @@
         <v>27.27387237548828</v>
       </c>
       <c r="B190" t="n">
-        <v>10.137131690979</v>
+        <v>10.13713264465332</v>
       </c>
       <c r="C190" t="n">
         <v>-2.001528024673462</v>
       </c>
       <c r="D190" t="n">
-        <v>-5.111008644104004</v>
+        <v>-5.111007213592529</v>
       </c>
       <c r="E190" t="n">
-        <v>-0.09692776203155518</v>
+        <v>-0.09692789614200592</v>
       </c>
       <c r="F190" t="n">
-        <v>8.719694137573242</v>
+        <v>8.719693183898926</v>
       </c>
     </row>
     <row r="191">
@@ -4245,16 +4245,16 @@
         <v>27.07018280029297</v>
       </c>
       <c r="B191" t="n">
-        <v>3.845995426177979</v>
+        <v>3.845994710922241</v>
       </c>
       <c r="C191" t="n">
-        <v>-3.156124591827393</v>
+        <v>-3.156124830245972</v>
       </c>
       <c r="D191" t="n">
-        <v>-7.423369407653809</v>
+        <v>-7.423369884490967</v>
       </c>
       <c r="E191" t="n">
-        <v>0.1920355558395386</v>
+        <v>0.1920343488454819</v>
       </c>
       <c r="F191" t="n">
         <v>10.03079605102539</v>
@@ -4265,16 +4265,16 @@
         <v>27.34112739562988</v>
       </c>
       <c r="B192" t="n">
-        <v>-0.3549018204212189</v>
+        <v>-0.3549021780490875</v>
       </c>
       <c r="C192" t="n">
-        <v>-2.798229694366455</v>
+        <v>-2.798229932785034</v>
       </c>
       <c r="D192" t="n">
-        <v>-9.715960502624512</v>
+        <v>-9.715959548950195</v>
       </c>
       <c r="E192" t="n">
-        <v>0.5040949583053589</v>
+        <v>0.5040943622589111</v>
       </c>
       <c r="F192" t="n">
         <v>11.13447856903076</v>
@@ -4285,16 +4285,16 @@
         <v>27.94517707824707</v>
       </c>
       <c r="B193" t="n">
-        <v>-2.091498851776123</v>
+        <v>-2.091499328613281</v>
       </c>
       <c r="C193" t="n">
         <v>-1.59312117099762</v>
       </c>
       <c r="D193" t="n">
-        <v>-11.89795780181885</v>
+        <v>-11.89795684814453</v>
       </c>
       <c r="E193" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314435720443726</v>
       </c>
       <c r="F193" t="n">
         <v>11.957594871521</v>
@@ -4305,16 +4305,16 @@
         <v>28.60050201416016</v>
       </c>
       <c r="B194" t="n">
-        <v>-1.584760189056396</v>
+        <v>-1.584759593009949</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.2559510171413422</v>
+        <v>-0.2559512257575989</v>
       </c>
       <c r="D194" t="n">
-        <v>-13.87221050262451</v>
+        <v>-13.8722095489502</v>
       </c>
       <c r="E194" t="n">
-        <v>1.631898760795593</v>
+        <v>1.631897807121277</v>
       </c>
       <c r="F194" t="n">
         <v>12.46585655212402</v>
@@ -4325,16 +4325,16 @@
         <v>29.13460350036621</v>
       </c>
       <c r="B195" t="n">
-        <v>0.5982822775840759</v>
+        <v>0.5982815027236938</v>
       </c>
       <c r="C195" t="n">
-        <v>0.6736176013946533</v>
+        <v>0.6736177802085876</v>
       </c>
       <c r="D195" t="n">
-        <v>-15.52835750579834</v>
+        <v>-15.52835655212402</v>
       </c>
       <c r="E195" t="n">
-        <v>2.841628789901733</v>
+        <v>2.841629028320312</v>
       </c>
       <c r="F195" t="n">
         <v>12.65200805664062</v>
@@ -4345,16 +4345,16 @@
         <v>29.48074150085449</v>
       </c>
       <c r="B196" t="n">
-        <v>3.644351482391357</v>
+        <v>3.644351005554199</v>
       </c>
       <c r="C196" t="n">
-        <v>0.4265215694904327</v>
+        <v>0.4265217185020447</v>
       </c>
       <c r="D196" t="n">
         <v>-16.73695182800293</v>
       </c>
       <c r="E196" t="n">
-        <v>4.801170349121094</v>
+        <v>4.801170825958252</v>
       </c>
       <c r="F196" t="n">
         <v>12.40149021148682</v>
@@ -4362,7 +4362,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>29.63055992126465</v>
+        <v>29.63055801391602</v>
       </c>
       <c r="B197" t="n">
         <v>6.670427799224854</v>
@@ -4371,13 +4371,13 @@
         <v>-1.718868374824524</v>
       </c>
       <c r="D197" t="n">
-        <v>-17.35958290100098</v>
+        <v>-17.35958480834961</v>
       </c>
       <c r="E197" t="n">
-        <v>7.625986099243164</v>
+        <v>7.625985145568848</v>
       </c>
       <c r="F197" t="n">
-        <v>11.31737518310547</v>
+        <v>11.31737422943115</v>
       </c>
     </row>
     <row r="198">
@@ -4385,10 +4385,10 @@
         <v>29.68305587768555</v>
       </c>
       <c r="B198" t="n">
-        <v>9.641530990600586</v>
+        <v>9.641531944274902</v>
       </c>
       <c r="C198" t="n">
-        <v>-4.753839015960693</v>
+        <v>-4.753839492797852</v>
       </c>
       <c r="D198" t="n">
         <v>-17.27353096008301</v>
@@ -4405,7 +4405,7 @@
         <v>32.72341537475586</v>
       </c>
       <c r="B199" t="n">
-        <v>8.115839004516602</v>
+        <v>8.115839958190918</v>
       </c>
       <c r="C199" t="n">
         <v>-4.783977031707764</v>
@@ -4414,7 +4414,7 @@
         <v>-16.03171348571777</v>
       </c>
       <c r="E199" t="n">
-        <v>12.90883731842041</v>
+        <v>12.90883827209473</v>
       </c>
       <c r="F199" t="n">
         <v>2.589628219604492</v>
@@ -4428,10 +4428,10 @@
         <v>12.72963428497314</v>
       </c>
       <c r="C200" t="n">
-        <v>-6.459099769592285</v>
+        <v>-6.459100246429443</v>
       </c>
       <c r="D200" t="n">
-        <v>-14.21571063995361</v>
+        <v>-14.21571350097656</v>
       </c>
       <c r="E200" t="n">
         <v>18.38468551635742</v>
@@ -4445,19 +4445,19 @@
         <v>33.80759811401367</v>
       </c>
       <c r="B201" t="n">
-        <v>16.8465461730957</v>
+        <v>16.84654808044434</v>
       </c>
       <c r="C201" t="n">
-        <v>-6.288715839385986</v>
+        <v>-6.288716316223145</v>
       </c>
       <c r="D201" t="n">
-        <v>-11.67458438873291</v>
+        <v>-11.67458343505859</v>
       </c>
       <c r="E201" t="n">
         <v>24.25799369812012</v>
       </c>
       <c r="F201" t="n">
-        <v>-11.8911657333374</v>
+        <v>-11.89116477966309</v>
       </c>
     </row>
     <row r="202">
@@ -4471,18 +4471,18 @@
         <v>-4.581882476806641</v>
       </c>
       <c r="D202" t="n">
-        <v>-8.495539665222168</v>
+        <v>-8.495540618896484</v>
       </c>
       <c r="E202" t="n">
         <v>30.4012508392334</v>
       </c>
       <c r="F202" t="n">
-        <v>-17.53884506225586</v>
+        <v>-17.53884696960449</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>31.99574279785156</v>
+        <v>31.99574089050293</v>
       </c>
       <c r="B203" t="n">
         <v>20.23374176025391</v>
@@ -4491,13 +4491,13 @@
         <v>-2.28954005241394</v>
       </c>
       <c r="D203" t="n">
-        <v>-4.755084037780762</v>
+        <v>-4.755082607269287</v>
       </c>
       <c r="E203" t="n">
-        <v>36.70731353759766</v>
+        <v>36.70731735229492</v>
       </c>
       <c r="F203" t="n">
-        <v>-18.70958137512207</v>
+        <v>-18.7095832824707</v>
       </c>
     </row>
     <row r="204">
@@ -4508,56 +4508,56 @@
         <v>19.42002105712891</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.1829331815242767</v>
+        <v>-0.1829331666231155</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.5478314757347107</v>
+        <v>-0.5478312373161316</v>
       </c>
       <c r="E204" t="n">
-        <v>42.85980987548828</v>
+        <v>42.85981369018555</v>
       </c>
       <c r="F204" t="n">
-        <v>-16.22261619567871</v>
+        <v>-16.22262001037598</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>27.44333457946777</v>
+        <v>27.44333267211914</v>
       </c>
       <c r="B205" t="n">
         <v>17.82676696777344</v>
       </c>
       <c r="C205" t="n">
-        <v>1.404116630554199</v>
+        <v>1.40411651134491</v>
       </c>
       <c r="D205" t="n">
-        <v>3.977254867553711</v>
+        <v>3.97725510597229</v>
       </c>
       <c r="E205" t="n">
-        <v>48.2772102355957</v>
+        <v>48.27721405029297</v>
       </c>
       <c r="F205" t="n">
-        <v>-12.19832515716553</v>
+        <v>-12.19832420349121</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>24.69412994384766</v>
+        <v>24.69412803649902</v>
       </c>
       <c r="B206" t="n">
         <v>15.8731164932251</v>
       </c>
       <c r="C206" t="n">
-        <v>2.432731151580811</v>
+        <v>2.43273138999939</v>
       </c>
       <c r="D206" t="n">
         <v>8.617197036743164</v>
       </c>
       <c r="E206" t="n">
-        <v>52.35831451416016</v>
+        <v>52.35831832885742</v>
       </c>
       <c r="F206" t="n">
-        <v>-8.143244743347168</v>
+        <v>-8.143243789672852</v>
       </c>
     </row>
     <row r="207">
@@ -4565,19 +4565,19 @@
         <v>21.76468849182129</v>
       </c>
       <c r="B207" t="n">
-        <v>13.42293357849121</v>
+        <v>13.42293453216553</v>
       </c>
       <c r="C207" t="n">
-        <v>2.914615869522095</v>
+        <v>2.914616346359253</v>
       </c>
       <c r="D207" t="n">
         <v>13.1414623260498</v>
       </c>
       <c r="E207" t="n">
-        <v>54.70961380004883</v>
+        <v>54.70962142944336</v>
       </c>
       <c r="F207" t="n">
-        <v>-4.75229024887085</v>
+        <v>-4.752289772033691</v>
       </c>
     </row>
     <row r="208">
@@ -4585,7 +4585,7 @@
         <v>18.69356155395508</v>
       </c>
       <c r="B208" t="n">
-        <v>10.3438835144043</v>
+        <v>10.34388446807861</v>
       </c>
       <c r="C208" t="n">
         <v>2.92203688621521</v>
@@ -4605,19 +4605,19 @@
         <v>15.61940097808838</v>
       </c>
       <c r="B209" t="n">
-        <v>7.067324161529541</v>
+        <v>7.067324638366699</v>
       </c>
       <c r="C209" t="n">
-        <v>2.754967212677002</v>
+        <v>2.754967451095581</v>
       </c>
       <c r="D209" t="n">
         <v>21.07096099853516</v>
       </c>
       <c r="E209" t="n">
-        <v>53.99266052246094</v>
+        <v>53.9926643371582</v>
       </c>
       <c r="F209" t="n">
-        <v>0.2048963159322739</v>
+        <v>0.2048962563276291</v>
       </c>
     </row>
     <row r="210">
@@ -4625,7 +4625,7 @@
         <v>12.70389652252197</v>
       </c>
       <c r="B210" t="n">
-        <v>4.252721309661865</v>
+        <v>4.252721786499023</v>
       </c>
       <c r="C210" t="n">
         <v>2.780195474624634</v>
@@ -4634,7 +4634,7 @@
         <v>24.23367881774902</v>
       </c>
       <c r="E210" t="n">
-        <v>51.18368911743164</v>
+        <v>51.18369293212891</v>
       </c>
       <c r="F210" t="n">
         <v>2.188397407531738</v>
@@ -4642,10 +4642,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>9.996804237365723</v>
+        <v>9.996805191040039</v>
       </c>
       <c r="B211" t="n">
-        <v>2.210823535919189</v>
+        <v>2.210823059082031</v>
       </c>
       <c r="C211" t="n">
         <v>3.17165207862854</v>
@@ -4657,24 +4657,24 @@
         <v>46.96974182128906</v>
       </c>
       <c r="F211" t="n">
-        <v>3.746608018875122</v>
+        <v>3.746608257293701</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>7.427087306976318</v>
+        <v>7.427088260650635</v>
       </c>
       <c r="B212" t="n">
-        <v>0.8014644980430603</v>
+        <v>0.8014646768569946</v>
       </c>
       <c r="C212" t="n">
-        <v>3.840819358825684</v>
+        <v>3.840819597244263</v>
       </c>
       <c r="D212" t="n">
         <v>28.62588500976562</v>
       </c>
       <c r="E212" t="n">
-        <v>41.46113204956055</v>
+        <v>41.46113586425781</v>
       </c>
       <c r="F212" t="n">
         <v>4.496410846710205</v>
@@ -4685,7 +4685,7 @@
         <v>4.894728183746338</v>
       </c>
       <c r="B213" t="n">
-        <v>-0.2763762772083282</v>
+        <v>-0.2763780653476715</v>
       </c>
       <c r="C213" t="n">
         <v>4.592483997344971</v>
@@ -4697,24 +4697,24 @@
         <v>34.75399780273438</v>
       </c>
       <c r="F213" t="n">
-        <v>4.105072975158691</v>
+        <v>4.10507345199585</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>2.356503009796143</v>
+        <v>2.356503248214722</v>
       </c>
       <c r="B214" t="n">
-        <v>-1.204879283905029</v>
+        <v>-1.204878687858582</v>
       </c>
       <c r="C214" t="n">
-        <v>5.3277268409729</v>
+        <v>5.327726364135742</v>
       </c>
       <c r="D214" t="n">
-        <v>30.36335945129395</v>
+        <v>30.36335754394531</v>
       </c>
       <c r="E214" t="n">
-        <v>27.0286808013916</v>
+        <v>27.02868270874023</v>
       </c>
       <c r="F214" t="n">
         <v>2.539838552474976</v>
@@ -4722,13 +4722,13 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>-0.1404252350330353</v>
+        <v>-0.1404249519109726</v>
       </c>
       <c r="B215" t="n">
-        <v>-1.9502272605896</v>
+        <v>-1.950227618217468</v>
       </c>
       <c r="C215" t="n">
-        <v>6.122319221496582</v>
+        <v>6.122318744659424</v>
       </c>
       <c r="D215" t="n">
         <v>30.44340896606445</v>
@@ -4737,18 +4737,18 @@
         <v>18.66259574890137</v>
       </c>
       <c r="F215" t="n">
-        <v>0.275970458984375</v>
+        <v>0.2759703993797302</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>-2.472937107086182</v>
+        <v>-2.472936868667603</v>
       </c>
       <c r="B216" t="n">
-        <v>-2.305810451507568</v>
+        <v>-2.305811882019043</v>
       </c>
       <c r="C216" t="n">
-        <v>7.148920059204102</v>
+        <v>7.148919582366943</v>
       </c>
       <c r="D216" t="n">
         <v>30.28093338012695</v>
@@ -4757,15 +4757,15 @@
         <v>10.31049251556396</v>
       </c>
       <c r="F216" t="n">
-        <v>-1.903061389923096</v>
+        <v>-1.903061509132385</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>-4.500633716583252</v>
+        <v>-4.500632286071777</v>
       </c>
       <c r="B217" t="n">
-        <v>-2.013082027435303</v>
+        <v>-2.013080596923828</v>
       </c>
       <c r="C217" t="n">
         <v>8.541282653808594</v>
@@ -4774,18 +4774,18 @@
         <v>30.15394401550293</v>
       </c>
       <c r="E217" t="n">
-        <v>2.915609121322632</v>
+        <v>2.915609836578369</v>
       </c>
       <c r="F217" t="n">
-        <v>-3.395564794540405</v>
+        <v>-3.395565032958984</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>-6.168215274810791</v>
+        <v>-6.168215751647949</v>
       </c>
       <c r="B218" t="n">
-        <v>-0.9690757393836975</v>
+        <v>-0.969075083732605</v>
       </c>
       <c r="C218" t="n">
         <v>10.24686908721924</v>
@@ -4797,32 +4797,32 @@
         <v>-2.425783395767212</v>
       </c>
       <c r="F218" t="n">
-        <v>-3.991297006607056</v>
+        <v>-3.991297245025635</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>-7.530977725982666</v>
+        <v>-7.530978202819824</v>
       </c>
       <c r="B219" t="n">
-        <v>0.7058605551719666</v>
+        <v>0.7058602571487427</v>
       </c>
       <c r="C219" t="n">
-        <v>11.99321937561035</v>
+        <v>11.99322032928467</v>
       </c>
       <c r="D219" t="n">
         <v>30.77606201171875</v>
       </c>
       <c r="E219" t="n">
-        <v>-4.842243194580078</v>
+        <v>-4.842244625091553</v>
       </c>
       <c r="F219" t="n">
-        <v>-3.744931936264038</v>
+        <v>-3.744932174682617</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>-8.682629585266113</v>
+        <v>-8.68262767791748</v>
       </c>
       <c r="B220" t="n">
         <v>2.814561367034912</v>
@@ -4834,30 +4834,30 @@
         <v>31.53286170959473</v>
       </c>
       <c r="E220" t="n">
-        <v>-4.160192489624023</v>
+        <v>-4.160191535949707</v>
       </c>
       <c r="F220" t="n">
-        <v>-3.045682191848755</v>
+        <v>-3.045681953430176</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>-9.62076473236084</v>
+        <v>-9.620762825012207</v>
       </c>
       <c r="B221" t="n">
-        <v>5.362067699432373</v>
+        <v>5.362067222595215</v>
       </c>
       <c r="C221" t="n">
-        <v>14.10321140289307</v>
+        <v>14.10321235656738</v>
       </c>
       <c r="D221" t="n">
-        <v>32.38537979125977</v>
+        <v>32.38538360595703</v>
       </c>
       <c r="E221" t="n">
-        <v>-1.08768093585968</v>
+        <v>-1.087680459022522</v>
       </c>
       <c r="F221" t="n">
-        <v>-2.71554160118103</v>
+        <v>-2.715541362762451</v>
       </c>
     </row>
     <row r="222">
@@ -4865,7 +4865,7 @@
         <v>-10.18505001068115</v>
       </c>
       <c r="B222" t="n">
-        <v>8.628350257873535</v>
+        <v>8.628351211547852</v>
       </c>
       <c r="C222" t="n">
         <v>13.9066333770752</v>
@@ -4874,10 +4874,10 @@
         <v>33.16251373291016</v>
       </c>
       <c r="E222" t="n">
-        <v>3.114234685897827</v>
+        <v>3.114234924316406</v>
       </c>
       <c r="F222" t="n">
-        <v>-3.691694974899292</v>
+        <v>-3.691694736480713</v>
       </c>
     </row>
     <row r="223">
@@ -4885,16 +4885,16 @@
         <v>-10.13324451446533</v>
       </c>
       <c r="B223" t="n">
-        <v>12.89998149871826</v>
+        <v>12.89998245239258</v>
       </c>
       <c r="C223" t="n">
         <v>12.39472103118896</v>
       </c>
       <c r="D223" t="n">
-        <v>33.78033828735352</v>
+        <v>33.78034210205078</v>
       </c>
       <c r="E223" t="n">
-        <v>7.368969917297363</v>
+        <v>7.36897087097168</v>
       </c>
       <c r="F223" t="n">
         <v>-6.174063682556152</v>
@@ -4902,7 +4902,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>-9.296061515808105</v>
+        <v>-9.296059608459473</v>
       </c>
       <c r="B224" t="n">
         <v>18.09382438659668</v>
@@ -4917,15 +4917,15 @@
         <v>11.19097518920898</v>
       </c>
       <c r="F224" t="n">
-        <v>-6.304224014282227</v>
+        <v>-6.304224491119385</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>-7.674902439117432</v>
+        <v>-7.67490291595459</v>
       </c>
       <c r="B225" t="n">
-        <v>23.70100975036621</v>
+        <v>23.70101165771484</v>
       </c>
       <c r="C225" t="n">
         <v>2.032542943954468</v>
@@ -4934,7 +4934,7 @@
         <v>36.92168807983398</v>
       </c>
       <c r="E225" t="n">
-        <v>14.83047676086426</v>
+        <v>14.83047866821289</v>
       </c>
       <c r="F225" t="n">
         <v>-8.207394599914551</v>
@@ -4942,10 +4942,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>-5.44089937210083</v>
+        <v>-5.440899848937988</v>
       </c>
       <c r="B226" t="n">
-        <v>29.23537445068359</v>
+        <v>29.23537635803223</v>
       </c>
       <c r="C226" t="n">
         <v>-6.969193935394287</v>
@@ -4954,7 +4954,7 @@
         <v>36.69089508056641</v>
       </c>
       <c r="E226" t="n">
-        <v>18.04172897338867</v>
+        <v>18.04172706604004</v>
       </c>
       <c r="F226" t="n">
         <v>-8.190280914306641</v>
@@ -4962,13 +4962,13 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>-2.660976886749268</v>
+        <v>-2.660976648330688</v>
       </c>
       <c r="B227" t="n">
-        <v>34.73098373413086</v>
+        <v>34.73097991943359</v>
       </c>
       <c r="C227" t="n">
-        <v>-14.55852794647217</v>
+        <v>-14.55852699279785</v>
       </c>
       <c r="D227" t="n">
         <v>35.83695220947266</v>
@@ -4982,10 +4982,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>0.7270388007164001</v>
+        <v>0.7270400524139404</v>
       </c>
       <c r="B228" t="n">
-        <v>40.63057708740234</v>
+        <v>40.63057327270508</v>
       </c>
       <c r="C228" t="n">
         <v>-16.95425224304199</v>
@@ -5008,16 +5008,16 @@
         <v>47.07179260253906</v>
       </c>
       <c r="C229" t="n">
-        <v>-14.53153228759766</v>
+        <v>-14.53153133392334</v>
       </c>
       <c r="D229" t="n">
-        <v>31.97977828979492</v>
+        <v>31.97977638244629</v>
       </c>
       <c r="E229" t="n">
-        <v>20.37187767028809</v>
+        <v>20.37187957763672</v>
       </c>
       <c r="F229" t="n">
-        <v>-2.779771089553833</v>
+        <v>-2.779771327972412</v>
       </c>
     </row>
     <row r="230">
@@ -5028,7 +5028,7 @@
         <v>53.28283309936523</v>
       </c>
       <c r="C230" t="n">
-        <v>-10.12814044952393</v>
+        <v>-10.12813949584961</v>
       </c>
       <c r="D230" t="n">
         <v>29.21370887756348</v>
@@ -5037,7 +5037,7 @@
         <v>18.75815200805664</v>
       </c>
       <c r="F230" t="n">
-        <v>-1.171901941299438</v>
+        <v>-1.171901822090149</v>
       </c>
     </row>
     <row r="231">
@@ -5048,16 +5048,16 @@
         <v>58.09766387939453</v>
       </c>
       <c r="C231" t="n">
-        <v>-5.716984272003174</v>
+        <v>-5.716983795166016</v>
       </c>
       <c r="D231" t="n">
         <v>26.18086433410645</v>
       </c>
       <c r="E231" t="n">
-        <v>16.65291404724121</v>
+        <v>16.65291213989258</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.005332360975444317</v>
+        <v>-0.005332418717443943</v>
       </c>
     </row>
     <row r="232">
@@ -5065,16 +5065,16 @@
         <v>17.14870452880859</v>
       </c>
       <c r="B232" t="n">
-        <v>60.7369499206543</v>
+        <v>60.73695373535156</v>
       </c>
       <c r="C232" t="n">
         <v>-2.068775653839111</v>
       </c>
       <c r="D232" t="n">
-        <v>23.05877876281738</v>
+        <v>23.05878067016602</v>
       </c>
       <c r="E232" t="n">
-        <v>14.27495861053467</v>
+        <v>14.27495765686035</v>
       </c>
       <c r="F232" t="n">
         <v>0.6683197021484375</v>
@@ -5088,13 +5088,13 @@
         <v>60.86723709106445</v>
       </c>
       <c r="C233" t="n">
-        <v>0.5338540077209473</v>
+        <v>0.5338539481163025</v>
       </c>
       <c r="D233" t="n">
         <v>19.95163154602051</v>
       </c>
       <c r="E233" t="n">
-        <v>11.73736763000488</v>
+        <v>11.73736667633057</v>
       </c>
       <c r="F233" t="n">
         <v>0.93326336145401</v>
@@ -5102,13 +5102,13 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>22.93546867370605</v>
+        <v>22.93546676635742</v>
       </c>
       <c r="B234" t="n">
         <v>58.5799674987793</v>
       </c>
       <c r="C234" t="n">
-        <v>2.13553524017334</v>
+        <v>2.135535001754761</v>
       </c>
       <c r="D234" t="n">
         <v>16.92017936706543</v>
@@ -5128,7 +5128,7 @@
         <v>54.17561721801758</v>
       </c>
       <c r="C235" t="n">
-        <v>3.0105881690979</v>
+        <v>3.010588407516479</v>
       </c>
       <c r="D235" t="n">
         <v>14.00596809387207</v>
@@ -5142,10 +5142,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>26.29769325256348</v>
+        <v>26.29769134521484</v>
       </c>
       <c r="B236" t="n">
-        <v>48.02933883666992</v>
+        <v>48.02933502197266</v>
       </c>
       <c r="C236" t="n">
         <v>3.411523580551147</v>
@@ -5154,7 +5154,7 @@
         <v>11.22652244567871</v>
       </c>
       <c r="E236" t="n">
-        <v>5.45721435546875</v>
+        <v>5.457214832305908</v>
       </c>
       <c r="F236" t="n">
         <v>1.95520806312561</v>
@@ -5168,7 +5168,7 @@
         <v>40.59378433227539</v>
       </c>
       <c r="C237" t="n">
-        <v>3.351086616516113</v>
+        <v>3.351086854934692</v>
       </c>
       <c r="D237" t="n">
         <v>8.558294296264648</v>
@@ -5188,13 +5188,13 @@
         <v>32.41020584106445</v>
       </c>
       <c r="C238" t="n">
-        <v>2.600748538970947</v>
+        <v>2.600748777389526</v>
       </c>
       <c r="D238" t="n">
         <v>5.930117607116699</v>
       </c>
       <c r="E238" t="n">
-        <v>3.478049993515015</v>
+        <v>3.478049755096436</v>
       </c>
       <c r="F238" t="n">
         <v>4.125571250915527</v>
@@ -5202,19 +5202,19 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>27.18849563598633</v>
+        <v>27.1884937286377</v>
       </c>
       <c r="B239" t="n">
-        <v>24.06142425537109</v>
+        <v>24.06142616271973</v>
       </c>
       <c r="C239" t="n">
-        <v>0.9494385719299316</v>
+        <v>0.949438750743866</v>
       </c>
       <c r="D239" t="n">
-        <v>3.244021415710449</v>
+        <v>3.244021654129028</v>
       </c>
       <c r="E239" t="n">
-        <v>2.72213339805603</v>
+        <v>2.722131967544556</v>
       </c>
       <c r="F239" t="n">
         <v>5.272953033447266</v>
@@ -5222,7 +5222,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>26.78322410583496</v>
+        <v>26.78322601318359</v>
       </c>
       <c r="B240" t="n">
         <v>16.09529304504395</v>
@@ -5231,10 +5231,10 @@
         <v>-1.355484843254089</v>
       </c>
       <c r="D240" t="n">
-        <v>0.4227877259254456</v>
+        <v>0.4227879643440247</v>
       </c>
       <c r="E240" t="n">
-        <v>1.878974795341492</v>
+        <v>1.878975033760071</v>
       </c>
       <c r="F240" t="n">
         <v>6.249489784240723</v>
@@ -5248,21 +5248,21 @@
         <v>9.015069961547852</v>
       </c>
       <c r="C241" t="n">
-        <v>-3.36154317855835</v>
+        <v>-3.361543416976929</v>
       </c>
       <c r="D241" t="n">
-        <v>-2.540711402893066</v>
+        <v>-2.540710210800171</v>
       </c>
       <c r="E241" t="n">
         <v>0.9102362394332886</v>
       </c>
       <c r="F241" t="n">
-        <v>7.068041801452637</v>
+        <v>7.068041324615479</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>26.32605934143066</v>
+        <v>26.32605743408203</v>
       </c>
       <c r="B242" t="n">
         <v>3.313672542572021</v>
@@ -5271,30 +5271,30 @@
         <v>-3.967965602874756</v>
       </c>
       <c r="D242" t="n">
-        <v>-5.562167167663574</v>
+        <v>-5.562167644500732</v>
       </c>
       <c r="E242" t="n">
-        <v>-0.08888065814971924</v>
+        <v>-0.08888007700443268</v>
       </c>
       <c r="F242" t="n">
-        <v>7.768786907196045</v>
+        <v>7.768787384033203</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>26.6735782623291</v>
+        <v>26.67357635498047</v>
       </c>
       <c r="B243" t="n">
-        <v>-0.5154204964637756</v>
+        <v>-0.5154212713241577</v>
       </c>
       <c r="C243" t="n">
-        <v>-3.133388996124268</v>
+        <v>-3.133389472961426</v>
       </c>
       <c r="D243" t="n">
-        <v>-8.497763633728027</v>
+        <v>-8.497764587402344</v>
       </c>
       <c r="E243" t="n">
-        <v>-0.9346886873245239</v>
+        <v>-0.9346901178359985</v>
       </c>
       <c r="F243" t="n">
         <v>8.368043899536133</v>
@@ -5305,16 +5305,16 @@
         <v>27.29908561706543</v>
       </c>
       <c r="B244" t="n">
-        <v>-2.156371593475342</v>
+        <v>-2.1563720703125</v>
       </c>
       <c r="C244" t="n">
         <v>-1.871567368507385</v>
       </c>
       <c r="D244" t="n">
-        <v>-11.19789409637451</v>
+        <v>-11.1978931427002</v>
       </c>
       <c r="E244" t="n">
-        <v>-1.421621441841125</v>
+        <v>-1.421621322631836</v>
       </c>
       <c r="F244" t="n">
         <v>8.86894702911377</v>
@@ -5325,19 +5325,19 @@
         <v>27.95905685424805</v>
       </c>
       <c r="B245" t="n">
-        <v>-1.769334316253662</v>
+        <v>-1.769333720207214</v>
       </c>
       <c r="C245" t="n">
         <v>-1.282746195793152</v>
       </c>
       <c r="D245" t="n">
-        <v>-13.53405284881592</v>
+        <v>-13.53405380249023</v>
       </c>
       <c r="E245" t="n">
-        <v>-1.350719571113586</v>
+        <v>-1.350719213485718</v>
       </c>
       <c r="F245" t="n">
-        <v>9.24886417388916</v>
+        <v>9.248863220214844</v>
       </c>
     </row>
     <row r="246">
@@ -5345,16 +5345,16 @@
         <v>28.52372550964355</v>
       </c>
       <c r="B246" t="n">
-        <v>0.2792725265026093</v>
+        <v>0.279273122549057</v>
       </c>
       <c r="C246" t="n">
-        <v>-1.847443461418152</v>
+        <v>-1.847443580627441</v>
       </c>
       <c r="D246" t="n">
-        <v>-15.39406108856201</v>
+        <v>-15.3940601348877</v>
       </c>
       <c r="E246" t="n">
-        <v>-0.5190259218215942</v>
+        <v>-0.5190241932868958</v>
       </c>
       <c r="F246" t="n">
         <v>9.439068794250488</v>
@@ -5365,36 +5365,36 @@
         <v>28.9925479888916</v>
       </c>
       <c r="B247" t="n">
-        <v>3.517055034637451</v>
+        <v>3.51705527305603</v>
       </c>
       <c r="C247" t="n">
         <v>-3.327019691467285</v>
       </c>
       <c r="D247" t="n">
-        <v>-16.66752433776855</v>
+        <v>-16.66752815246582</v>
       </c>
       <c r="E247" t="n">
-        <v>1.267757296562195</v>
+        <v>1.267757534980774</v>
       </c>
       <c r="F247" t="n">
-        <v>9.326447486877441</v>
+        <v>9.326446533203125</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>29.39312553405762</v>
+        <v>29.39312362670898</v>
       </c>
       <c r="B248" t="n">
-        <v>7.358150959014893</v>
+        <v>7.358151435852051</v>
       </c>
       <c r="C248" t="n">
         <v>-5.071263313293457</v>
       </c>
       <c r="D248" t="n">
-        <v>-17.24724006652832</v>
+        <v>-17.24724388122559</v>
       </c>
       <c r="E248" t="n">
-        <v>4.134988784790039</v>
+        <v>4.134987831115723</v>
       </c>
       <c r="F248" t="n">
         <v>8.633082389831543</v>
@@ -5411,27 +5411,27 @@
         <v>-6.292547225952148</v>
       </c>
       <c r="D249" t="n">
-        <v>-17.04879188537598</v>
+        <v>-17.04879379272461</v>
       </c>
       <c r="E249" t="n">
         <v>8.071102142333984</v>
       </c>
       <c r="F249" t="n">
-        <v>6.696539878845215</v>
+        <v>6.696540355682373</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>31.6697883605957</v>
+        <v>31.66978645324707</v>
       </c>
       <c r="B250" t="n">
-        <v>9.35643482208252</v>
+        <v>9.356435775756836</v>
       </c>
       <c r="C250" t="n">
-        <v>-3.321012496948242</v>
+        <v>-3.321012258529663</v>
       </c>
       <c r="D250" t="n">
-        <v>-17.92427253723145</v>
+        <v>-17.92427635192871</v>
       </c>
       <c r="E250" t="n">
         <v>18.3529109954834</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>31.87593460083008</v>
+        <v>31.87593269348145</v>
       </c>
       <c r="B251" t="n">
         <v>12.98259449005127</v>
@@ -5451,10 +5451,10 @@
         <v>-5.858014106750488</v>
       </c>
       <c r="D251" t="n">
-        <v>-16.00893211364746</v>
+        <v>-16.00893402099609</v>
       </c>
       <c r="E251" t="n">
-        <v>23.39445686340332</v>
+        <v>23.39445495605469</v>
       </c>
       <c r="F251" t="n">
         <v>-6.667009353637695</v>
@@ -5462,22 +5462,22 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>31.93228912353516</v>
+        <v>31.93228721618652</v>
       </c>
       <c r="B252" t="n">
-        <v>16.9053840637207</v>
+        <v>16.90538597106934</v>
       </c>
       <c r="C252" t="n">
         <v>-6.107502937316895</v>
       </c>
       <c r="D252" t="n">
-        <v>-13.26381206512451</v>
+        <v>-13.2638111114502</v>
       </c>
       <c r="E252" t="n">
         <v>29.27588653564453</v>
       </c>
       <c r="F252" t="n">
-        <v>-14.34745502471924</v>
+        <v>-14.34745407104492</v>
       </c>
     </row>
     <row r="253">
@@ -5491,30 +5491,30 @@
         <v>-4.296149730682373</v>
       </c>
       <c r="D253" t="n">
-        <v>-9.748528480529785</v>
+        <v>-9.748527526855469</v>
       </c>
       <c r="E253" t="n">
         <v>36.14126968383789</v>
       </c>
       <c r="F253" t="n">
-        <v>-17.57941246032715</v>
+        <v>-17.57941436767578</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>30.20388603210449</v>
+        <v>30.20388412475586</v>
       </c>
       <c r="B254" t="n">
         <v>21.53725242614746</v>
       </c>
       <c r="C254" t="n">
-        <v>-1.859370112419128</v>
+        <v>-1.859369993209839</v>
       </c>
       <c r="D254" t="n">
-        <v>-5.587170600891113</v>
+        <v>-5.587169170379639</v>
       </c>
       <c r="E254" t="n">
-        <v>43.60052871704102</v>
+        <v>43.60053253173828</v>
       </c>
       <c r="F254" t="n">
         <v>-15.54479312896729</v>
@@ -5522,19 +5522,19 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>27.82575607299805</v>
+        <v>27.82575416564941</v>
       </c>
       <c r="B255" t="n">
         <v>20.2386646270752</v>
       </c>
       <c r="C255" t="n">
-        <v>0.1563394367694855</v>
+        <v>0.1563393324613571</v>
       </c>
       <c r="D255" t="n">
-        <v>-0.9973248839378357</v>
+        <v>-0.9973246455192566</v>
       </c>
       <c r="E255" t="n">
-        <v>50.55423736572266</v>
+        <v>50.55424118041992</v>
       </c>
       <c r="F255" t="n">
         <v>-10.69872379302979</v>
@@ -5548,10 +5548,10 @@
         <v>17.47593688964844</v>
       </c>
       <c r="C256" t="n">
-        <v>1.591849207878113</v>
+        <v>1.591848969459534</v>
       </c>
       <c r="D256" t="n">
-        <v>3.693599700927734</v>
+        <v>3.693598985671997</v>
       </c>
       <c r="E256" t="n">
         <v>55.79479217529297</v>
@@ -5574,10 +5574,10 @@
         <v>8.169285774230957</v>
       </c>
       <c r="E257" t="n">
-        <v>58.60061645507812</v>
+        <v>58.60062026977539</v>
       </c>
       <c r="F257" t="n">
-        <v>-0.8587443828582764</v>
+        <v>-0.8587444424629211</v>
       </c>
     </row>
     <row r="258">
@@ -5585,19 +5585,19 @@
         <v>18.97776985168457</v>
       </c>
       <c r="B258" t="n">
-        <v>13.11509799957275</v>
+        <v>13.11509895324707</v>
       </c>
       <c r="C258" t="n">
-        <v>3.841182231903076</v>
+        <v>3.841182470321655</v>
       </c>
       <c r="D258" t="n">
-        <v>12.20143699645996</v>
+        <v>12.20143604278564</v>
       </c>
       <c r="E258" t="n">
         <v>58.77616882324219</v>
       </c>
       <c r="F258" t="n">
-        <v>2.073701620101929</v>
+        <v>2.07370138168335</v>
       </c>
     </row>
     <row r="259">
@@ -5614,7 +5614,7 @@
         <v>15.67985439300537</v>
       </c>
       <c r="E259" t="n">
-        <v>56.53317260742188</v>
+        <v>56.53317642211914</v>
       </c>
       <c r="F259" t="n">
         <v>3.506303548812866</v>
@@ -5634,10 +5634,10 @@
         <v>18.56222534179688</v>
       </c>
       <c r="E260" t="n">
-        <v>52.38088226318359</v>
+        <v>52.38088607788086</v>
       </c>
       <c r="F260" t="n">
-        <v>4.035130500793457</v>
+        <v>4.035130977630615</v>
       </c>
     </row>
     <row r="261">
@@ -5648,7 +5648,7 @@
         <v>7.982079982757568</v>
       </c>
       <c r="C261" t="n">
-        <v>5.62659740447998</v>
+        <v>5.626596927642822</v>
       </c>
       <c r="D261" t="n">
         <v>20.80656051635742</v>
@@ -5662,13 +5662,13 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>8.672327995300293</v>
+        <v>8.672328948974609</v>
       </c>
       <c r="B262" t="n">
-        <v>5.682637691497803</v>
+        <v>5.682638168334961</v>
       </c>
       <c r="C262" t="n">
-        <v>5.849120140075684</v>
+        <v>5.849119663238525</v>
       </c>
       <c r="D262" t="n">
         <v>22.37074279785156</v>
@@ -5677,18 +5677,18 @@
         <v>40.2563362121582</v>
       </c>
       <c r="F262" t="n">
-        <v>4.190563201904297</v>
+        <v>4.190563678741455</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>5.844159603118896</v>
+        <v>5.844160079956055</v>
       </c>
       <c r="B263" t="n">
-        <v>3.59528112411499</v>
+        <v>3.595280170440674</v>
       </c>
       <c r="C263" t="n">
-        <v>6.184038639068604</v>
+        <v>6.184037685394287</v>
       </c>
       <c r="D263" t="n">
         <v>23.26683044433594</v>
@@ -5702,13 +5702,13 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>2.984753131866455</v>
+        <v>2.984753370285034</v>
       </c>
       <c r="B264" t="n">
-        <v>1.955738544464111</v>
+        <v>1.955737709999084</v>
       </c>
       <c r="C264" t="n">
-        <v>6.777114868164062</v>
+        <v>6.777115345001221</v>
       </c>
       <c r="D264" t="n">
         <v>23.59543800354004</v>
@@ -5722,13 +5722,13 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>0.1822294890880585</v>
+        <v>0.1822297722101212</v>
       </c>
       <c r="B265" t="n">
-        <v>0.8602756857872009</v>
+        <v>0.8602753877639771</v>
       </c>
       <c r="C265" t="n">
-        <v>7.666539192199707</v>
+        <v>7.666538715362549</v>
       </c>
       <c r="D265" t="n">
         <v>23.53094673156738</v>
@@ -5742,50 +5742,50 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>-2.444584369659424</v>
+        <v>-2.444584131240845</v>
       </c>
       <c r="B266" t="n">
-        <v>0.3979191482067108</v>
+        <v>0.3979187905788422</v>
       </c>
       <c r="C266" t="n">
         <v>8.844539642333984</v>
       </c>
       <c r="D266" t="n">
-        <v>23.31101417541504</v>
+        <v>23.31101226806641</v>
       </c>
       <c r="E266" t="n">
         <v>8.901814460754395</v>
       </c>
       <c r="F266" t="n">
-        <v>-0.01673091575503349</v>
+        <v>-0.01673097163438797</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>-4.782082080841064</v>
+        <v>-4.782082557678223</v>
       </c>
       <c r="B267" t="n">
-        <v>0.6112102866172791</v>
+        <v>0.6112099885940552</v>
       </c>
       <c r="C267" t="n">
-        <v>10.2617712020874</v>
+        <v>10.26177310943604</v>
       </c>
       <c r="D267" t="n">
         <v>23.1527042388916</v>
       </c>
       <c r="E267" t="n">
-        <v>2.307258367538452</v>
+        <v>2.307258129119873</v>
       </c>
       <c r="F267" t="n">
-        <v>-0.7932679653167725</v>
+        <v>-0.7932680249214172</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>-6.775272846221924</v>
+        <v>-6.775273323059082</v>
       </c>
       <c r="B268" t="n">
-        <v>1.412596225738525</v>
+        <v>1.412595391273499</v>
       </c>
       <c r="C268" t="n">
         <v>11.76390361785889</v>
@@ -5794,30 +5794,30 @@
         <v>23.20088577270508</v>
       </c>
       <c r="E268" t="n">
-        <v>-2.506288766860962</v>
+        <v>-2.506289005279541</v>
       </c>
       <c r="F268" t="n">
-        <v>-0.9441509246826172</v>
+        <v>-0.9441507458686829</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>-8.457690238952637</v>
+        <v>-8.457688331604004</v>
       </c>
       <c r="B269" t="n">
         <v>2.572008609771729</v>
       </c>
       <c r="C269" t="n">
-        <v>13.08506107330322</v>
+        <v>13.08506202697754</v>
       </c>
       <c r="D269" t="n">
         <v>23.49345016479492</v>
       </c>
       <c r="E269" t="n">
-        <v>-4.942520141601562</v>
+        <v>-4.942519664764404</v>
       </c>
       <c r="F269" t="n">
-        <v>-0.5351746082305908</v>
+        <v>-0.5351746678352356</v>
       </c>
     </row>
     <row r="270">
@@ -5825,19 +5825,19 @@
         <v>-9.914505958557129</v>
       </c>
       <c r="B270" t="n">
-        <v>3.869619846343994</v>
+        <v>3.869619607925415</v>
       </c>
       <c r="C270" t="n">
-        <v>13.97856426239014</v>
+        <v>13.97856521606445</v>
       </c>
       <c r="D270" t="n">
         <v>23.98394203186035</v>
       </c>
       <c r="E270" t="n">
-        <v>-4.872562408447266</v>
+        <v>-4.872562885284424</v>
       </c>
       <c r="F270" t="n">
-        <v>0.1904264539480209</v>
+        <v>0.1904263943433762</v>
       </c>
     </row>
     <row r="271">
@@ -5848,13 +5848,13 @@
         <v>5.337913036346436</v>
       </c>
       <c r="C271" t="n">
-        <v>14.42394065856934</v>
+        <v>14.42394256591797</v>
       </c>
       <c r="D271" t="n">
         <v>24.58280944824219</v>
       </c>
       <c r="E271" t="n">
-        <v>-2.732731103897095</v>
+        <v>-2.732729911804199</v>
       </c>
       <c r="F271" t="n">
         <v>0.7501280307769775</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>-12.15121936798096</v>
+        <v>-12.15121746063232</v>
       </c>
       <c r="B272" t="n">
         <v>7.319169521331787</v>
@@ -5874,10 +5874,10 @@
         <v>25.18586921691895</v>
       </c>
       <c r="E272" t="n">
-        <v>0.6705931425094604</v>
+        <v>0.6705914735794067</v>
       </c>
       <c r="F272" t="n">
-        <v>0.4851627349853516</v>
+        <v>0.4851627945899963</v>
       </c>
     </row>
     <row r="273">
@@ -5885,19 +5885,19 @@
         <v>-12.62585544586182</v>
       </c>
       <c r="B273" t="n">
-        <v>10.28879261016846</v>
+        <v>10.28879356384277</v>
       </c>
       <c r="C273" t="n">
-        <v>14.03341197967529</v>
+        <v>14.03341293334961</v>
       </c>
       <c r="D273" t="n">
         <v>25.73011589050293</v>
       </c>
       <c r="E273" t="n">
-        <v>4.542939186096191</v>
+        <v>4.542938232421875</v>
       </c>
       <c r="F273" t="n">
-        <v>-1.091395854949951</v>
+        <v>-1.09139621257782</v>
       </c>
     </row>
     <row r="274">
@@ -5911,13 +5911,13 @@
         <v>12.35265159606934</v>
       </c>
       <c r="D274" t="n">
-        <v>26.21180152893066</v>
+        <v>26.2118034362793</v>
       </c>
       <c r="E274" t="n">
-        <v>8.490161895751953</v>
+        <v>8.490160942077637</v>
       </c>
       <c r="F274" t="n">
-        <v>-3.587116956710815</v>
+        <v>-3.587116718292236</v>
       </c>
     </row>
     <row r="275">
@@ -5925,19 +5925,19 @@
         <v>-11.25396633148193</v>
       </c>
       <c r="B275" t="n">
-        <v>19.80963134765625</v>
+        <v>19.80963325500488</v>
       </c>
       <c r="C275" t="n">
         <v>8.268256187438965</v>
       </c>
       <c r="D275" t="n">
-        <v>31.90181350708008</v>
+        <v>31.90181159973145</v>
       </c>
       <c r="E275" t="n">
         <v>9.901643753051758</v>
       </c>
       <c r="F275" t="n">
-        <v>-3.978342294692993</v>
+        <v>-3.978342056274414</v>
       </c>
     </row>
     <row r="276">
@@ -5948,13 +5948,13 @@
         <v>25.51922607421875</v>
       </c>
       <c r="C276" t="n">
-        <v>0.7406582832336426</v>
+        <v>0.7406582236289978</v>
       </c>
       <c r="D276" t="n">
         <v>32.05158233642578</v>
       </c>
       <c r="E276" t="n">
-        <v>13.37623023986816</v>
+        <v>13.37623119354248</v>
       </c>
       <c r="F276" t="n">
         <v>-6.384820938110352</v>
@@ -5962,7 +5962,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>-7.038326740264893</v>
+        <v>-7.038327217102051</v>
       </c>
       <c r="B277" t="n">
         <v>31.05095100402832</v>
@@ -5974,7 +5974,7 @@
         <v>31.75988578796387</v>
       </c>
       <c r="E277" t="n">
-        <v>16.45963478088379</v>
+        <v>16.45963287353516</v>
       </c>
       <c r="F277" t="n">
         <v>-6.757152557373047</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>-4.389912128448486</v>
+        <v>-4.389910697937012</v>
       </c>
       <c r="B278" t="n">
-        <v>36.28329849243164</v>
+        <v>36.28329467773438</v>
       </c>
       <c r="C278" t="n">
         <v>-15.86844348907471</v>
@@ -6002,33 +6002,33 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>-1.338901996612549</v>
+        <v>-1.338902711868286</v>
       </c>
       <c r="B279" t="n">
-        <v>41.59658813476562</v>
+        <v>41.59658432006836</v>
       </c>
       <c r="C279" t="n">
-        <v>-17.52120971679688</v>
+        <v>-17.52121162414551</v>
       </c>
       <c r="D279" t="n">
         <v>29.37483024597168</v>
       </c>
       <c r="E279" t="n">
-        <v>20.1416187286377</v>
+        <v>20.14161682128906</v>
       </c>
       <c r="F279" t="n">
-        <v>-2.611788034439087</v>
+        <v>-2.611788272857666</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>2.275186061859131</v>
+        <v>2.275187253952026</v>
       </c>
       <c r="B280" t="n">
-        <v>47.29164505004883</v>
+        <v>47.29164123535156</v>
       </c>
       <c r="C280" t="n">
-        <v>-14.7103853225708</v>
+        <v>-14.71038341522217</v>
       </c>
       <c r="D280" t="n">
         <v>27.15071487426758</v>
@@ -6037,7 +6037,7 @@
         <v>19.93883895874023</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.422720193862915</v>
+        <v>-0.4227201342582703</v>
       </c>
     </row>
     <row r="281">
@@ -6054,7 +6054,7 @@
         <v>24.37943649291992</v>
       </c>
       <c r="E281" t="n">
-        <v>18.67798805236816</v>
+        <v>18.67798614501953</v>
       </c>
       <c r="F281" t="n">
         <v>1.242243409156799</v>
@@ -6085,10 +6085,10 @@
         <v>14.93144512176514</v>
       </c>
       <c r="B283" t="n">
-        <v>60.28279876708984</v>
+        <v>60.28279495239258</v>
       </c>
       <c r="C283" t="n">
-        <v>-1.677970051765442</v>
+        <v>-1.677969932556152</v>
       </c>
       <c r="D283" t="n">
         <v>18.06912994384766</v>
@@ -6108,7 +6108,7 @@
         <v>60.81088638305664</v>
       </c>
       <c r="C284" t="n">
-        <v>1.485304594039917</v>
+        <v>1.485304474830627</v>
       </c>
       <c r="D284" t="n">
         <v>14.85952091217041</v>
@@ -6117,7 +6117,7 @@
         <v>12.25128364562988</v>
       </c>
       <c r="F284" t="n">
-        <v>3.900246620178223</v>
+        <v>3.900246858596802</v>
       </c>
     </row>
     <row r="285">
@@ -6128,7 +6128,7 @@
         <v>59.03470230102539</v>
       </c>
       <c r="C285" t="n">
-        <v>3.687251091003418</v>
+        <v>3.687250852584839</v>
       </c>
       <c r="D285" t="n">
         <v>11.71191692352295</v>
@@ -6145,7 +6145,7 @@
         <v>23.69665718078613</v>
       </c>
       <c r="B286" t="n">
-        <v>55.16071701049805</v>
+        <v>55.16071319580078</v>
       </c>
       <c r="C286" t="n">
         <v>4.812975883483887</v>
@@ -6154,15 +6154,15 @@
         <v>8.657866477966309</v>
       </c>
       <c r="E286" t="n">
-        <v>6.796085357666016</v>
+        <v>6.796084403991699</v>
       </c>
       <c r="F286" t="n">
-        <v>3.950659275054932</v>
+        <v>3.950659513473511</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>25.34774971008301</v>
+        <v>25.34774780273438</v>
       </c>
       <c r="B287" t="n">
         <v>49.54737854003906</v>
@@ -6174,7 +6174,7 @@
         <v>5.721749305725098</v>
       </c>
       <c r="E287" t="n">
-        <v>4.566328048706055</v>
+        <v>4.566327571868896</v>
       </c>
       <c r="F287" t="n">
         <v>4.229508399963379</v>
@@ -6185,16 +6185,16 @@
         <v>26.42864799499512</v>
       </c>
       <c r="B288" t="n">
-        <v>42.6045036315918</v>
+        <v>42.60449981689453</v>
       </c>
       <c r="C288" t="n">
         <v>4.659284591674805</v>
       </c>
       <c r="D288" t="n">
-        <v>2.917705535888672</v>
+        <v>2.917705774307251</v>
       </c>
       <c r="E288" t="n">
-        <v>2.998502492904663</v>
+        <v>2.998502254486084</v>
       </c>
       <c r="F288" t="n">
         <v>4.915377140045166</v>
@@ -6208,13 +6208,13 @@
         <v>34.83768463134766</v>
       </c>
       <c r="C289" t="n">
-        <v>3.637292146682739</v>
+        <v>3.637291669845581</v>
       </c>
       <c r="D289" t="n">
-        <v>0.2260294556617737</v>
+        <v>0.226029708981514</v>
       </c>
       <c r="E289" t="n">
-        <v>2.077577352523804</v>
+        <v>2.077577590942383</v>
       </c>
       <c r="F289" t="n">
         <v>6.00917387008667</v>
@@ -6228,16 +6228,16 @@
         <v>26.84604263305664</v>
       </c>
       <c r="C290" t="n">
-        <v>2.140953063964844</v>
+        <v>2.140953302383423</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.410183906555176</v>
+        <v>-2.410184621810913</v>
       </c>
       <c r="E290" t="n">
-        <v>1.61303699016571</v>
+        <v>1.613036751747131</v>
       </c>
       <c r="F290" t="n">
-        <v>7.393526554107666</v>
+        <v>7.393527030944824</v>
       </c>
     </row>
     <row r="291">
@@ -6251,10 +6251,10 @@
         <v>0.7043432593345642</v>
       </c>
       <c r="D291" t="n">
-        <v>-5.05064868927002</v>
+        <v>-5.050649166107178</v>
       </c>
       <c r="E291" t="n">
-        <v>1.343419909477234</v>
+        <v>1.343421101570129</v>
       </c>
       <c r="F291" t="n">
         <v>8.840039253234863</v>
@@ -6268,16 +6268,16 @@
         <v>11.99857044219971</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.1150012984871864</v>
+        <v>-0.1150015071034431</v>
       </c>
       <c r="D292" t="n">
-        <v>-7.705105781555176</v>
+        <v>-7.705106258392334</v>
       </c>
       <c r="E292" t="n">
-        <v>1.087509036064148</v>
+        <v>1.087509274482727</v>
       </c>
       <c r="F292" t="n">
-        <v>10.10252475738525</v>
+        <v>10.10252571105957</v>
       </c>
     </row>
     <row r="293">
@@ -6285,36 +6285,36 @@
         <v>26.18528747558594</v>
       </c>
       <c r="B293" t="n">
-        <v>5.646430492401123</v>
+        <v>5.646430015563965</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.2775132358074188</v>
+        <v>-0.277513325214386</v>
       </c>
       <c r="D293" t="n">
-        <v>-10.306077003479</v>
+        <v>-10.30607795715332</v>
       </c>
       <c r="E293" t="n">
-        <v>0.8509958982467651</v>
+        <v>0.8509944677352905</v>
       </c>
       <c r="F293" t="n">
-        <v>11.04039001464844</v>
+        <v>11.04039096832275</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>26.11285781860352</v>
+        <v>26.11285591125488</v>
       </c>
       <c r="B294" t="n">
-        <v>0.6741699576377869</v>
+        <v>0.674169659614563</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.1022987142205238</v>
+        <v>-0.1022985652089119</v>
       </c>
       <c r="D294" t="n">
-        <v>-12.73534679412842</v>
+        <v>-12.73534774780273</v>
       </c>
       <c r="E294" t="n">
-        <v>0.8164900541305542</v>
+        <v>0.8164905309677124</v>
       </c>
       <c r="F294" t="n">
         <v>11.68004131317139</v>
@@ -6325,19 +6325,19 @@
         <v>26.33414459228516</v>
       </c>
       <c r="B295" t="n">
-        <v>-2.132318019866943</v>
+        <v>-2.132318496704102</v>
       </c>
       <c r="C295" t="n">
-        <v>0.2722843587398529</v>
+        <v>0.272284209728241</v>
       </c>
       <c r="D295" t="n">
-        <v>-14.87861919403076</v>
+        <v>-14.87862014770508</v>
       </c>
       <c r="E295" t="n">
-        <v>1.230445742607117</v>
+        <v>1.23044741153717</v>
       </c>
       <c r="F295" t="n">
-        <v>12.15431213378906</v>
+        <v>12.15431308746338</v>
       </c>
     </row>
     <row r="296">
@@ -6345,19 +6345,19 @@
         <v>26.79885673522949</v>
       </c>
       <c r="B296" t="n">
-        <v>-2.43464994430542</v>
+        <v>-2.434649467468262</v>
       </c>
       <c r="C296" t="n">
-        <v>0.9026802182197571</v>
+        <v>0.9026803374290466</v>
       </c>
       <c r="D296" t="n">
-        <v>-16.65167045593262</v>
+        <v>-16.65167427062988</v>
       </c>
       <c r="E296" t="n">
-        <v>2.305284261703491</v>
+        <v>2.30528450012207</v>
       </c>
       <c r="F296" t="n">
-        <v>12.54055786132812</v>
+        <v>12.54055881500244</v>
       </c>
     </row>
     <row r="297">
@@ -6365,19 +6365,19 @@
         <v>27.35630035400391</v>
       </c>
       <c r="B297" t="n">
-        <v>-0.6113258004188538</v>
+        <v>-0.6113256216049194</v>
       </c>
       <c r="C297" t="n">
-        <v>1.627059459686279</v>
+        <v>1.627059102058411</v>
       </c>
       <c r="D297" t="n">
-        <v>-18.02019309997559</v>
+        <v>-18.02019691467285</v>
       </c>
       <c r="E297" t="n">
-        <v>4.127233505249023</v>
+        <v>4.127233028411865</v>
       </c>
       <c r="F297" t="n">
-        <v>12.72392463684082</v>
+        <v>12.72392559051514</v>
       </c>
     </row>
     <row r="298">
@@ -6385,19 +6385,19 @@
         <v>27.75378608703613</v>
       </c>
       <c r="B298" t="n">
-        <v>2.294563770294189</v>
+        <v>2.294563293457031</v>
       </c>
       <c r="C298" t="n">
-        <v>1.70838725566864</v>
+        <v>1.708387494087219</v>
       </c>
       <c r="D298" t="n">
-        <v>-18.9348316192627</v>
+        <v>-18.93483543395996</v>
       </c>
       <c r="E298" t="n">
-        <v>6.708157539367676</v>
+        <v>6.708157062530518</v>
       </c>
       <c r="F298" t="n">
-        <v>12.35292053222656</v>
+        <v>12.35292148590088</v>
       </c>
     </row>
     <row r="299">
@@ -6405,19 +6405,19 @@
         <v>27.7932243347168</v>
       </c>
       <c r="B299" t="n">
-        <v>5.071384906768799</v>
+        <v>5.071383953094482</v>
       </c>
       <c r="C299" t="n">
-        <v>0.1474975645542145</v>
+        <v>0.1474975794553757</v>
       </c>
       <c r="D299" t="n">
         <v>-19.3039493560791</v>
       </c>
       <c r="E299" t="n">
-        <v>9.998783111572266</v>
+        <v>9.998782157897949</v>
       </c>
       <c r="F299" t="n">
-        <v>10.83739376068115</v>
+        <v>10.83739566802979</v>
       </c>
     </row>
     <row r="300">
@@ -6428,7 +6428,7 @@
         <v>7.407253742218018</v>
       </c>
       <c r="C300" t="n">
-        <v>-2.949342727661133</v>
+        <v>-2.949343204498291</v>
       </c>
       <c r="D300" t="n">
         <v>-19.00379371643066</v>
@@ -6445,7 +6445,7 @@
         <v>31.08670043945312</v>
       </c>
       <c r="B301" t="n">
-        <v>9.238124847412109</v>
+        <v>9.238125801086426</v>
       </c>
       <c r="C301" t="n">
         <v>-3.012162685394287</v>
@@ -6457,41 +6457,41 @@
         <v>16.28764343261719</v>
       </c>
       <c r="F301" t="n">
-        <v>-0.6944396495819092</v>
+        <v>-0.6944399476051331</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>31.59165573120117</v>
+        <v>31.59165382385254</v>
       </c>
       <c r="B302" t="n">
         <v>13.06134128570557</v>
       </c>
       <c r="C302" t="n">
-        <v>-5.081531047821045</v>
+        <v>-5.081531524658203</v>
       </c>
       <c r="D302" t="n">
-        <v>-15.53035640716553</v>
+        <v>-15.53035545349121</v>
       </c>
       <c r="E302" t="n">
-        <v>21.677001953125</v>
+        <v>21.67700004577637</v>
       </c>
       <c r="F302" t="n">
-        <v>-8.705644607543945</v>
+        <v>-8.705643653869629</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>31.84779739379883</v>
+        <v>31.8477954864502</v>
       </c>
       <c r="B303" t="n">
         <v>16.73609352111816</v>
       </c>
       <c r="C303" t="n">
-        <v>-5.623135566711426</v>
+        <v>-5.623136043548584</v>
       </c>
       <c r="D303" t="n">
-        <v>-12.30511379241943</v>
+        <v>-12.30511474609375</v>
       </c>
       <c r="E303" t="n">
         <v>27.86951637268066</v>
@@ -6502,16 +6502,16 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>31.55015182495117</v>
+        <v>31.55014991760254</v>
       </c>
       <c r="B304" t="n">
         <v>19.40524101257324</v>
       </c>
       <c r="C304" t="n">
-        <v>-4.682677268981934</v>
+        <v>-4.682677745819092</v>
       </c>
       <c r="D304" t="n">
-        <v>-8.382142066955566</v>
+        <v>-8.38214111328125</v>
       </c>
       <c r="E304" t="n">
         <v>34.65926361083984</v>
@@ -6522,22 +6522,22 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>30.39152908325195</v>
+        <v>30.39153099060059</v>
       </c>
       <c r="B305" t="n">
         <v>20.10323905944824</v>
       </c>
       <c r="C305" t="n">
-        <v>-3.121367454528809</v>
+        <v>-3.121367692947388</v>
       </c>
       <c r="D305" t="n">
-        <v>-3.973160743713379</v>
+        <v>-3.973161458969116</v>
       </c>
       <c r="E305" t="n">
         <v>41.58562469482422</v>
       </c>
       <c r="F305" t="n">
-        <v>-17.43003273010254</v>
+        <v>-17.43003463745117</v>
       </c>
     </row>
     <row r="306">
@@ -6548,16 +6548,16 @@
         <v>18.78349304199219</v>
       </c>
       <c r="C306" t="n">
-        <v>-1.646306872367859</v>
+        <v>-1.646306753158569</v>
       </c>
       <c r="D306" t="n">
-        <v>0.7387877106666565</v>
+        <v>0.7387879490852356</v>
       </c>
       <c r="E306" t="n">
-        <v>47.93990707397461</v>
+        <v>47.93991088867188</v>
       </c>
       <c r="F306" t="n">
-        <v>-13.67917251586914</v>
+        <v>-13.67917156219482</v>
       </c>
     </row>
     <row r="307">
@@ -6568,13 +6568,13 @@
         <v>16.41655158996582</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.3866532742977142</v>
+        <v>-0.3866532444953918</v>
       </c>
       <c r="D307" t="n">
         <v>5.578110694885254</v>
       </c>
       <c r="E307" t="n">
-        <v>53.00543212890625</v>
+        <v>53.00543594360352</v>
       </c>
       <c r="F307" t="n">
         <v>-9.418597221374512</v>
@@ -6594,7 +6594,7 @@
         <v>10.3545618057251</v>
       </c>
       <c r="E308" t="n">
-        <v>56.30694580078125</v>
+        <v>56.30694961547852</v>
       </c>
       <c r="F308" t="n">
         <v>-5.667858123779297</v>
@@ -6608,16 +6608,16 @@
         <v>12.27369117736816</v>
       </c>
       <c r="C309" t="n">
-        <v>1.88377046585083</v>
+        <v>1.883770108222961</v>
       </c>
       <c r="D309" t="n">
         <v>14.86788082122803</v>
       </c>
       <c r="E309" t="n">
-        <v>57.64303207397461</v>
+        <v>57.64303970336914</v>
       </c>
       <c r="F309" t="n">
-        <v>-2.741374254226685</v>
+        <v>-2.741374492645264</v>
       </c>
     </row>
     <row r="310">
@@ -6625,19 +6625,19 @@
         <v>17.87735557556152</v>
       </c>
       <c r="B310" t="n">
-        <v>10.45798587799072</v>
+        <v>10.45798683166504</v>
       </c>
       <c r="C310" t="n">
-        <v>2.646105289459229</v>
+        <v>2.646105527877808</v>
       </c>
       <c r="D310" t="n">
         <v>18.93386268615723</v>
       </c>
       <c r="E310" t="n">
-        <v>57.01817321777344</v>
+        <v>57.0181770324707</v>
       </c>
       <c r="F310" t="n">
-        <v>-0.4954097270965576</v>
+        <v>-0.4954095482826233</v>
       </c>
     </row>
     <row r="311">
@@ -6648,16 +6648,16 @@
         <v>8.244766235351562</v>
       </c>
       <c r="C311" t="n">
-        <v>2.945981502532959</v>
+        <v>2.945981740951538</v>
       </c>
       <c r="D311" t="n">
         <v>22.4028148651123</v>
       </c>
       <c r="E311" t="n">
-        <v>54.56760025024414</v>
+        <v>54.56760406494141</v>
       </c>
       <c r="F311" t="n">
-        <v>1.353364944458008</v>
+        <v>1.353364825248718</v>
       </c>
     </row>
     <row r="312">
@@ -6671,10 +6671,10 @@
         <v>2.958673238754272</v>
       </c>
       <c r="D312" t="n">
-        <v>25.16475868225098</v>
+        <v>25.16476058959961</v>
       </c>
       <c r="E312" t="n">
-        <v>50.47197341918945</v>
+        <v>50.47197723388672</v>
       </c>
       <c r="F312" t="n">
         <v>2.857524394989014</v>
@@ -6702,13 +6702,13 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>7.074121952056885</v>
+        <v>7.074122428894043</v>
       </c>
       <c r="B314" t="n">
-        <v>1.315016269683838</v>
+        <v>1.315016865730286</v>
       </c>
       <c r="C314" t="n">
-        <v>3.395411968231201</v>
+        <v>3.395411729812622</v>
       </c>
       <c r="D314" t="n">
         <v>28.35718727111816</v>
@@ -6722,19 +6722,19 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>4.494717121124268</v>
+        <v>4.494717597961426</v>
       </c>
       <c r="B315" t="n">
-        <v>0.06683583557605743</v>
+        <v>0.06683549284934998</v>
       </c>
       <c r="C315" t="n">
-        <v>4.075055122375488</v>
+        <v>4.07505464553833</v>
       </c>
       <c r="D315" t="n">
         <v>28.83552742004395</v>
       </c>
       <c r="E315" t="n">
-        <v>29.94781112670898</v>
+        <v>29.94781303405762</v>
       </c>
       <c r="F315" t="n">
         <v>2.958987712860107</v>
@@ -6742,10 +6742,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>2.043290615081787</v>
+        <v>2.04328989982605</v>
       </c>
       <c r="B316" t="n">
-        <v>-0.5185371041297913</v>
+        <v>-0.5185364484786987</v>
       </c>
       <c r="C316" t="n">
         <v>5.040204524993896</v>
@@ -6762,59 +6762,59 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>-0.2908263504505157</v>
+        <v>-0.2908270061016083</v>
       </c>
       <c r="B317" t="n">
-        <v>-0.5851092934608459</v>
+        <v>-0.5851105451583862</v>
       </c>
       <c r="C317" t="n">
-        <v>6.27881908416748</v>
+        <v>6.278818607330322</v>
       </c>
       <c r="D317" t="n">
-        <v>28.26858329772949</v>
+        <v>28.26858139038086</v>
       </c>
       <c r="E317" t="n">
-        <v>12.59984302520752</v>
+        <v>12.59984397888184</v>
       </c>
       <c r="F317" t="n">
-        <v>0.09127604216337204</v>
+        <v>0.09127610176801682</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>-2.513737201690674</v>
+        <v>-2.513736963272095</v>
       </c>
       <c r="B318" t="n">
-        <v>-0.2890010178089142</v>
+        <v>-0.2890013754367828</v>
       </c>
       <c r="C318" t="n">
-        <v>7.767562866210938</v>
+        <v>7.767562389373779</v>
       </c>
       <c r="D318" t="n">
         <v>27.77482223510742</v>
       </c>
       <c r="E318" t="n">
-        <v>4.697787284851074</v>
+        <v>4.697786808013916</v>
       </c>
       <c r="F318" t="n">
-        <v>-1.157662153244019</v>
+        <v>-1.157662510871887</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>-4.596842288970947</v>
+        <v>-4.596842765808105</v>
       </c>
       <c r="B319" t="n">
-        <v>0.2924351394176483</v>
+        <v>0.2924347817897797</v>
       </c>
       <c r="C319" t="n">
-        <v>9.412167549133301</v>
+        <v>9.412168502807617</v>
       </c>
       <c r="D319" t="n">
         <v>27.5660514831543</v>
       </c>
       <c r="E319" t="n">
-        <v>-1.424286007881165</v>
+        <v>-1.424284934997559</v>
       </c>
       <c r="F319" t="n">
         <v>-2.020572900772095</v>
@@ -6822,42 +6822,42 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>-6.49478006362915</v>
+        <v>-6.494780540466309</v>
       </c>
       <c r="B320" t="n">
-        <v>1.158592700958252</v>
+        <v>1.158592343330383</v>
       </c>
       <c r="C320" t="n">
-        <v>11.05802536010742</v>
+        <v>11.05802631378174</v>
       </c>
       <c r="D320" t="n">
         <v>27.82413673400879</v>
       </c>
       <c r="E320" t="n">
-        <v>-4.860734939575195</v>
+        <v>-4.860735416412354</v>
       </c>
       <c r="F320" t="n">
-        <v>-2.453289747238159</v>
+        <v>-2.45328950881958</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>-8.176962852478027</v>
+        <v>-8.17696475982666</v>
       </c>
       <c r="B321" t="n">
         <v>2.336090564727783</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48443603515625</v>
+        <v>12.48443698883057</v>
       </c>
       <c r="D321" t="n">
         <v>28.50441741943359</v>
       </c>
       <c r="E321" t="n">
-        <v>-5.260976791381836</v>
+        <v>-5.26097583770752</v>
       </c>
       <c r="F321" t="n">
-        <v>-2.448487997055054</v>
+        <v>-2.448488235473633</v>
       </c>
     </row>
     <row r="322">
@@ -6865,16 +6865,16 @@
         <v>-9.616084098815918</v>
       </c>
       <c r="B322" t="n">
-        <v>3.88789701461792</v>
+        <v>3.887897729873657</v>
       </c>
       <c r="C322" t="n">
-        <v>13.44190311431885</v>
+        <v>13.44190406799316</v>
       </c>
       <c r="D322" t="n">
         <v>29.38434791564941</v>
       </c>
       <c r="E322" t="n">
-        <v>-3.072067499160767</v>
+        <v>-3.072068452835083</v>
       </c>
       <c r="F322" t="n">
         <v>-2.23276162147522</v>
@@ -6882,22 +6882,22 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>-10.72534084320068</v>
+        <v>-10.72533893585205</v>
       </c>
       <c r="B323" t="n">
-        <v>5.991917133331299</v>
+        <v>5.991916656494141</v>
       </c>
       <c r="C323" t="n">
         <v>13.76377487182617</v>
       </c>
       <c r="D323" t="n">
-        <v>30.20112800598145</v>
+        <v>30.20112609863281</v>
       </c>
       <c r="E323" t="n">
-        <v>0.6637495756149292</v>
+        <v>0.6637489795684814</v>
       </c>
       <c r="F323" t="n">
-        <v>-2.400422334671021</v>
+        <v>-2.4004225730896</v>
       </c>
     </row>
     <row r="324">
@@ -6908,21 +6908,21 @@
         <v>8.960597038269043</v>
       </c>
       <c r="C324" t="n">
-        <v>13.32777214050293</v>
+        <v>13.32777404785156</v>
       </c>
       <c r="D324" t="n">
-        <v>30.79345512390137</v>
+        <v>30.79345321655273</v>
       </c>
       <c r="E324" t="n">
-        <v>4.755143165588379</v>
+        <v>4.755142688751221</v>
       </c>
       <c r="F324" t="n">
-        <v>-3.62670111656189</v>
+        <v>-3.626701354980469</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>-11.18564319610596</v>
+        <v>-11.18564128875732</v>
       </c>
       <c r="B325" t="n">
         <v>13.06296539306641</v>
@@ -6934,7 +6934,7 @@
         <v>31.16432571411133</v>
       </c>
       <c r="E325" t="n">
-        <v>8.50784969329834</v>
+        <v>8.507850646972656</v>
       </c>
       <c r="F325" t="n">
         <v>-5.855995655059814</v>
@@ -6948,16 +6948,16 @@
         <v>18.18915748596191</v>
       </c>
       <c r="C326" t="n">
-        <v>8.210342407226562</v>
+        <v>8.210343360900879</v>
       </c>
       <c r="D326" t="n">
         <v>35.12921905517578</v>
       </c>
       <c r="E326" t="n">
-        <v>9.886085510253906</v>
+        <v>9.886086463928223</v>
       </c>
       <c r="F326" t="n">
-        <v>-2.825040578842163</v>
+        <v>-2.825040340423584</v>
       </c>
     </row>
     <row r="327">
@@ -6974,24 +6974,24 @@
         <v>34.98503112792969</v>
       </c>
       <c r="E327" t="n">
-        <v>12.92237186431885</v>
+        <v>12.92237091064453</v>
       </c>
       <c r="F327" t="n">
-        <v>-5.510586738586426</v>
+        <v>-5.510586261749268</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>-6.209860324859619</v>
+        <v>-6.209860801696777</v>
       </c>
       <c r="B328" t="n">
         <v>29.22015953063965</v>
       </c>
       <c r="C328" t="n">
-        <v>-7.456206798553467</v>
+        <v>-7.456207275390625</v>
       </c>
       <c r="D328" t="n">
-        <v>34.66277313232422</v>
+        <v>34.66277694702148</v>
       </c>
       <c r="E328" t="n">
         <v>16.15936851501465</v>
@@ -7002,13 +7002,13 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>-3.597980976104736</v>
+        <v>-3.597981691360474</v>
       </c>
       <c r="B329" t="n">
         <v>34.4768180847168</v>
       </c>
       <c r="C329" t="n">
-        <v>-15.58848857879639</v>
+        <v>-15.58848762512207</v>
       </c>
       <c r="D329" t="n">
         <v>33.97869873046875</v>
@@ -7017,15 +7017,15 @@
         <v>19.26612281799316</v>
       </c>
       <c r="F329" t="n">
-        <v>-5.942198276519775</v>
+        <v>-5.942197799682617</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>-0.597452700138092</v>
+        <v>-0.5974533557891846</v>
       </c>
       <c r="B330" t="n">
-        <v>39.9274787902832</v>
+        <v>39.92747497558594</v>
       </c>
       <c r="C330" t="n">
         <v>-18.4377269744873</v>
@@ -7037,12 +7037,12 @@
         <v>21.28592300415039</v>
       </c>
       <c r="F330" t="n">
-        <v>-4.081764221191406</v>
+        <v>-4.081763744354248</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2.856654644012451</v>
+        <v>2.856655836105347</v>
       </c>
       <c r="B331" t="n">
         <v>45.81814956665039</v>
@@ -7054,10 +7054,10 @@
         <v>30.52180099487305</v>
       </c>
       <c r="E331" t="n">
-        <v>21.61802101135254</v>
+        <v>21.61802291870117</v>
       </c>
       <c r="F331" t="n">
-        <v>-1.967394113540649</v>
+        <v>-1.967394232749939</v>
       </c>
     </row>
     <row r="332">
@@ -7068,7 +7068,7 @@
         <v>51.62485885620117</v>
       </c>
       <c r="C332" t="n">
-        <v>-11.08823013305664</v>
+        <v>-11.08822917938232</v>
       </c>
       <c r="D332" t="n">
         <v>27.70955657958984</v>
@@ -7077,27 +7077,27 @@
         <v>20.3947639465332</v>
       </c>
       <c r="F332" t="n">
-        <v>-0.2073061615228653</v>
+        <v>-0.2073062211275101</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>10.58195209503174</v>
+        <v>10.58195304870605</v>
       </c>
       <c r="B333" t="n">
-        <v>56.3541374206543</v>
+        <v>56.35413360595703</v>
       </c>
       <c r="C333" t="n">
         <v>-6.182998657226562</v>
       </c>
       <c r="D333" t="n">
-        <v>24.47668647766113</v>
+        <v>24.4766845703125</v>
       </c>
       <c r="E333" t="n">
         <v>18.20417785644531</v>
       </c>
       <c r="F333" t="n">
-        <v>0.9674418568611145</v>
+        <v>0.9674419164657593</v>
       </c>
     </row>
     <row r="334">
@@ -7108,16 +7108,16 @@
         <v>59.2757453918457</v>
       </c>
       <c r="C334" t="n">
-        <v>-2.070919752120972</v>
+        <v>-2.070919990539551</v>
       </c>
       <c r="D334" t="n">
         <v>21.09543228149414</v>
       </c>
       <c r="E334" t="n">
-        <v>15.60925960540771</v>
+        <v>15.6092586517334</v>
       </c>
       <c r="F334" t="n">
-        <v>1.598337650299072</v>
+        <v>1.598337531089783</v>
       </c>
     </row>
     <row r="335">
@@ -7125,10 +7125,10 @@
         <v>17.62735366821289</v>
       </c>
       <c r="B335" t="n">
-        <v>60.05558013916016</v>
+        <v>60.05557632446289</v>
       </c>
       <c r="C335" t="n">
-        <v>1.018105983734131</v>
+        <v>1.018105864524841</v>
       </c>
       <c r="D335" t="n">
         <v>17.7625904083252</v>
@@ -7137,7 +7137,7 @@
         <v>12.92425918579102</v>
       </c>
       <c r="F335" t="n">
-        <v>1.863215088844299</v>
+        <v>1.86321496963501</v>
       </c>
     </row>
     <row r="336">
@@ -7148,7 +7148,7 @@
         <v>58.65088653564453</v>
       </c>
       <c r="C336" t="n">
-        <v>3.050923585891724</v>
+        <v>3.050924062728882</v>
       </c>
       <c r="D336" t="n">
         <v>14.59097766876221</v>
@@ -7168,7 +7168,7 @@
         <v>55.17965698242188</v>
       </c>
       <c r="C337" t="n">
-        <v>4.08879566192627</v>
+        <v>4.088795185089111</v>
       </c>
       <c r="D337" t="n">
         <v>11.62412071228027</v>
@@ -7177,7 +7177,7 @@
         <v>8.174695014953613</v>
       </c>
       <c r="F337" t="n">
-        <v>2.490543603897095</v>
+        <v>2.490543365478516</v>
       </c>
     </row>
     <row r="338">
@@ -7185,19 +7185,19 @@
         <v>24.64143753051758</v>
       </c>
       <c r="B338" t="n">
-        <v>49.84169006347656</v>
+        <v>49.8416862487793</v>
       </c>
       <c r="C338" t="n">
         <v>4.264204978942871</v>
       </c>
       <c r="D338" t="n">
-        <v>8.840459823608398</v>
+        <v>8.840458869934082</v>
       </c>
       <c r="E338" t="n">
         <v>6.516834259033203</v>
       </c>
       <c r="F338" t="n">
-        <v>3.392050504684448</v>
+        <v>3.392050743103027</v>
       </c>
     </row>
     <row r="339">
@@ -7214,7 +7214,7 @@
         <v>6.159235954284668</v>
       </c>
       <c r="E339" t="n">
-        <v>5.366410255432129</v>
+        <v>5.366409778594971</v>
       </c>
       <c r="F339" t="n">
         <v>4.711570739746094</v>
@@ -7231,13 +7231,13 @@
         <v>2.283150911331177</v>
       </c>
       <c r="D340" t="n">
-        <v>3.46970272064209</v>
+        <v>3.469702959060669</v>
       </c>
       <c r="E340" t="n">
         <v>4.548820495605469</v>
       </c>
       <c r="F340" t="n">
-        <v>6.238394737243652</v>
+        <v>6.238395214080811</v>
       </c>
     </row>
     <row r="341">
@@ -7248,13 +7248,13 @@
         <v>26.53713989257812</v>
       </c>
       <c r="C341" t="n">
-        <v>0.2739945352077484</v>
+        <v>0.2739946246147156</v>
       </c>
       <c r="D341" t="n">
-        <v>0.6750727295875549</v>
+        <v>0.6750720143318176</v>
       </c>
       <c r="E341" t="n">
-        <v>3.864812612533569</v>
+        <v>3.864813804626465</v>
       </c>
       <c r="F341" t="n">
         <v>7.750905513763428</v>
@@ -7268,16 +7268,16 @@
         <v>18.49092292785645</v>
       </c>
       <c r="C342" t="n">
-        <v>-1.708052515983582</v>
+        <v>-1.708052396774292</v>
       </c>
       <c r="D342" t="n">
-        <v>-2.266816139221191</v>
+        <v>-2.266816854476929</v>
       </c>
       <c r="E342" t="n">
-        <v>3.184818029403687</v>
+        <v>3.184818744659424</v>
       </c>
       <c r="F342" t="n">
-        <v>9.176568031311035</v>
+        <v>9.176567077636719</v>
       </c>
     </row>
     <row r="343">
@@ -7285,36 +7285,36 @@
         <v>26.05327606201172</v>
       </c>
       <c r="B343" t="n">
-        <v>11.33625507354736</v>
+        <v>11.33625602722168</v>
       </c>
       <c r="C343" t="n">
-        <v>-2.777345418930054</v>
+        <v>-2.777345657348633</v>
       </c>
       <c r="D343" t="n">
-        <v>-5.323197364807129</v>
+        <v>-5.323195934295654</v>
       </c>
       <c r="E343" t="n">
-        <v>2.490949392318726</v>
+        <v>2.4909508228302</v>
       </c>
       <c r="F343" t="n">
-        <v>10.55712604522705</v>
+        <v>10.55712699890137</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>25.9245777130127</v>
+        <v>25.92457580566406</v>
       </c>
       <c r="B344" t="n">
         <v>5.423089504241943</v>
       </c>
       <c r="C344" t="n">
-        <v>-2.654611349105835</v>
+        <v>-2.654611587524414</v>
       </c>
       <c r="D344" t="n">
-        <v>-8.385991096496582</v>
+        <v>-8.385990142822266</v>
       </c>
       <c r="E344" t="n">
-        <v>1.876876711845398</v>
+        <v>1.876876473426819</v>
       </c>
       <c r="F344" t="n">
         <v>11.85321807861328</v>
@@ -7325,16 +7325,16 @@
         <v>26.04547691345215</v>
       </c>
       <c r="B345" t="n">
-        <v>1.197557926177979</v>
+        <v>1.19755756855011</v>
       </c>
       <c r="C345" t="n">
-        <v>-1.986711621284485</v>
+        <v>-1.986711502075195</v>
       </c>
       <c r="D345" t="n">
-        <v>-11.30513477325439</v>
+        <v>-11.30513572692871</v>
       </c>
       <c r="E345" t="n">
-        <v>1.493549227714539</v>
+        <v>1.493548512458801</v>
       </c>
       <c r="F345" t="n">
         <v>12.93313312530518</v>
@@ -7345,19 +7345,19 @@
         <v>26.34553337097168</v>
       </c>
       <c r="B346" t="n">
-        <v>-0.9006667733192444</v>
+        <v>-0.9006670713424683</v>
       </c>
       <c r="C346" t="n">
-        <v>-1.429258942604065</v>
+        <v>-1.429259061813354</v>
       </c>
       <c r="D346" t="n">
-        <v>-13.93363285064697</v>
+        <v>-13.93363189697266</v>
       </c>
       <c r="E346" t="n">
-        <v>1.505535006523132</v>
+        <v>1.505536913871765</v>
       </c>
       <c r="F346" t="n">
-        <v>13.67775630950928</v>
+        <v>13.67775726318359</v>
       </c>
     </row>
     <row r="347">
@@ -7365,16 +7365,16 @@
         <v>26.6917552947998</v>
       </c>
       <c r="B347" t="n">
-        <v>-0.8145785927772522</v>
+        <v>-0.8145779371261597</v>
       </c>
       <c r="C347" t="n">
-        <v>-1.07324755191803</v>
+        <v>-1.07324743270874</v>
       </c>
       <c r="D347" t="n">
-        <v>-16.15388679504395</v>
+        <v>-16.15388870239258</v>
       </c>
       <c r="E347" t="n">
-        <v>2.072435140609741</v>
+        <v>2.072434902191162</v>
       </c>
       <c r="F347" t="n">
         <v>13.98475742340088</v>
@@ -7385,16 +7385,16 @@
         <v>27.0377368927002</v>
       </c>
       <c r="B348" t="n">
-        <v>1.117689609527588</v>
+        <v>1.117690682411194</v>
       </c>
       <c r="C348" t="n">
         <v>-1.053805947303772</v>
       </c>
       <c r="D348" t="n">
-        <v>-17.88127708435059</v>
+        <v>-17.88127899169922</v>
       </c>
       <c r="E348" t="n">
-        <v>3.321691274642944</v>
+        <v>3.321691989898682</v>
       </c>
       <c r="F348" t="n">
         <v>13.69215297698975</v>
@@ -7411,10 +7411,10 @@
         <v>-1.944524168968201</v>
       </c>
       <c r="D349" t="n">
-        <v>-19.03940391540527</v>
+        <v>-19.03940773010254</v>
       </c>
       <c r="E349" t="n">
-        <v>5.328330039978027</v>
+        <v>5.328330516815186</v>
       </c>
       <c r="F349" t="n">
         <v>12.51068115234375</v>
@@ -7425,7 +7425,7 @@
         <v>27.84372138977051</v>
       </c>
       <c r="B350" t="n">
-        <v>7.858650684356689</v>
+        <v>7.858651161193848</v>
       </c>
       <c r="C350" t="n">
         <v>-4.101238250732422</v>
@@ -7434,7 +7434,7 @@
         <v>-19.52038764953613</v>
       </c>
       <c r="E350" t="n">
-        <v>8.130465507507324</v>
+        <v>8.130464553833008</v>
       </c>
       <c r="F350" t="n">
         <v>10.05116844177246</v>
@@ -7445,13 +7445,13 @@
         <v>28.28158950805664</v>
       </c>
       <c r="B351" t="n">
-        <v>11.53035354614258</v>
+        <v>11.53035449981689</v>
       </c>
       <c r="C351" t="n">
-        <v>-6.54477071762085</v>
+        <v>-6.544770240783691</v>
       </c>
       <c r="D351" t="n">
-        <v>-19.17511558532715</v>
+        <v>-19.17511940002441</v>
       </c>
       <c r="E351" t="n">
         <v>11.76816463470459</v>
@@ -7465,39 +7465,39 @@
         <v>32.18456268310547</v>
       </c>
       <c r="B352" t="n">
-        <v>0.4702286422252655</v>
+        <v>0.4702292382717133</v>
       </c>
       <c r="C352" t="n">
-        <v>-5.446859359741211</v>
+        <v>-5.446859836578369</v>
       </c>
       <c r="D352" t="n">
-        <v>-4.766512870788574</v>
+        <v>-4.766513347625732</v>
       </c>
       <c r="E352" t="n">
         <v>20.71337890625</v>
       </c>
       <c r="F352" t="n">
-        <v>11.18691635131836</v>
+        <v>11.18691730499268</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>30.90678405761719</v>
+        <v>30.90678215026855</v>
       </c>
       <c r="B353" t="n">
-        <v>1.628519535064697</v>
+        <v>1.628518223762512</v>
       </c>
       <c r="C353" t="n">
-        <v>-7.153579235076904</v>
+        <v>-7.153579711914062</v>
       </c>
       <c r="D353" t="n">
-        <v>-4.451542854309082</v>
+        <v>-4.451541423797607</v>
       </c>
       <c r="E353" t="n">
         <v>24.97526550292969</v>
       </c>
       <c r="F353" t="n">
-        <v>7.456565856933594</v>
+        <v>7.456566333770752</v>
       </c>
     </row>
     <row r="354">
@@ -7505,13 +7505,13 @@
         <v>29.37425804138184</v>
       </c>
       <c r="B354" t="n">
-        <v>2.633837223052979</v>
+        <v>2.63383674621582</v>
       </c>
       <c r="C354" t="n">
-        <v>-7.99292516708374</v>
+        <v>-7.992926120758057</v>
       </c>
       <c r="D354" t="n">
-        <v>-3.407353401184082</v>
+        <v>-3.407354116439819</v>
       </c>
       <c r="E354" t="n">
         <v>30.06590270996094</v>
@@ -7528,16 +7528,16 @@
         <v>3.36967134475708</v>
       </c>
       <c r="C355" t="n">
-        <v>-7.874218463897705</v>
+        <v>-7.874218940734863</v>
       </c>
       <c r="D355" t="n">
-        <v>-1.554974555969238</v>
+        <v>-1.55497419834137</v>
       </c>
       <c r="E355" t="n">
-        <v>35.98350524902344</v>
+        <v>35.9835090637207</v>
       </c>
       <c r="F355" t="n">
-        <v>-4.798434734344482</v>
+        <v>-4.798434257507324</v>
       </c>
     </row>
     <row r="356">
@@ -7545,13 +7545,13 @@
         <v>25.55225372314453</v>
       </c>
       <c r="B356" t="n">
-        <v>3.632641315460205</v>
+        <v>3.632641792297363</v>
       </c>
       <c r="C356" t="n">
         <v>-7.030215740203857</v>
       </c>
       <c r="D356" t="n">
-        <v>1.124112129211426</v>
+        <v>1.124110579490662</v>
       </c>
       <c r="E356" t="n">
         <v>42.61345291137695</v>
@@ -7565,19 +7565,19 @@
         <v>23.2596549987793</v>
       </c>
       <c r="B357" t="n">
-        <v>3.348804950714111</v>
+        <v>3.348803758621216</v>
       </c>
       <c r="C357" t="n">
         <v>-5.898867130279541</v>
       </c>
       <c r="D357" t="n">
-        <v>4.491733551025391</v>
+        <v>4.491734027862549</v>
       </c>
       <c r="E357" t="n">
-        <v>49.48035049438477</v>
+        <v>49.48035430908203</v>
       </c>
       <c r="F357" t="n">
-        <v>-15.23729801177979</v>
+        <v>-15.23729610443115</v>
       </c>
     </row>
     <row r="358">
@@ -7585,7 +7585,7 @@
         <v>20.79283332824707</v>
       </c>
       <c r="B358" t="n">
-        <v>2.588546276092529</v>
+        <v>2.588545799255371</v>
       </c>
       <c r="C358" t="n">
         <v>-4.782667636871338</v>
@@ -7605,13 +7605,13 @@
         <v>18.25476455688477</v>
       </c>
       <c r="B359" t="n">
-        <v>1.52885103225708</v>
+        <v>1.52885115146637</v>
       </c>
       <c r="C359" t="n">
-        <v>-3.806577682495117</v>
+        <v>-3.806578159332275</v>
       </c>
       <c r="D359" t="n">
-        <v>12.3337230682373</v>
+        <v>12.33372211456299</v>
       </c>
       <c r="E359" t="n">
         <v>60.83515930175781</v>
@@ -7625,27 +7625,27 @@
         <v>15.75786018371582</v>
       </c>
       <c r="B360" t="n">
-        <v>0.4145340621471405</v>
+        <v>0.4145337045192719</v>
       </c>
       <c r="C360" t="n">
-        <v>-2.917726039886475</v>
+        <v>-2.917726278305054</v>
       </c>
       <c r="D360" t="n">
         <v>16.28795433044434</v>
       </c>
       <c r="E360" t="n">
-        <v>63.94036865234375</v>
+        <v>63.94037246704102</v>
       </c>
       <c r="F360" t="n">
-        <v>-9.02980899810791</v>
+        <v>-9.029808044433594</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>13.3914794921875</v>
+        <v>13.39148044586182</v>
       </c>
       <c r="B361" t="n">
-        <v>-0.5524478554725647</v>
+        <v>-0.5524471998214722</v>
       </c>
       <c r="C361" t="n">
         <v>-1.998679280281067</v>
@@ -7654,7 +7654,7 @@
         <v>19.99280166625977</v>
       </c>
       <c r="E361" t="n">
-        <v>65.00290679931641</v>
+        <v>65.00289916992188</v>
       </c>
       <c r="F361" t="n">
         <v>-4.445043087005615</v>
@@ -7665,10 +7665,10 @@
         <v>11.22716903686523</v>
       </c>
       <c r="B362" t="n">
-        <v>-1.225450038909912</v>
+        <v>-1.225449442863464</v>
       </c>
       <c r="C362" t="n">
-        <v>-0.9531592130661011</v>
+        <v>-0.9531591534614563</v>
       </c>
       <c r="D362" t="n">
         <v>23.31063270568848</v>
@@ -7677,27 +7677,27 @@
         <v>63.98999404907227</v>
       </c>
       <c r="F362" t="n">
-        <v>-0.2534463405609131</v>
+        <v>-0.2534464001655579</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>9.282946586608887</v>
+        <v>9.282947540283203</v>
       </c>
       <c r="B363" t="n">
-        <v>-1.564139842987061</v>
+        <v>-1.564140200614929</v>
       </c>
       <c r="C363" t="n">
-        <v>0.242927759885788</v>
+        <v>0.2429277151823044</v>
       </c>
       <c r="D363" t="n">
-        <v>26.17411804199219</v>
+        <v>26.17411613464355</v>
       </c>
       <c r="E363" t="n">
-        <v>61.12539291381836</v>
+        <v>61.12539672851562</v>
       </c>
       <c r="F363" t="n">
-        <v>3.173304080963135</v>
+        <v>3.173304319381714</v>
       </c>
     </row>
     <row r="364">
@@ -7705,16 +7705,16 @@
         <v>7.528273105621338</v>
       </c>
       <c r="B364" t="n">
-        <v>-1.60957670211792</v>
+        <v>-1.609577059745789</v>
       </c>
       <c r="C364" t="n">
-        <v>1.563114523887634</v>
+        <v>1.563114285469055</v>
       </c>
       <c r="D364" t="n">
-        <v>28.53836441040039</v>
+        <v>28.53836631774902</v>
       </c>
       <c r="E364" t="n">
-        <v>56.63148498535156</v>
+        <v>56.63148880004883</v>
       </c>
       <c r="F364" t="n">
         <v>5.678918361663818</v>
@@ -7725,16 +7725,16 @@
         <v>5.913900852203369</v>
       </c>
       <c r="B365" t="n">
-        <v>-1.425002574920654</v>
+        <v>-1.425002932548523</v>
       </c>
       <c r="C365" t="n">
-        <v>2.978968143463135</v>
+        <v>2.978968381881714</v>
       </c>
       <c r="D365" t="n">
-        <v>30.33066940307617</v>
+        <v>30.33066749572754</v>
       </c>
       <c r="E365" t="n">
-        <v>50.65621185302734</v>
+        <v>50.65621566772461</v>
       </c>
       <c r="F365" t="n">
         <v>7.143065452575684</v>
@@ -7742,50 +7742,50 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>4.380726337432861</v>
+        <v>4.38072681427002</v>
       </c>
       <c r="B366" t="n">
-        <v>-1.092338085174561</v>
+        <v>-1.092338442802429</v>
       </c>
       <c r="C366" t="n">
         <v>4.459642887115479</v>
       </c>
       <c r="D366" t="n">
-        <v>31.53822135925293</v>
+        <v>31.5382194519043</v>
       </c>
       <c r="E366" t="n">
-        <v>43.55517959594727</v>
+        <v>43.55518341064453</v>
       </c>
       <c r="F366" t="n">
-        <v>7.576859474182129</v>
+        <v>7.576859951019287</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>2.88119649887085</v>
+        <v>2.881196737289429</v>
       </c>
       <c r="B367" t="n">
-        <v>-0.6992946267127991</v>
+        <v>-0.6992944478988647</v>
       </c>
       <c r="C367" t="n">
-        <v>5.957253932952881</v>
+        <v>5.957252979278564</v>
       </c>
       <c r="D367" t="n">
         <v>32.17497634887695</v>
       </c>
       <c r="E367" t="n">
-        <v>35.74450302124023</v>
+        <v>35.7445068359375</v>
       </c>
       <c r="F367" t="n">
-        <v>7.062152862548828</v>
+        <v>7.062153339385986</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1.387698650360107</v>
+        <v>1.387699842453003</v>
       </c>
       <c r="B368" t="n">
-        <v>-0.3274493515491486</v>
+        <v>-0.3274487555027008</v>
       </c>
       <c r="C368" t="n">
         <v>7.40183687210083</v>
@@ -7802,16 +7802,16 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>-0.09775307774543762</v>
+        <v>-0.09775279462337494</v>
       </c>
       <c r="B369" t="n">
-        <v>-0.01871637813746929</v>
+        <v>-0.01871528849005699</v>
       </c>
       <c r="C369" t="n">
-        <v>8.734431266784668</v>
+        <v>8.734432220458984</v>
       </c>
       <c r="D369" t="n">
-        <v>32.00242233276367</v>
+        <v>32.00242614746094</v>
       </c>
       <c r="E369" t="n">
         <v>19.82099533081055</v>
@@ -7822,30 +7822,30 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>-1.537333011627197</v>
+        <v>-1.537332773208618</v>
       </c>
       <c r="B370" t="n">
-        <v>0.2691349685192108</v>
+        <v>0.2691350877285004</v>
       </c>
       <c r="C370" t="n">
         <v>9.943787574768066</v>
       </c>
       <c r="D370" t="n">
-        <v>31.51648330688477</v>
+        <v>31.51648139953613</v>
       </c>
       <c r="E370" t="n">
-        <v>12.7351713180542</v>
+        <v>12.73517227172852</v>
       </c>
       <c r="F370" t="n">
-        <v>2.890978097915649</v>
+        <v>2.890978336334229</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>-2.873898029327393</v>
+        <v>-2.873897790908813</v>
       </c>
       <c r="B371" t="n">
-        <v>0.6441749930381775</v>
+        <v>0.6441742181777954</v>
       </c>
       <c r="C371" t="n">
         <v>11.02846813201904</v>
@@ -7862,19 +7862,19 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>-4.061039447784424</v>
+        <v>-4.061038017272949</v>
       </c>
       <c r="B372" t="n">
-        <v>1.240339756011963</v>
+        <v>1.240339875221252</v>
       </c>
       <c r="C372" t="n">
-        <v>11.96594429016113</v>
+        <v>11.96594524383545</v>
       </c>
       <c r="D372" t="n">
         <v>30.56024932861328</v>
       </c>
       <c r="E372" t="n">
-        <v>3.567991018295288</v>
+        <v>3.567989826202393</v>
       </c>
       <c r="F372" t="n">
         <v>2.097066164016724</v>
@@ -7882,19 +7882,19 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>-5.103540897369385</v>
+        <v>-5.103541374206543</v>
       </c>
       <c r="B373" t="n">
-        <v>2.135078907012939</v>
+        <v>2.135077953338623</v>
       </c>
       <c r="C373" t="n">
-        <v>12.72584915161133</v>
+        <v>12.72585010528564</v>
       </c>
       <c r="D373" t="n">
         <v>30.24405097961426</v>
       </c>
       <c r="E373" t="n">
-        <v>2.108869314193726</v>
+        <v>2.10886812210083</v>
       </c>
       <c r="F373" t="n">
         <v>2.046056747436523</v>
@@ -7902,19 +7902,19 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>-6.032995700836182</v>
+        <v>-6.03299617767334</v>
       </c>
       <c r="B374" t="n">
-        <v>3.360687732696533</v>
+        <v>3.360688209533691</v>
       </c>
       <c r="C374" t="n">
-        <v>13.26511192321777</v>
+        <v>13.26511287689209</v>
       </c>
       <c r="D374" t="n">
-        <v>29.98687553405762</v>
+        <v>29.98687362670898</v>
       </c>
       <c r="E374" t="n">
-        <v>2.479589223861694</v>
+        <v>2.479588270187378</v>
       </c>
       <c r="F374" t="n">
         <v>1.349458336830139</v>
@@ -7922,27 +7922,27 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>-6.888832569122314</v>
+        <v>-6.888833045959473</v>
       </c>
       <c r="B375" t="n">
         <v>4.920792102813721</v>
       </c>
       <c r="C375" t="n">
-        <v>13.49739742279053</v>
+        <v>13.49739837646484</v>
       </c>
       <c r="D375" t="n">
         <v>29.67742347717285</v>
       </c>
       <c r="E375" t="n">
-        <v>3.815744161605835</v>
+        <v>3.815743923187256</v>
       </c>
       <c r="F375" t="n">
-        <v>-0.4979970455169678</v>
+        <v>-0.4979971051216125</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>-7.680296421051025</v>
+        <v>-7.680294990539551</v>
       </c>
       <c r="B376" t="n">
         <v>6.797675609588623</v>
@@ -7957,27 +7957,27 @@
         <v>5.452352523803711</v>
       </c>
       <c r="F376" t="n">
-        <v>-3.368997812271118</v>
+        <v>-3.368997573852539</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>-8.333846092224121</v>
+        <v>-8.333844184875488</v>
       </c>
       <c r="B377" t="n">
         <v>9.057034492492676</v>
       </c>
       <c r="C377" t="n">
-        <v>12.34715557098389</v>
+        <v>12.3471565246582</v>
       </c>
       <c r="D377" t="n">
         <v>32.72652816772461</v>
       </c>
       <c r="E377" t="n">
-        <v>3.954198598861694</v>
+        <v>3.954197883605957</v>
       </c>
       <c r="F377" t="n">
-        <v>-2.018710374832153</v>
+        <v>-2.018710613250732</v>
       </c>
     </row>
     <row r="378">
@@ -7985,27 +7985,27 @@
         <v>-8.65126895904541</v>
       </c>
       <c r="B378" t="n">
-        <v>11.89263534545898</v>
+        <v>11.8926362991333</v>
       </c>
       <c r="C378" t="n">
-        <v>10.21060657501221</v>
+        <v>10.21060752868652</v>
       </c>
       <c r="D378" t="n">
         <v>31.99587821960449</v>
       </c>
       <c r="E378" t="n">
-        <v>5.740692138671875</v>
+        <v>5.740691661834717</v>
       </c>
       <c r="F378" t="n">
-        <v>-4.987511157989502</v>
+        <v>-4.987510204315186</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>-8.401888847351074</v>
+        <v>-8.401886940002441</v>
       </c>
       <c r="B379" t="n">
-        <v>15.4909029006958</v>
+        <v>15.49090194702148</v>
       </c>
       <c r="C379" t="n">
         <v>6.513414859771729</v>
@@ -8022,7 +8022,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>-7.352436542510986</v>
+        <v>-7.352437019348145</v>
       </c>
       <c r="B380" t="n">
         <v>20.05574989318848</v>
@@ -8042,16 +8042,16 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>-5.302992343902588</v>
+        <v>-5.302992820739746</v>
       </c>
       <c r="B381" t="n">
         <v>25.77397155761719</v>
       </c>
       <c r="C381" t="n">
-        <v>-5.712520122528076</v>
+        <v>-5.712520599365234</v>
       </c>
       <c r="D381" t="n">
-        <v>28.63880920410156</v>
+        <v>28.63880729675293</v>
       </c>
       <c r="E381" t="n">
         <v>10.726806640625</v>
@@ -8062,7 +8062,7 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>-2.296520709991455</v>
+        <v>-2.296520471572876</v>
       </c>
       <c r="B382" t="n">
         <v>32.53843688964844</v>
@@ -8077,12 +8077,12 @@
         <v>11.35634899139404</v>
       </c>
       <c r="F382" t="n">
-        <v>-3.928467988967896</v>
+        <v>-3.928468227386475</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1.515322208404541</v>
+        <v>1.51532244682312</v>
       </c>
       <c r="B383" t="n">
         <v>40.00061416625977</v>
@@ -8097,7 +8097,7 @@
         <v>11.24954319000244</v>
       </c>
       <c r="F383" t="n">
-        <v>-2.108511686325073</v>
+        <v>-2.108511447906494</v>
       </c>
     </row>
     <row r="384">
@@ -8114,10 +8114,10 @@
         <v>22.55454063415527</v>
       </c>
       <c r="E384" t="n">
-        <v>10.4977560043335</v>
+        <v>10.49775505065918</v>
       </c>
       <c r="F384" t="n">
-        <v>-0.6197891235351562</v>
+        <v>-0.619789183139801</v>
       </c>
     </row>
     <row r="385">
@@ -8131,24 +8131,24 @@
         <v>-17.98023223876953</v>
       </c>
       <c r="D385" t="n">
-        <v>20.17120170593262</v>
+        <v>20.17119979858398</v>
       </c>
       <c r="E385" t="n">
         <v>9.335121154785156</v>
       </c>
       <c r="F385" t="n">
-        <v>0.5427780151367188</v>
+        <v>0.542777955532074</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>15.02622032165527</v>
+        <v>15.02622127532959</v>
       </c>
       <c r="B386" t="n">
         <v>59.16970825195312</v>
       </c>
       <c r="C386" t="n">
-        <v>-14.0917854309082</v>
+        <v>-14.09178352355957</v>
       </c>
       <c r="D386" t="n">
         <v>17.78373146057129</v>
@@ -8174,7 +8174,7 @@
         <v>15.4851770401001</v>
       </c>
       <c r="E387" t="n">
-        <v>6.65914249420166</v>
+        <v>6.659141540527344</v>
       </c>
       <c r="F387" t="n">
         <v>2.330123901367188</v>
@@ -8185,7 +8185,7 @@
         <v>23.22729301452637</v>
       </c>
       <c r="B388" t="n">
-        <v>63.22077178955078</v>
+        <v>63.22076797485352</v>
       </c>
       <c r="C388" t="n">
         <v>-4.501337051391602</v>
@@ -8208,7 +8208,7 @@
         <v>62.29937744140625</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.4982365071773529</v>
+        <v>-0.4982362389564514</v>
       </c>
       <c r="D389" t="n">
         <v>11.38720321655273</v>
@@ -8222,19 +8222,19 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>29.6345100402832</v>
+        <v>29.63450813293457</v>
       </c>
       <c r="B390" t="n">
         <v>59.57680511474609</v>
       </c>
       <c r="C390" t="n">
-        <v>2.575315952301025</v>
+        <v>2.575315713882446</v>
       </c>
       <c r="D390" t="n">
-        <v>9.631290435791016</v>
+        <v>9.631291389465332</v>
       </c>
       <c r="E390" t="n">
-        <v>4.592556953430176</v>
+        <v>4.592555522918701</v>
       </c>
       <c r="F390" t="n">
         <v>5.233340740203857</v>
@@ -8251,13 +8251,13 @@
         <v>4.721826076507568</v>
       </c>
       <c r="D391" t="n">
-        <v>8.033862113952637</v>
+        <v>8.03386116027832</v>
       </c>
       <c r="E391" t="n">
-        <v>4.66374683380127</v>
+        <v>4.663746356964111</v>
       </c>
       <c r="F391" t="n">
-        <v>6.500419616699219</v>
+        <v>6.500420093536377</v>
       </c>
     </row>
     <row r="392">
@@ -8271,7 +8271,7 @@
         <v>5.979248523712158</v>
       </c>
       <c r="D392" t="n">
-        <v>6.547124862670898</v>
+        <v>6.547125339508057</v>
       </c>
       <c r="E392" t="n">
         <v>5.001801490783691</v>
@@ -8291,7 +8291,7 @@
         <v>6.306888103485107</v>
       </c>
       <c r="D393" t="n">
-        <v>5.113339424133301</v>
+        <v>5.113339900970459</v>
       </c>
       <c r="E393" t="n">
         <v>5.475825309753418</v>
@@ -8311,10 +8311,10 @@
         <v>5.759813785552979</v>
       </c>
       <c r="D394" t="n">
-        <v>3.693695068359375</v>
+        <v>3.693696260452271</v>
       </c>
       <c r="E394" t="n">
-        <v>5.973424911499023</v>
+        <v>5.973424434661865</v>
       </c>
       <c r="F394" t="n">
         <v>10.35428142547607</v>
@@ -8325,19 +8325,19 @@
         <v>35.24254989624023</v>
       </c>
       <c r="B395" t="n">
-        <v>26.83361053466797</v>
+        <v>26.8336124420166</v>
       </c>
       <c r="C395" t="n">
-        <v>4.673953056335449</v>
+        <v>4.673952579498291</v>
       </c>
       <c r="D395" t="n">
-        <v>2.295432090759277</v>
+        <v>2.295432329177856</v>
       </c>
       <c r="E395" t="n">
-        <v>6.470980644226074</v>
+        <v>6.470981597900391</v>
       </c>
       <c r="F395" t="n">
-        <v>11.41267967224121</v>
+        <v>11.41268062591553</v>
       </c>
     </row>
     <row r="396">
@@ -8348,10 +8348,10 @@
         <v>18.53747749328613</v>
       </c>
       <c r="C396" t="n">
-        <v>3.561429738998413</v>
+        <v>3.561430215835571</v>
       </c>
       <c r="D396" t="n">
-        <v>0.9632273316383362</v>
+        <v>0.9632256627082825</v>
       </c>
       <c r="E396" t="n">
         <v>7.037947654724121</v>
@@ -8362,42 +8362,42 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>34.10770797729492</v>
+        <v>34.10771179199219</v>
       </c>
       <c r="B397" t="n">
         <v>10.68671321868896</v>
       </c>
       <c r="C397" t="n">
-        <v>2.868484020233154</v>
+        <v>2.868483781814575</v>
       </c>
       <c r="D397" t="n">
-        <v>-0.2601136565208435</v>
+        <v>-0.260112464427948</v>
       </c>
       <c r="E397" t="n">
         <v>7.784333229064941</v>
       </c>
       <c r="F397" t="n">
-        <v>13.04567050933838</v>
+        <v>13.04566955566406</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>33.40517044067383</v>
+        <v>33.40517425537109</v>
       </c>
       <c r="B398" t="n">
-        <v>4.010454654693604</v>
+        <v>4.010455131530762</v>
       </c>
       <c r="C398" t="n">
-        <v>2.595665454864502</v>
+        <v>2.595665693283081</v>
       </c>
       <c r="D398" t="n">
-        <v>-1.352969169616699</v>
+        <v>-1.352968811988831</v>
       </c>
       <c r="E398" t="n">
         <v>8.821805000305176</v>
       </c>
       <c r="F398" t="n">
-        <v>13.61008262634277</v>
+        <v>13.61008167266846</v>
       </c>
     </row>
     <row r="399">
@@ -8405,16 +8405,16 @@
         <v>32.80168151855469</v>
       </c>
       <c r="B399" t="n">
-        <v>-0.6952090859413147</v>
+        <v>-0.6952074766159058</v>
       </c>
       <c r="C399" t="n">
-        <v>2.392953872680664</v>
+        <v>2.392954111099243</v>
       </c>
       <c r="D399" t="n">
-        <v>-2.325984001159668</v>
+        <v>-2.325983762741089</v>
       </c>
       <c r="E399" t="n">
-        <v>10.2313814163208</v>
+        <v>10.23138046264648</v>
       </c>
       <c r="F399" t="n">
         <v>14.00447368621826</v>
@@ -8425,13 +8425,13 @@
         <v>32.36367797851562</v>
       </c>
       <c r="B400" t="n">
-        <v>-2.828565120697021</v>
+        <v>-2.82856559753418</v>
       </c>
       <c r="C400" t="n">
         <v>1.644481301307678</v>
       </c>
       <c r="D400" t="n">
-        <v>-3.202292442321777</v>
+        <v>-3.202293157577515</v>
       </c>
       <c r="E400" t="n">
         <v>12.05041790008545</v>
@@ -8445,19 +8445,19 @@
         <v>32.06182098388672</v>
       </c>
       <c r="B401" t="n">
-        <v>-2.635667324066162</v>
+        <v>-2.635666847229004</v>
       </c>
       <c r="C401" t="n">
-        <v>-0.2177453935146332</v>
+        <v>-0.2177451401948929</v>
       </c>
       <c r="D401" t="n">
-        <v>-3.965994834899902</v>
+        <v>-3.96599555015564</v>
       </c>
       <c r="E401" t="n">
         <v>14.34756755828857</v>
       </c>
       <c r="F401" t="n">
-        <v>14.06607437133789</v>
+        <v>14.06607532501221</v>
       </c>
     </row>
   </sheetData>
